--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulm\.cursor\projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D390062-8965-4D51-8333-078EF7CF90D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D40138-E467-4488-9034-F0F8F3AEEE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,10 +17,13 @@
     <sheet name="OptionRules" sheetId="2" r:id="rId2"/>
     <sheet name="OutputLayout" sheetId="5" r:id="rId3"/>
     <sheet name="ActionType" sheetId="6" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="4" state="hidden" r:id="rId5"/>
+    <sheet name="OR_Coupang" sheetId="7" r:id="rId5"/>
+    <sheet name="OL_Coupang" sheetId="8" r:id="rId6"/>
+    <sheet name="Sheet3" sheetId="4" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">OptionRules!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">OR_Coupang!$A$1:$D$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="510">
   <si>
     <t>보내는사람</t>
   </si>
@@ -1395,6 +1398,377 @@
   <si>
     <t>FORMAT_QTY</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>옵션ID</t>
+  </si>
+  <si>
+    <t>최초등록등록상품명/옵션명</t>
+  </si>
+  <si>
+    <t>구매수량</t>
+  </si>
+  <si>
+    <t>상품명 옵션</t>
+  </si>
+  <si>
+    <t>발주서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>옵션 규칙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@참가자미 다시,2개 특대 (250~350g)</t>
+  </si>
+  <si>
+    <t>참가자미 다시,2개 특대 (250~350g) x1</t>
+  </si>
+  <si>
+    <t>참가자미 특대 (250~350g) [2*{구매수량}]개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@오징어순대 아바이순대,700g 1개 야채 오징어순대 2미+명태회무침 세트</t>
+  </si>
+  <si>
+    <t>오징어순대 아바이순대,700g 1개 야채 오징어순대 2미+명태회무침 세트 x1</t>
+  </si>
+  <si>
+    <t>야채 오징어순대 [2*{구매수량}]미+명태회무침 {구매수량}개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@초코오징어,1개 1.3kg내외 원양산 반건조오징어 대 10마리</t>
+  </si>
+  <si>
+    <t>초코오징어,1개 1.3kg내외 원양산 반건조오징어 대 10마리 x1</t>
+  </si>
+  <si>
+    <t>원양산 반건조오징어 대 [10*{구매수량}]마리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@오징어순대 아바이순대,1kg 1개 전통 아바이순대</t>
+  </si>
+  <si>
+    <t>오징어순대 아바이순대,1kg 1개 전통 아바이순대 x1</t>
+  </si>
+  <si>
+    <t>1kg 전통 아바이순대 {구매수량}개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@오징어순대 아바이순대,350g 1개 수제 슬라이스 오징어순대 1미 (순한맛)</t>
+  </si>
+  <si>
+    <t>오징어순대 아바이순대,350g 1개 수제 슬라이스 오징어순대 1미 (순한맛) x2</t>
+  </si>
+  <si>
+    <t>350g 수제 슬라이스 오징어순대 (순한맛) [1*{구매수량}]미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@ 문어다리 새로등록,1개 특대 1.5kg내외</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 문어다리 새로등록,1개 특대 1.5kg내외 x1</t>
+  </si>
+  <si>
+    <t>문어다리특대 1.5kg내외 {구매수량}개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@오징어순대 아바이순대,500g 1개 설악 오징어순대 2미+명태회무침 세트</t>
+  </si>
+  <si>
+    <t>오징어순대 아바이순대,500g 1개 설악 오징어순대 2미+명태회무침 세트 x1</t>
+  </si>
+  <si>
+    <t>설악 오징어순대 [2*{구매수량}]미+명태회무침 {구매수량}개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@홍게 새로등록,1개 라면용홍게 3kg내외(자숙)</t>
+  </si>
+  <si>
+    <t>홍게 새로등록,1개 라면용홍게 3kg내외(자숙) x1</t>
+  </si>
+  <si>
+    <t>라면용홍게 3kg내외(자숙) {구매수량}개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@초코오징어,1개 1~1.1kg내외 특가 냉동오징어 (3~5마리)</t>
+  </si>
+  <si>
+    <t>초코오징어,1개 1~1.1kg내외 특가 냉동오징어 (3~5마리) x1</t>
+  </si>
+  <si>
+    <t>냉동오징어 (3~5마리) {구매수량}개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@명이김 선물세트 3호,1개</t>
+  </si>
+  <si>
+    <t>명이김 선물세트 3호,1개 x1</t>
+  </si>
+  <si>
+    <t>명이김 3호,[1*{구매수량}]개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@코다리 새로 등록,1개 속초 절단코다리 1kg내외</t>
+  </si>
+  <si>
+    <t>코다리 새로 등록,1개 속초 절단코다리 1kg내외 x2</t>
+  </si>
+  <si>
+    <t>속초 절단코다리 1kg내외 {구매수량}개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@코다리 새로 등록,1개 속초 프리미엄 코다리 8마리 (49cm내외)</t>
+  </si>
+  <si>
+    <t>코다리 새로 등록,1개 속초 프리미엄 코다리 8마리 (49cm내외) x2</t>
+  </si>
+  <si>
+    <t>속초 프리미엄 코다리 (49cm내외) [8*{구매수량}]마리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@반건조오징어만 새로,1개 원양산 반건조오징어 대 10마리 (1.3kg내외)</t>
+  </si>
+  <si>
+    <t>반건조오징어만 새로,1개 원양산 반건조오징어 대 10마리 (1.3kg내외) x1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">반건조오징어 대 (1.3kg내외) [10*{구매수량}]마리 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@오징어순대 아바이순대,2kg 1개 전통 아바이순대</t>
+  </si>
+  <si>
+    <t>오징어순대 아바이순대,2kg 1개 전통 아바이순대 x1</t>
+  </si>
+  <si>
+    <t>2kg 전통 아바이순대 [1*{구매수량}]개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@명이김 선물세트 4호,1개</t>
+  </si>
+  <si>
+    <t>명이김 선물세트 4호,1개 x1</t>
+  </si>
+  <si>
+    <t>명이김 4호,[1*{구매수량}]개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@ 문어다리 새로등록,1개 소 600g내외</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 문어다리 새로등록,1개 소 600g내외 x1</t>
+  </si>
+  <si>
+    <t>문어다리 소 600g내외 [1*{구매수량}]개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@참가자미 다시,6개 특대 (250~350g)</t>
+  </si>
+  <si>
+    <t>참가자미 다시,6개 특대 (250~350g) x1</t>
+  </si>
+  <si>
+    <t>참가자미 특대 (250~350g) [6개 *{구매수량}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@무라벨 일반식혜 1.5L,3개 1.5L</t>
+  </si>
+  <si>
+    <t>무라벨 일반식혜 1.5L,3개 1.5L x1</t>
+  </si>
+  <si>
+    <t>쭈구리 일반식혜 1.5L [3 *{구매수량}]개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@ NEW 메로,1개 1kg 최고다농수산 메로 목살</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NEW 메로,1개 1kg 최고다농수산 메로 목살 x2</t>
+  </si>
+  <si>
+    <t>메로 목살 {구매수량}개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@오징어순대 아바이순대,600g 1개 고기 오징어순대 2미</t>
+  </si>
+  <si>
+    <t>오징어순대 아바이순대,600g 1개 고기 오징어순대 2미 x1</t>
+  </si>
+  <si>
+    <t>고기 오징어순대 [2*{구매수량}]미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@ NEW 문어,소문어 (600g~5kg) *특가* A급 동해 피문어 1kg내외 (자숙)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NEW 문어,소문어 (600g~5kg) *특가* A급 동해 피문어 1kg내외 (자숙) x1</t>
+  </si>
+  <si>
+    <t>피문어 1kg내외 (자숙) {구매수량}개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@장어,손질장어 500g</t>
+  </si>
+  <si>
+    <t>장어,손질장어 500g x1</t>
+  </si>
+  <si>
+    <t>손질장어 [0.5kg *{구매수량}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@반건조오징어만 새로,1개 원양산 반건조오징어 특대 10마리 (1.5kg내외)</t>
+  </si>
+  <si>
+    <t>반건조오징어만 새로,1개 원양산 반건조오징어 특대 10마리 (1.5kg내외) x1</t>
+  </si>
+  <si>
+    <t>반건조오징어 특대 (1.5kg내외) [10마리 *{x구매수량}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@장어,장어 머리+뼈 1kg (장어탕/튀김용)</t>
+  </si>
+  <si>
+    <t>장어,장어 머리+뼈 1kg (장어탕/튀김용) x3</t>
+  </si>
+  <si>
+    <t>장어 머리+뼈(장어탕/튀김용) [1*{구매수량}]kg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@초코오징어,1개 1.5kg내외 원양산 반건조오징어 특대 10마리</t>
+  </si>
+  <si>
+    <t>초코오징어,1개 1.5kg내외 원양산 반건조오징어 특대 10마리 x1</t>
+  </si>
+  <si>
+    <t>1.5kg내외 반건조오징어 특대 [10*{구매수량}]마리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@호박식혜 용량으로새로,9개 500ml</t>
+  </si>
+  <si>
+    <t>호박식혜 용량으로새로,9개 500ml x1</t>
+  </si>
+  <si>
+    <t>호박식혜 [9 *{구매수량}]개 500ml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@양미리 도루묵 기름가자미,1개 햇 반건조 기름가자미(물가자미) 중 5미 5미</t>
+  </si>
+  <si>
+    <t>양미리 도루묵 기름가자미,1개 햇 반건조 기름가자미(물가자미) 중 5미 5미 x1</t>
+  </si>
+  <si>
+    <t>햇 반건조 기름가자미(물가자미) 중 [5 *{구매수량}]미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@장어,초벌구이 장어 1kg</t>
+  </si>
+  <si>
+    <t>장어,초벌구이 장어 1kg x2</t>
+  </si>
+  <si>
+    <t>초벌구이 장어 [1 * {구매수량}]kg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@초코오징어,1개 특가 통찜/물회용 선동한치 500g (5~7미내외)</t>
+  </si>
+  <si>
+    <t>초코오징어,1개 특가 통찜/물회용 선동한치 500g (5~7미내외) x1</t>
+  </si>
+  <si>
+    <t>선동한치 500g (5~7미내외) {x구매수량}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;&gt; 이건 수량 표현을 어떻게 하지?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@코다리,1개 속초 깔끔코다리 특대 10마리 (48cm내외)</t>
+  </si>
+  <si>
+    <t>코다리,1개 속초 깔끔코다리 특대 10마리 (48cm내외) x1</t>
+  </si>
+  <si>
+    <t>속초 깔끔코다리 특대 [10 * {구매수량}]마리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80648858000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@오징어순대 아바이순대,1개 야채 오징어순대 2미 (600g)</t>
+  </si>
+  <si>
+    <t>오징어순대 아바이순대,1개 야채 오징어순대 2미 (600g) x1</t>
+  </si>
+  <si>
+    <t>야채 오징어순대 [2*{구매수량}]미 (600g)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@호박식혜,500ml 9개</t>
+  </si>
+  <si>
+    <t>호박식혜,500ml 9개 x1</t>
+  </si>
+  <si>
+    <t>호박식혜,500ml [9 * {구매수량}]개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@ NEW 문어,소문어 (600g~5kg) A급 동해 피문어 2kg내외 (자숙)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NEW 문어,소문어 (600g~5kg) A급 동해 피문어 2kg내외 (자숙) x1</t>
+  </si>
+  <si>
+    <t>동해 피문어 2kg내외 (자숙) {x구매수량}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수취인이름</t>
+  </si>
+  <si>
+    <t>수취인전화번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수취인 주소</t>
+  </si>
+  <si>
+    <t>수정된 주문</t>
   </si>
   <si>
     <r>
@@ -1698,7 +2072,27 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">냉동오징어 / ,젓갈 선택: ,당일퀵, A급, 골뱅이 선택: , set, 가리비 선택: </t>
+      <t xml:space="preserve">냉동오징어 / ,젓갈 선택: ,당일퀵, A급, 골뱅이 선택: , set, 가리비 선택: , 반건조우럭 한정, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="3"/>
+      </rPr>
+      <t>❄️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">아이스팩 추가: , (기본 2개 제공), 꿀조합! 오로바일렌 올리브오일&amp;초장: </t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1710,7 +2104,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1921,8 +2315,29 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1961,6 +2376,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2037,10 +2464,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2209,11 +2639,147 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="28" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2" xfId="1" xr:uid="{43FE286E-9DC8-4DAC-B7DA-9700614DD751}"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="36">
+    <dxf>
+      <font>
+        <color indexed="20"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="45"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="20"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="45"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="20"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="45"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color indexed="20"/>
@@ -3045,7 +3611,7 @@
         <v>169</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>398</v>
+        <v>509</v>
       </c>
       <c r="F8" s="42" t="s">
         <v>170</v>
@@ -5639,6 +6205,3028 @@
       </c>
       <c r="E100" s="36" t="s">
         <v>201</v>
+      </c>
+      <c r="F100" s="49"/>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="B101" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C101" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D101" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="E101" s="32"/>
+      <c r="F101" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="B102" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C102" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="D102" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="E102" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F102" s="49"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="B103" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C103" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="D103" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E103" s="32"/>
+      <c r="F103" s="32" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="B104" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C104" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D104" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E104" s="32"/>
+      <c r="F104" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="B105" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C105" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D105" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="E105" s="32"/>
+      <c r="F105" s="32" t="s">
+        <v>139</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="D27">
+    <cfRule type="duplicateValues" dxfId="35" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D34">
+    <cfRule type="duplicateValues" dxfId="34" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D58:D59">
+    <cfRule type="duplicateValues" dxfId="33" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D59">
+    <cfRule type="duplicateValues" dxfId="32" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D79">
+    <cfRule type="duplicateValues" dxfId="31" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D83">
+    <cfRule type="expression" dxfId="27" priority="1" stopIfTrue="1">
+      <formula>AND(COUNTIF($A$1:$A$65514, D83)+COUNTIF(#REF!, D83)&gt;1,NOT(ISBLANK(D83)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D87">
+    <cfRule type="expression" dxfId="26" priority="2" stopIfTrue="1">
+      <formula>AND(COUNTIF($J$1:$J$65514, D87)+COUNTIF(#REF!, D87)&gt;1,NOT(ISBLANK(D87)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D89">
+    <cfRule type="duplicateValues" dxfId="25" priority="3" stopIfTrue="1"/>
+    <cfRule type="expression" dxfId="24" priority="4" stopIfTrue="1">
+      <formula>AND(COUNTIF($N$1:$N$65514, D89)+COUNTIF(#REF!, D89)&gt;1,NOT(ISBLANK(D89)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52549504-4590-40BA-B8EA-337736F4028C}">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="6.92578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.35546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.35546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="29.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>252</v>
+      </c>
+      <c r="E2" s="45" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="60" t="s">
+        <v>254</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>169</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" s="60" t="s">
+        <v>256</v>
+      </c>
+      <c r="E3" s="60" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="60" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="60" t="s">
+        <v>272</v>
+      </c>
+      <c r="D4" s="60" t="s">
+        <v>257</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="60" t="s">
+        <v>258</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>238</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>259</v>
+      </c>
+      <c r="D5" s="60" t="s">
+        <v>260</v>
+      </c>
+      <c r="E5" s="60" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="60" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" s="60" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>262</v>
+      </c>
+      <c r="D6" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="60" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="60" t="s">
+        <v>261</v>
+      </c>
+      <c r="B7" s="60" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" s="60" t="s">
+        <v>263</v>
+      </c>
+      <c r="D7" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="E7" s="61" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="60" t="s">
+        <v>261</v>
+      </c>
+      <c r="B8" s="60" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="60" t="s">
+        <v>277</v>
+      </c>
+      <c r="D8" s="60" t="s">
+        <v>223</v>
+      </c>
+      <c r="E8" s="60" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="60" t="s">
+        <v>279</v>
+      </c>
+      <c r="D9" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="E9" s="60" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="B10" s="60" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="60" t="s">
+        <v>265</v>
+      </c>
+      <c r="D10" s="60" t="s">
+        <v>266</v>
+      </c>
+      <c r="E10" s="60" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" s="60" t="s">
+        <v>267</v>
+      </c>
+      <c r="D11" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="E11" s="60" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="60" t="s">
+        <v>268</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>397</v>
+      </c>
+      <c r="C12" s="60" t="s">
+        <v>269</v>
+      </c>
+      <c r="D12" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="E12" s="60" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="45" t="s">
+        <v>283</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>284</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="60" t="s">
+        <v>286</v>
+      </c>
+      <c r="B16" s="60" t="s">
+        <v>299</v>
+      </c>
+      <c r="C16" s="60" t="s">
+        <v>287</v>
+      </c>
+      <c r="D16" s="60" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="60" t="s">
+        <v>288</v>
+      </c>
+      <c r="B17" s="60" t="s">
+        <v>301</v>
+      </c>
+      <c r="C17" s="60" t="s">
+        <v>289</v>
+      </c>
+      <c r="D17" s="60" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="60" t="s">
+        <v>352</v>
+      </c>
+      <c r="B18" s="60" t="s">
+        <v>301</v>
+      </c>
+      <c r="C18" s="60" t="s">
+        <v>289</v>
+      </c>
+      <c r="D18" s="60" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="60" t="s">
+        <v>290</v>
+      </c>
+      <c r="B19" s="60" t="s">
+        <v>291</v>
+      </c>
+      <c r="C19" s="60" t="s">
+        <v>292</v>
+      </c>
+      <c r="D19" s="60" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="60" t="s">
+        <v>293</v>
+      </c>
+      <c r="B20" s="60" t="s">
+        <v>294</v>
+      </c>
+      <c r="C20" s="60" t="s">
+        <v>295</v>
+      </c>
+      <c r="D20" s="60"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="60" t="s">
+        <v>296</v>
+      </c>
+      <c r="B21" s="60" t="s">
+        <v>297</v>
+      </c>
+      <c r="C21" s="60" t="s">
+        <v>298</v>
+      </c>
+      <c r="D21" s="60"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="60" t="s">
+        <v>304</v>
+      </c>
+      <c r="B22" s="60" t="s">
+        <v>305</v>
+      </c>
+      <c r="C22" s="60" t="s">
+        <v>306</v>
+      </c>
+      <c r="D22" s="60" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="60" t="s">
+        <v>307</v>
+      </c>
+      <c r="B23" s="60" t="s">
+        <v>308</v>
+      </c>
+      <c r="C23" s="60" t="s">
+        <v>309</v>
+      </c>
+      <c r="D23" s="60" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="60" t="s">
+        <v>310</v>
+      </c>
+      <c r="B24" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="C24" s="60" t="s">
+        <v>312</v>
+      </c>
+      <c r="D24" s="60" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="60" t="s">
+        <v>320</v>
+      </c>
+      <c r="B25" s="60" t="s">
+        <v>321</v>
+      </c>
+      <c r="C25" s="60" t="s">
+        <v>322</v>
+      </c>
+      <c r="D25" s="60" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="60" t="s">
+        <v>334</v>
+      </c>
+      <c r="B26" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="C26" s="60" t="s">
+        <v>336</v>
+      </c>
+      <c r="D26" s="60" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="60" t="s">
+        <v>290</v>
+      </c>
+      <c r="B27" s="60" t="s">
+        <v>338</v>
+      </c>
+      <c r="C27" s="60" t="s">
+        <v>339</v>
+      </c>
+      <c r="D27" s="60" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="60" t="s">
+        <v>307</v>
+      </c>
+      <c r="B28" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="C28" s="60" t="s">
+        <v>342</v>
+      </c>
+      <c r="D28" s="60" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="60" t="s">
+        <v>344</v>
+      </c>
+      <c r="B29" s="60" t="s">
+        <v>345</v>
+      </c>
+      <c r="C29" s="60" t="s">
+        <v>346</v>
+      </c>
+      <c r="D29" s="60" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D32A38B-82FC-45BC-A8B8-FA7B747A95DC}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001"/>
+  <cols>
+    <col min="1" max="1" width="13.2109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.78515625" style="63" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="63" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.78515625" style="63" customWidth="1"/>
+    <col min="6" max="6" width="78.2109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="63"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="62" t="s">
+        <v>398</v>
+      </c>
+      <c r="B1" s="62" t="s">
+        <v>399</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>400</v>
+      </c>
+      <c r="D1" s="62" t="s">
+        <v>401</v>
+      </c>
+      <c r="E1" s="62" t="s">
+        <v>402</v>
+      </c>
+      <c r="F1" s="62" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="64">
+        <v>90726181415</v>
+      </c>
+      <c r="B2" s="63" t="s">
+        <v>404</v>
+      </c>
+      <c r="C2" s="65">
+        <v>1</v>
+      </c>
+      <c r="D2" s="63" t="s">
+        <v>405</v>
+      </c>
+      <c r="E2" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" s="66" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="64">
+        <v>90463359240</v>
+      </c>
+      <c r="B3" s="63" t="s">
+        <v>407</v>
+      </c>
+      <c r="C3" s="65">
+        <v>1</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>408</v>
+      </c>
+      <c r="E3" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F3" s="66" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="64">
+        <v>86263737582</v>
+      </c>
+      <c r="B4" s="63" t="s">
+        <v>410</v>
+      </c>
+      <c r="C4" s="65">
+        <v>1</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>411</v>
+      </c>
+      <c r="E4" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F4" s="66" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="64">
+        <v>90318747741</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>413</v>
+      </c>
+      <c r="C5" s="65">
+        <v>1</v>
+      </c>
+      <c r="D5" s="63" t="s">
+        <v>414</v>
+      </c>
+      <c r="E5" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F5" s="66" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="64">
+        <v>80648858007</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>416</v>
+      </c>
+      <c r="C6" s="65">
+        <v>2</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>417</v>
+      </c>
+      <c r="E6" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" s="66" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="64">
+        <v>93220547947</v>
+      </c>
+      <c r="B7" s="63" t="s">
+        <v>419</v>
+      </c>
+      <c r="C7" s="65">
+        <v>1</v>
+      </c>
+      <c r="D7" s="63" t="s">
+        <v>420</v>
+      </c>
+      <c r="E7" s="66" t="s">
+        <v>199</v>
+      </c>
+      <c r="F7" s="66" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="64">
+        <v>80648858026</v>
+      </c>
+      <c r="B8" s="63" t="s">
+        <v>422</v>
+      </c>
+      <c r="C8" s="65">
+        <v>1</v>
+      </c>
+      <c r="D8" s="63" t="s">
+        <v>423</v>
+      </c>
+      <c r="E8" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F8" s="66" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="64">
+        <v>91021780775</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>425</v>
+      </c>
+      <c r="C9" s="65">
+        <v>1</v>
+      </c>
+      <c r="D9" s="63" t="s">
+        <v>426</v>
+      </c>
+      <c r="E9" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F9" s="66" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="64">
+        <v>84634968862</v>
+      </c>
+      <c r="B10" s="63" t="s">
+        <v>428</v>
+      </c>
+      <c r="C10" s="65">
+        <v>1</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>429</v>
+      </c>
+      <c r="E10" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F10" s="66" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="64">
+        <v>93672537464</v>
+      </c>
+      <c r="B11" s="63" t="s">
+        <v>431</v>
+      </c>
+      <c r="C11" s="65">
+        <v>1</v>
+      </c>
+      <c r="D11" s="63" t="s">
+        <v>432</v>
+      </c>
+      <c r="E11" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F11" s="66" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="64">
+        <v>93179170670</v>
+      </c>
+      <c r="B12" s="63" t="s">
+        <v>434</v>
+      </c>
+      <c r="C12" s="65">
+        <v>2</v>
+      </c>
+      <c r="D12" s="63" t="s">
+        <v>435</v>
+      </c>
+      <c r="E12" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F12" s="66" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="64">
+        <v>93179170628</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>437</v>
+      </c>
+      <c r="C13" s="65">
+        <v>2</v>
+      </c>
+      <c r="D13" s="63" t="s">
+        <v>438</v>
+      </c>
+      <c r="E13" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F13" s="66" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="64">
+        <v>88176237136</v>
+      </c>
+      <c r="B14" s="63" t="s">
+        <v>440</v>
+      </c>
+      <c r="C14" s="65">
+        <v>1</v>
+      </c>
+      <c r="D14" s="63" t="s">
+        <v>441</v>
+      </c>
+      <c r="E14" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F14" s="66" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="64">
+        <v>90318747755</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>443</v>
+      </c>
+      <c r="C15" s="65">
+        <v>1</v>
+      </c>
+      <c r="D15" s="63" t="s">
+        <v>444</v>
+      </c>
+      <c r="E15" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F15" s="66" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="64">
+        <v>93672571449</v>
+      </c>
+      <c r="B16" s="63" t="s">
+        <v>446</v>
+      </c>
+      <c r="C16" s="65">
+        <v>1</v>
+      </c>
+      <c r="D16" s="63" t="s">
+        <v>447</v>
+      </c>
+      <c r="E16" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F16" s="66" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="64">
+        <v>93220547933</v>
+      </c>
+      <c r="B17" s="63" t="s">
+        <v>449</v>
+      </c>
+      <c r="C17" s="65">
+        <v>1</v>
+      </c>
+      <c r="D17" s="63" t="s">
+        <v>450</v>
+      </c>
+      <c r="E17" s="66" t="s">
+        <v>199</v>
+      </c>
+      <c r="F17" s="66" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="64">
+        <v>90726181419</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>452</v>
+      </c>
+      <c r="C18" s="65">
+        <v>1</v>
+      </c>
+      <c r="D18" s="63" t="s">
+        <v>453</v>
+      </c>
+      <c r="E18" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F18" s="66" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="64">
+        <v>87880167762</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>455</v>
+      </c>
+      <c r="C19" s="65">
+        <v>1</v>
+      </c>
+      <c r="D19" s="63" t="s">
+        <v>456</v>
+      </c>
+      <c r="E19" s="66" t="s">
+        <v>198</v>
+      </c>
+      <c r="F19" s="66" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="64">
+        <v>88186960178</v>
+      </c>
+      <c r="B20" s="63" t="s">
+        <v>458</v>
+      </c>
+      <c r="C20" s="65">
+        <v>2</v>
+      </c>
+      <c r="D20" s="63" t="s">
+        <v>459</v>
+      </c>
+      <c r="E20" s="66" t="s">
+        <v>197</v>
+      </c>
+      <c r="F20" s="66" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="64">
+        <v>88128325479</v>
+      </c>
+      <c r="B21" s="63" t="s">
+        <v>461</v>
+      </c>
+      <c r="C21" s="65">
+        <v>1</v>
+      </c>
+      <c r="D21" s="63" t="s">
+        <v>462</v>
+      </c>
+      <c r="E21" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F21" s="66" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="64">
+        <v>82314858827</v>
+      </c>
+      <c r="B22" s="63" t="s">
+        <v>464</v>
+      </c>
+      <c r="C22" s="65">
+        <v>1</v>
+      </c>
+      <c r="D22" s="63" t="s">
+        <v>465</v>
+      </c>
+      <c r="E22" s="66" t="s">
+        <v>199</v>
+      </c>
+      <c r="F22" s="66" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="64">
+        <v>75338048760</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>467</v>
+      </c>
+      <c r="C23" s="65">
+        <v>1</v>
+      </c>
+      <c r="D23" s="63" t="s">
+        <v>468</v>
+      </c>
+      <c r="E23" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F23" s="66" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="64">
+        <v>88176237168</v>
+      </c>
+      <c r="B24" s="63" t="s">
+        <v>470</v>
+      </c>
+      <c r="C24" s="65">
+        <v>1</v>
+      </c>
+      <c r="D24" s="63" t="s">
+        <v>471</v>
+      </c>
+      <c r="E24" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F24" s="66" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="64">
+        <v>77218920858</v>
+      </c>
+      <c r="B25" s="63" t="s">
+        <v>473</v>
+      </c>
+      <c r="C25" s="65">
+        <v>3</v>
+      </c>
+      <c r="D25" s="63" t="s">
+        <v>474</v>
+      </c>
+      <c r="E25" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F25" s="66" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="64">
+        <v>86263737587</v>
+      </c>
+      <c r="B26" s="63" t="s">
+        <v>476</v>
+      </c>
+      <c r="C26" s="65">
+        <v>1</v>
+      </c>
+      <c r="D26" s="63" t="s">
+        <v>477</v>
+      </c>
+      <c r="E26" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F26" s="66" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="64">
+        <v>87992013846</v>
+      </c>
+      <c r="B27" s="63" t="s">
+        <v>479</v>
+      </c>
+      <c r="C27" s="65">
+        <v>1</v>
+      </c>
+      <c r="D27" s="63" t="s">
+        <v>480</v>
+      </c>
+      <c r="E27" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F27" s="66" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="64">
+        <v>83700756628</v>
+      </c>
+      <c r="B28" s="63" t="s">
+        <v>482</v>
+      </c>
+      <c r="C28" s="65">
+        <v>1</v>
+      </c>
+      <c r="D28" s="63" t="s">
+        <v>483</v>
+      </c>
+      <c r="E28" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F28" s="66" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="64">
+        <v>73671510910</v>
+      </c>
+      <c r="B29" s="63" t="s">
+        <v>485</v>
+      </c>
+      <c r="C29" s="65">
+        <v>2</v>
+      </c>
+      <c r="D29" s="63" t="s">
+        <v>486</v>
+      </c>
+      <c r="E29" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F29" s="66" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="64">
+        <v>87418768783</v>
+      </c>
+      <c r="B30" s="63" t="s">
+        <v>488</v>
+      </c>
+      <c r="C30" s="65">
+        <v>1</v>
+      </c>
+      <c r="D30" s="63" t="s">
+        <v>489</v>
+      </c>
+      <c r="E30" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F30" s="66" t="s">
+        <v>490</v>
+      </c>
+      <c r="G30" s="63" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="64">
+        <v>74117666924</v>
+      </c>
+      <c r="B31" s="63" t="s">
+        <v>492</v>
+      </c>
+      <c r="C31" s="65">
+        <v>1</v>
+      </c>
+      <c r="D31" s="63" t="s">
+        <v>493</v>
+      </c>
+      <c r="E31" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F31" s="66" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="64" t="s">
+        <v>495</v>
+      </c>
+      <c r="B32" s="63" t="s">
+        <v>496</v>
+      </c>
+      <c r="C32" s="65">
+        <v>1</v>
+      </c>
+      <c r="D32" s="63" t="s">
+        <v>497</v>
+      </c>
+      <c r="E32" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F32" s="66" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="64">
+        <v>73672215064</v>
+      </c>
+      <c r="B33" s="63" t="s">
+        <v>499</v>
+      </c>
+      <c r="C33" s="65">
+        <v>1</v>
+      </c>
+      <c r="D33" s="63" t="s">
+        <v>500</v>
+      </c>
+      <c r="E33" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F33" s="66" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="64">
+        <v>88449262751</v>
+      </c>
+      <c r="B34" s="63" t="s">
+        <v>502</v>
+      </c>
+      <c r="C34" s="65">
+        <v>1</v>
+      </c>
+      <c r="D34" s="63" t="s">
+        <v>503</v>
+      </c>
+      <c r="E34" s="66" t="s">
+        <v>199</v>
+      </c>
+      <c r="F34" s="66" t="s">
+        <v>504</v>
+      </c>
+      <c r="G34" s="63" t="s">
+        <v>491</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF47BDA5-BDD2-472E-B146-E1B4432935BA}">
+  <dimension ref="A1:F105"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40.85546875" style="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.85546875" style="30" customWidth="1"/>
+    <col min="3" max="3" width="2.78515625" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" style="30" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="30" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.78515625" style="30" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="F1" s="41" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="34"/>
+      <c r="F2" s="47"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="34"/>
+      <c r="F3" s="47"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="35"/>
+      <c r="F4" s="48" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="35"/>
+      <c r="F5" s="48" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="34"/>
+      <c r="F6" s="47"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="34"/>
+      <c r="F7" s="47"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="35"/>
+      <c r="F8" s="48" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>505</v>
+      </c>
+      <c r="F9" s="49"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>506</v>
+      </c>
+      <c r="F10" s="49"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="34"/>
+      <c r="F11" s="47"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="34"/>
+      <c r="F12" s="47"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>507</v>
+      </c>
+      <c r="F13" s="49"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="34"/>
+      <c r="F14" s="47"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="34"/>
+      <c r="F15" s="47"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>508</v>
+      </c>
+      <c r="F16" s="49"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="35"/>
+      <c r="F17" s="55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="34"/>
+      <c r="F18" s="47"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="34"/>
+      <c r="F19" s="47"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="D20" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="49"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="34"/>
+      <c r="F21" s="47"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="34"/>
+      <c r="F22" s="47"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="37"/>
+      <c r="F23" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="37"/>
+      <c r="F24" s="50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="37"/>
+      <c r="F25" s="50" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>508</v>
+      </c>
+      <c r="F26" s="49"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>505</v>
+      </c>
+      <c r="F27" s="49"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>507</v>
+      </c>
+      <c r="F28" s="49"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="D29" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>506</v>
+      </c>
+      <c r="F29" s="49"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="37"/>
+      <c r="F30" s="50"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="49"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="D32" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>505</v>
+      </c>
+      <c r="F32" s="49"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="D33" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" s="49"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D34" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>507</v>
+      </c>
+      <c r="F34" s="49"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>383</v>
+      </c>
+      <c r="E35" s="26"/>
+      <c r="F35" s="40"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D36" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="E36" s="36" t="s">
+        <v>506</v>
+      </c>
+      <c r="F36" s="49"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C37" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>384</v>
+      </c>
+      <c r="E37" s="26"/>
+      <c r="F37" s="40"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>385</v>
+      </c>
+      <c r="E38" s="26"/>
+      <c r="F38" s="40"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>386</v>
+      </c>
+      <c r="E39" s="26"/>
+      <c r="F39" s="40"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C40" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D40" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="E40" s="36" t="s">
+        <v>508</v>
+      </c>
+      <c r="F40" s="49"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C41" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>387</v>
+      </c>
+      <c r="E41" s="26"/>
+      <c r="F41" s="40"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C42" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="D42" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="E42" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="49"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D43" s="26" t="s">
+        <v>388</v>
+      </c>
+      <c r="E43" s="26"/>
+      <c r="F43" s="40"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>389</v>
+      </c>
+      <c r="E44" s="26"/>
+      <c r="F44" s="40"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C45" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>390</v>
+      </c>
+      <c r="E45" s="26"/>
+      <c r="F45" s="40"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B46" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C46" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="E46" s="26"/>
+      <c r="F46" s="40"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C47" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="E47" s="26"/>
+      <c r="F47" s="40"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C48" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>393</v>
+      </c>
+      <c r="E48" s="26"/>
+      <c r="F48" s="40"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B49" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C49" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>394</v>
+      </c>
+      <c r="E49" s="26"/>
+      <c r="F49" s="40"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C50" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="D50" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="E50" s="31"/>
+      <c r="F50" s="51" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C51" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="D51" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="E51" s="31"/>
+      <c r="F51" s="51" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C52" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="D52" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="E52" s="31"/>
+      <c r="F52" s="51" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B53" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C53" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="D53" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="E53" s="38"/>
+      <c r="F53" s="52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C54" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="D54" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="E54" s="38"/>
+      <c r="F54" s="52" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B55" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C55" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D55" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="E55" s="38"/>
+      <c r="F55" s="52" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B56" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C56" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="D56" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="E56" s="38"/>
+      <c r="F56" s="52"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C57" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D57" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="E57" s="36" t="s">
+        <v>508</v>
+      </c>
+      <c r="F57" s="49"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C58" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="D58" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E58" s="36" t="s">
+        <v>505</v>
+      </c>
+      <c r="F58" s="49"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B59" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C59" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="D59" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="E59" s="36" t="s">
+        <v>507</v>
+      </c>
+      <c r="F59" s="49"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B60" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C60" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D60" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="E60" s="36" t="s">
+        <v>506</v>
+      </c>
+      <c r="F60" s="49"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B61" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C61" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D61" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="E61" s="38"/>
+      <c r="F61" s="52"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B62" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C62" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D62" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="49"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B63" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C63" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="D63" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="E63" s="36" t="s">
+        <v>505</v>
+      </c>
+      <c r="F63" s="49"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B64" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C64" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="D64" s="26" t="s">
+        <v>383</v>
+      </c>
+      <c r="E64" s="40"/>
+      <c r="F64" s="40"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B65" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C65" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D65" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E65" s="36" t="s">
+        <v>507</v>
+      </c>
+      <c r="F65" s="49"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B66" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C66" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="D66" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="E66" s="36" t="s">
+        <v>506</v>
+      </c>
+      <c r="F66" s="49"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B67" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C67" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D67" s="26" t="s">
+        <v>384</v>
+      </c>
+      <c r="E67" s="40"/>
+      <c r="F67" s="40"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B68" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C68" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="D68" s="26" t="s">
+        <v>385</v>
+      </c>
+      <c r="E68" s="26"/>
+      <c r="F68" s="40"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B69" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C69" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="D69" s="26" t="s">
+        <v>386</v>
+      </c>
+      <c r="E69" s="40"/>
+      <c r="F69" s="40"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B70" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C70" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D70" s="26" t="s">
+        <v>387</v>
+      </c>
+      <c r="E70" s="26"/>
+      <c r="F70" s="40"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B71" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C71" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D71" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="E71" s="36" t="s">
+        <v>508</v>
+      </c>
+      <c r="F71" s="49"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B72" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C72" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D72" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="E72" s="26"/>
+      <c r="F72" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B73" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C73" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="D73" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="E73" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" s="49"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B74" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C74" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="D74" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="E74" s="34"/>
+      <c r="F74" s="47" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B75" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C75" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="D75" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="34"/>
+      <c r="F75" s="47" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B76" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C76" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D76" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="E76" s="36" t="s">
+        <v>505</v>
+      </c>
+      <c r="F76" s="49"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B77" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C77" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="D77" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="E77" s="36" t="s">
+        <v>506</v>
+      </c>
+      <c r="F77" s="49"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B78" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C78" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D78" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E78" s="34"/>
+      <c r="F78" s="47"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B79" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C79" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="D79" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="E79" s="36" t="s">
+        <v>507</v>
+      </c>
+      <c r="F79" s="49"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B80" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C80" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="D80" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="E80" s="34"/>
+      <c r="F80" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B81" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C81" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D81" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="E81" s="36" t="s">
+        <v>508</v>
+      </c>
+      <c r="F81" s="49"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B82" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C82" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D82" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="E82" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F82" s="49"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B83" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C83" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="D83" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="E83" s="36" t="s">
+        <v>505</v>
+      </c>
+      <c r="F83" s="49"/>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B84" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C84" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="D84" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="E84" s="36" t="s">
+        <v>508</v>
+      </c>
+      <c r="F84" s="49"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B85" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C85" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D85" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="E85" s="28"/>
+      <c r="F85" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B86" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C86" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="D86" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="E86" s="28"/>
+      <c r="F86" s="53"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B87" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C87" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D87" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E87" s="36" t="s">
+        <v>506</v>
+      </c>
+      <c r="F87" s="49"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B88" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C88" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="D88" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="E88" s="27"/>
+      <c r="F88" s="54"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B89" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C89" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="D89" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="36" t="s">
+        <v>507</v>
+      </c>
+      <c r="F89" s="49"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B90" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C90" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D90" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="E90" s="28"/>
+      <c r="F90" s="53"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B91" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C91" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D91" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E91" s="28"/>
+      <c r="F91" s="53"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B92" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C92" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D92" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E92" s="27"/>
+      <c r="F92" s="54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B93" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C93" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="D93" s="27" t="s">
+        <v>348</v>
+      </c>
+      <c r="E93" s="27"/>
+      <c r="F93" s="54" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B94" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C94" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D94" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="E94" s="27"/>
+      <c r="F94" s="54" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B95" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C95" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="D95" s="28" t="s">
+        <v>367</v>
+      </c>
+      <c r="E95" s="28"/>
+      <c r="F95" s="53"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B96" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C96" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="D96" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="E96" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F96" s="49"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="B97" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C97" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="D97" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E97" s="36" t="s">
+        <v>505</v>
+      </c>
+      <c r="F97" s="49"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="B98" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C98" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="D98" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E98" s="36" t="s">
+        <v>506</v>
+      </c>
+      <c r="F98" s="49"/>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="B99" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C99" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D99" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="E99" s="36" t="s">
+        <v>507</v>
+      </c>
+      <c r="F99" s="49"/>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="B100" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C100" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="D100" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="E100" s="36" t="s">
+        <v>508</v>
       </c>
       <c r="F100" s="49"/>
     </row>
@@ -5772,450 +9360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52549504-4590-40BA-B8EA-337736F4028C}">
-  <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="6.92578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.35546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.35546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="29.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="45" t="s">
-        <v>250</v>
-      </c>
-      <c r="C2" s="45" t="s">
-        <v>251</v>
-      </c>
-      <c r="D2" s="45" t="s">
-        <v>252</v>
-      </c>
-      <c r="E2" s="45" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="60" t="s">
-        <v>254</v>
-      </c>
-      <c r="B3" s="60" t="s">
-        <v>169</v>
-      </c>
-      <c r="C3" s="60" t="s">
-        <v>255</v>
-      </c>
-      <c r="D3" s="60" t="s">
-        <v>256</v>
-      </c>
-      <c r="E3" s="60" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="60" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="60" t="s">
-        <v>166</v>
-      </c>
-      <c r="C4" s="60" t="s">
-        <v>272</v>
-      </c>
-      <c r="D4" s="60" t="s">
-        <v>257</v>
-      </c>
-      <c r="E4" s="60" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="60" t="s">
-        <v>258</v>
-      </c>
-      <c r="B5" s="60" t="s">
-        <v>238</v>
-      </c>
-      <c r="C5" s="60" t="s">
-        <v>259</v>
-      </c>
-      <c r="D5" s="60" t="s">
-        <v>260</v>
-      </c>
-      <c r="E5" s="60" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="60" t="s">
-        <v>261</v>
-      </c>
-      <c r="B6" s="60" t="s">
-        <v>172</v>
-      </c>
-      <c r="C6" s="60" t="s">
-        <v>262</v>
-      </c>
-      <c r="D6" s="60" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="60" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="60" t="s">
-        <v>261</v>
-      </c>
-      <c r="B7" s="60" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="60" t="s">
-        <v>263</v>
-      </c>
-      <c r="D7" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="E7" s="61" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="60" t="s">
-        <v>261</v>
-      </c>
-      <c r="B8" s="60" t="s">
-        <v>246</v>
-      </c>
-      <c r="C8" s="60" t="s">
-        <v>277</v>
-      </c>
-      <c r="D8" s="60" t="s">
-        <v>223</v>
-      </c>
-      <c r="E8" s="60" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="60" t="s">
-        <v>175</v>
-      </c>
-      <c r="B9" s="60" t="s">
-        <v>173</v>
-      </c>
-      <c r="C9" s="60" t="s">
-        <v>279</v>
-      </c>
-      <c r="D9" s="60" t="s">
-        <v>218</v>
-      </c>
-      <c r="E9" s="60" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="60" t="s">
-        <v>175</v>
-      </c>
-      <c r="B10" s="60" t="s">
-        <v>174</v>
-      </c>
-      <c r="C10" s="60" t="s">
-        <v>265</v>
-      </c>
-      <c r="D10" s="60" t="s">
-        <v>266</v>
-      </c>
-      <c r="E10" s="60" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="60" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11" s="60" t="s">
-        <v>213</v>
-      </c>
-      <c r="C11" s="60" t="s">
-        <v>267</v>
-      </c>
-      <c r="D11" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="E11" s="60" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="60" t="s">
-        <v>268</v>
-      </c>
-      <c r="B12" s="60" t="s">
-        <v>397</v>
-      </c>
-      <c r="C12" s="60" t="s">
-        <v>269</v>
-      </c>
-      <c r="D12" s="60" t="s">
-        <v>270</v>
-      </c>
-      <c r="E12" s="60" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="45" t="s">
-        <v>283</v>
-      </c>
-      <c r="B15" s="45" t="s">
-        <v>284</v>
-      </c>
-      <c r="C15" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="45" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="60" t="s">
-        <v>286</v>
-      </c>
-      <c r="B16" s="60" t="s">
-        <v>299</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>287</v>
-      </c>
-      <c r="D16" s="60" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="60" t="s">
-        <v>288</v>
-      </c>
-      <c r="B17" s="60" t="s">
-        <v>301</v>
-      </c>
-      <c r="C17" s="60" t="s">
-        <v>289</v>
-      </c>
-      <c r="D17" s="60" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="60" t="s">
-        <v>352</v>
-      </c>
-      <c r="B18" s="60" t="s">
-        <v>301</v>
-      </c>
-      <c r="C18" s="60" t="s">
-        <v>289</v>
-      </c>
-      <c r="D18" s="60" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="60" t="s">
-        <v>290</v>
-      </c>
-      <c r="B19" s="60" t="s">
-        <v>291</v>
-      </c>
-      <c r="C19" s="60" t="s">
-        <v>292</v>
-      </c>
-      <c r="D19" s="60" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="60" t="s">
-        <v>293</v>
-      </c>
-      <c r="B20" s="60" t="s">
-        <v>294</v>
-      </c>
-      <c r="C20" s="60" t="s">
-        <v>295</v>
-      </c>
-      <c r="D20" s="60"/>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="60" t="s">
-        <v>296</v>
-      </c>
-      <c r="B21" s="60" t="s">
-        <v>297</v>
-      </c>
-      <c r="C21" s="60" t="s">
-        <v>298</v>
-      </c>
-      <c r="D21" s="60"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="60" t="s">
-        <v>304</v>
-      </c>
-      <c r="B22" s="60" t="s">
-        <v>305</v>
-      </c>
-      <c r="C22" s="60" t="s">
-        <v>306</v>
-      </c>
-      <c r="D22" s="60" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="B23" s="60" t="s">
-        <v>308</v>
-      </c>
-      <c r="C23" s="60" t="s">
-        <v>309</v>
-      </c>
-      <c r="D23" s="60" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="60" t="s">
-        <v>310</v>
-      </c>
-      <c r="B24" s="60" t="s">
-        <v>311</v>
-      </c>
-      <c r="C24" s="60" t="s">
-        <v>312</v>
-      </c>
-      <c r="D24" s="60" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="60" t="s">
-        <v>320</v>
-      </c>
-      <c r="B25" s="60" t="s">
-        <v>321</v>
-      </c>
-      <c r="C25" s="60" t="s">
-        <v>322</v>
-      </c>
-      <c r="D25" s="60" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="60" t="s">
-        <v>334</v>
-      </c>
-      <c r="B26" s="60" t="s">
-        <v>335</v>
-      </c>
-      <c r="C26" s="60" t="s">
-        <v>336</v>
-      </c>
-      <c r="D26" s="60" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="60" t="s">
-        <v>290</v>
-      </c>
-      <c r="B27" s="60" t="s">
-        <v>338</v>
-      </c>
-      <c r="C27" s="60" t="s">
-        <v>339</v>
-      </c>
-      <c r="D27" s="60" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="B28" s="60" t="s">
-        <v>341</v>
-      </c>
-      <c r="C28" s="60" t="s">
-        <v>342</v>
-      </c>
-      <c r="D28" s="60" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="60" t="s">
-        <v>344</v>
-      </c>
-      <c r="B29" s="60" t="s">
-        <v>345</v>
-      </c>
-      <c r="C29" s="60" t="s">
-        <v>346</v>
-      </c>
-      <c r="D29" s="60" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D10536A-E0E0-49D9-841E-65214E1C7FD4}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:R56"/>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulm\.cursor\projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D40138-E467-4488-9034-F0F8F3AEEE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7269454A-F176-4425-8BD9-2B73375D0EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2092,7 +2092,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">아이스팩 추가: , (기본 2개 제공), 꿀조합! 오로바일렌 올리브오일&amp;초장: </t>
+      <t>아이스팩 추가: , (기본 2개 제공), 꿀조합! 오로바일렌 올리브오일&amp;초장: , 활멍게 선택:</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>

--- a/config.xlsx
+++ b/config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulm\.cursor\projects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulmann\Downloads\PJ_NAVER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7269454A-F176-4425-8BD9-2B73375D0EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A8BE92-B038-403C-985B-FA07D676E8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductRoute" sheetId="3" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="513">
   <si>
     <t>보내는사람</t>
   </si>
@@ -2096,6 +2096,17 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>장어 발주양식</t>
+  </si>
+  <si>
+    <t>장어 발주양식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2104,7 +2115,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3297,16 +3308,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2DCD00-F549-4147-9EE9-0753C5772E23}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" style="46" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.5" style="46" customWidth="1"/>
-    <col min="3" max="3" width="40.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="46"/>
+    <col min="1" max="1" width="7.75" style="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.58203125" style="46" customWidth="1"/>
+    <col min="3" max="3" width="40.83203125" style="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.1640625" style="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="58" t="s">
         <v>177</v>
       </c>
@@ -3317,7 +3328,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="57">
         <v>0</v>
       </c>
@@ -3328,7 +3339,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="57">
         <v>1</v>
       </c>
@@ -3339,7 +3350,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="57">
         <v>1</v>
       </c>
@@ -3350,7 +3361,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="57">
         <v>2</v>
       </c>
@@ -3361,7 +3372,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="57">
         <v>2</v>
       </c>
@@ -3372,7 +3383,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="57">
         <v>2</v>
       </c>
@@ -3383,7 +3394,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="57">
         <v>2</v>
       </c>
@@ -3394,7 +3405,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="57">
         <v>2</v>
       </c>
@@ -3405,7 +3416,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="57">
         <v>2</v>
       </c>
@@ -3416,7 +3427,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="57">
         <v>2</v>
       </c>
@@ -3427,14 +3438,25 @@
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" s="57">
+        <v>3</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>512</v>
+      </c>
+      <c r="C12" s="57" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13" s="57">
         <v>999</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B13" s="57" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C13" s="57" t="s">
         <v>129</v>
       </c>
     </row>
@@ -3448,18 +3470,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE8C8B0-87AB-4B5A-85D1-21EF511A776A}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F52"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.4140625" defaultRowHeight="14.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="57.78515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="35.92578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.42578125" style="2"/>
+    <col min="3" max="3" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="57.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="35.9140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.4140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="44" t="s">
         <v>5</v>
       </c>
@@ -3479,7 +3501,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="42">
         <v>1</v>
       </c>
@@ -3499,7 +3521,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="42">
         <v>2</v>
       </c>
@@ -3519,7 +3541,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="42">
         <v>3</v>
       </c>
@@ -3539,7 +3561,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="42">
         <v>4</v>
       </c>
@@ -3559,7 +3581,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="42">
         <v>5</v>
       </c>
@@ -3577,7 +3599,7 @@
       </c>
       <c r="F6" s="42"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="42">
         <v>6</v>
       </c>
@@ -3597,7 +3619,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="42">
         <v>7</v>
       </c>
@@ -3617,7 +3639,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="42">
         <v>8</v>
       </c>
@@ -3637,7 +3659,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="42">
         <v>9</v>
       </c>
@@ -3655,7 +3677,7 @@
       </c>
       <c r="F10" s="42"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="42">
         <v>10</v>
       </c>
@@ -3675,7 +3697,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="42">
         <v>11</v>
       </c>
@@ -3695,7 +3717,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="42">
         <v>12</v>
       </c>
@@ -3713,7 +3735,7 @@
       </c>
       <c r="F13" s="42"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="42">
         <v>13</v>
       </c>
@@ -3731,7 +3753,7 @@
       </c>
       <c r="F14" s="42"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="42">
         <v>14</v>
       </c>
@@ -3749,7 +3771,7 @@
       </c>
       <c r="F15" s="42"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="42">
         <v>15</v>
       </c>
@@ -3769,7 +3791,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="42">
         <v>16</v>
       </c>
@@ -3787,7 +3809,7 @@
       </c>
       <c r="F17" s="42"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="42">
         <v>17</v>
       </c>
@@ -3805,7 +3827,7 @@
       </c>
       <c r="F18" s="42"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="42">
         <v>18</v>
       </c>
@@ -3823,12 +3845,12 @@
       </c>
       <c r="F19" s="42"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="42">
         <v>19</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>192</v>
+        <v>511</v>
       </c>
       <c r="C20" s="42" t="s">
         <v>204</v>
@@ -3843,7 +3865,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="42">
         <v>20</v>
       </c>
@@ -3863,7 +3885,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="42">
         <v>21</v>
       </c>
@@ -3883,7 +3905,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="42">
         <v>22</v>
       </c>
@@ -3903,7 +3925,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="42">
         <v>23</v>
       </c>
@@ -3923,7 +3945,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="42">
         <v>24</v>
       </c>
@@ -3941,7 +3963,7 @@
       </c>
       <c r="F25" s="42"/>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="42">
         <v>25</v>
       </c>
@@ -3959,7 +3981,7 @@
       </c>
       <c r="F26" s="42"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="42">
         <v>26</v>
       </c>
@@ -3977,7 +3999,7 @@
       </c>
       <c r="F27" s="42"/>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="42">
         <v>27</v>
       </c>
@@ -3997,7 +4019,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="42">
         <v>28</v>
       </c>
@@ -4015,7 +4037,7 @@
       </c>
       <c r="F29" s="42"/>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="42">
         <v>29</v>
       </c>
@@ -4026,14 +4048,14 @@
         <v>356</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="E30" s="42" t="s">
-        <v>9</v>
+        <v>327</v>
       </c>
       <c r="F30" s="42"/>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="42">
         <v>30</v>
       </c>
@@ -4051,7 +4073,7 @@
       </c>
       <c r="F31" s="42"/>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="42">
         <v>31</v>
       </c>
@@ -4071,7 +4093,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" s="42">
         <v>32</v>
       </c>
@@ -4091,7 +4113,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="42">
         <v>33</v>
       </c>
@@ -4109,7 +4131,7 @@
       </c>
       <c r="F34" s="42"/>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="42">
         <v>34</v>
       </c>
@@ -4129,7 +4151,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="42">
         <v>35</v>
       </c>
@@ -4149,7 +4171,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="42">
         <v>36</v>
       </c>
@@ -4169,7 +4191,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" s="42">
         <v>37</v>
       </c>
@@ -4189,7 +4211,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="42">
         <v>38</v>
       </c>
@@ -4209,7 +4231,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="42">
         <v>39</v>
       </c>
@@ -4229,7 +4251,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" s="42">
         <v>40</v>
       </c>
@@ -4249,7 +4271,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" s="42">
         <v>41</v>
       </c>
@@ -4269,7 +4291,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" s="42">
         <v>42</v>
       </c>
@@ -4287,7 +4309,7 @@
       </c>
       <c r="F43" s="42"/>
     </row>
-    <row r="44" spans="1:6" ht="15.45">
+    <row r="44" spans="1:6" ht="16" x14ac:dyDescent="0.45">
       <c r="A44" s="42">
         <v>43</v>
       </c>
@@ -4307,7 +4329,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="15.45">
+    <row r="45" spans="1:6" ht="16" x14ac:dyDescent="0.45">
       <c r="A45" s="42">
         <v>44</v>
       </c>
@@ -4327,7 +4349,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="15.45">
+    <row r="46" spans="1:6" ht="16" x14ac:dyDescent="0.45">
       <c r="A46" s="42">
         <v>45</v>
       </c>
@@ -4345,7 +4367,7 @@
       </c>
       <c r="F46" s="42"/>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" s="42">
         <v>46</v>
       </c>
@@ -4365,7 +4387,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" s="42">
         <v>47</v>
       </c>
@@ -4385,7 +4407,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" s="42">
         <v>48</v>
       </c>
@@ -4405,7 +4427,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" s="42">
         <v>49</v>
       </c>
@@ -4423,7 +4445,7 @@
       </c>
       <c r="F50" s="42"/>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" s="42">
         <v>50</v>
       </c>
@@ -4441,7 +4463,7 @@
       </c>
       <c r="F51" s="42"/>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" s="42">
         <v>51</v>
       </c>
@@ -4470,19 +4492,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA8DE479-D69F-48E8-BF90-B067D08C8E1C}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:F105"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F114"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="40.85546875" style="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.85546875" style="30" customWidth="1"/>
-    <col min="3" max="3" width="2.78515625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" style="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="30" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.78515625" style="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="30"/>
+    <col min="1" max="1" width="40.83203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" style="30" customWidth="1"/>
+    <col min="3" max="3" width="2.75" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.58203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.75" style="30" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.1640625" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="41" t="s">
         <v>163</v>
       </c>
@@ -4502,7 +4524,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="32" t="s">
         <v>87</v>
       </c>
@@ -4518,7 +4540,7 @@
       <c r="E2" s="34"/>
       <c r="F2" s="47"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="32" t="s">
         <v>87</v>
       </c>
@@ -4534,7 +4556,7 @@
       <c r="E3" s="34"/>
       <c r="F3" s="47"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="32" t="s">
         <v>87</v>
       </c>
@@ -4552,7 +4574,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="32" t="s">
         <v>87</v>
       </c>
@@ -4570,7 +4592,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="32" t="s">
         <v>87</v>
       </c>
@@ -4586,7 +4608,7 @@
       <c r="E6" s="34"/>
       <c r="F6" s="47"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="32" t="s">
         <v>87</v>
       </c>
@@ -4602,7 +4624,7 @@
       <c r="E7" s="34"/>
       <c r="F7" s="47"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="32" t="s">
         <v>87</v>
       </c>
@@ -4620,7 +4642,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="32" t="s">
         <v>87</v>
       </c>
@@ -4638,7 +4660,7 @@
       </c>
       <c r="F9" s="49"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="32" t="s">
         <v>87</v>
       </c>
@@ -4656,7 +4678,7 @@
       </c>
       <c r="F10" s="49"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="32" t="s">
         <v>87</v>
       </c>
@@ -4672,7 +4694,7 @@
       <c r="E11" s="34"/>
       <c r="F11" s="47"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="32" t="s">
         <v>87</v>
       </c>
@@ -4688,7 +4710,7 @@
       <c r="E12" s="34"/>
       <c r="F12" s="47"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="32" t="s">
         <v>87</v>
       </c>
@@ -4706,7 +4728,7 @@
       </c>
       <c r="F13" s="49"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="32" t="s">
         <v>87</v>
       </c>
@@ -4722,7 +4744,7 @@
       <c r="E14" s="34"/>
       <c r="F14" s="47"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="32" t="s">
         <v>87</v>
       </c>
@@ -4738,7 +4760,7 @@
       <c r="E15" s="34"/>
       <c r="F15" s="47"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="32" t="s">
         <v>87</v>
       </c>
@@ -4756,7 +4778,7 @@
       </c>
       <c r="F16" s="49"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="32" t="s">
         <v>87</v>
       </c>
@@ -4774,7 +4796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="32" t="s">
         <v>87</v>
       </c>
@@ -4790,7 +4812,7 @@
       <c r="E18" s="34"/>
       <c r="F18" s="47"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="32" t="s">
         <v>87</v>
       </c>
@@ -4806,7 +4828,7 @@
       <c r="E19" s="34"/>
       <c r="F19" s="47"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="32" t="s">
         <v>87</v>
       </c>
@@ -4824,7 +4846,7 @@
       </c>
       <c r="F20" s="49"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="32" t="s">
         <v>87</v>
       </c>
@@ -4840,7 +4862,7 @@
       <c r="E21" s="34"/>
       <c r="F21" s="47"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="32" t="s">
         <v>87</v>
       </c>
@@ -4856,7 +4878,7 @@
       <c r="E22" s="34"/>
       <c r="F22" s="47"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="32" t="s">
         <v>93</v>
       </c>
@@ -4874,7 +4896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="32" t="s">
         <v>93</v>
       </c>
@@ -4892,7 +4914,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" s="32" t="s">
         <v>93</v>
       </c>
@@ -4910,7 +4932,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" s="32" t="s">
         <v>93</v>
       </c>
@@ -4928,7 +4950,7 @@
       </c>
       <c r="F26" s="49"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="32" t="s">
         <v>93</v>
       </c>
@@ -4946,7 +4968,7 @@
       </c>
       <c r="F27" s="49"/>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="32" t="s">
         <v>93</v>
       </c>
@@ -4964,7 +4986,7 @@
       </c>
       <c r="F28" s="49"/>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" s="32" t="s">
         <v>93</v>
       </c>
@@ -4982,7 +5004,7 @@
       </c>
       <c r="F29" s="49"/>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" s="32" t="s">
         <v>93</v>
       </c>
@@ -4998,7 +5020,7 @@
       <c r="E30" s="37"/>
       <c r="F30" s="50"/>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" s="32" t="s">
         <v>93</v>
       </c>
@@ -5016,7 +5038,7 @@
       </c>
       <c r="F31" s="49"/>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" s="32" t="s">
         <v>103</v>
       </c>
@@ -5034,7 +5056,7 @@
       </c>
       <c r="F32" s="49"/>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" s="32" t="s">
         <v>103</v>
       </c>
@@ -5052,7 +5074,7 @@
       </c>
       <c r="F33" s="49"/>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" s="32" t="s">
         <v>103</v>
       </c>
@@ -5070,7 +5092,7 @@
       </c>
       <c r="F34" s="49"/>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" s="32" t="s">
         <v>103</v>
       </c>
@@ -5086,7 +5108,7 @@
       <c r="E35" s="26"/>
       <c r="F35" s="40"/>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" s="32" t="s">
         <v>103</v>
       </c>
@@ -5104,7 +5126,7 @@
       </c>
       <c r="F36" s="49"/>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" s="32" t="s">
         <v>103</v>
       </c>
@@ -5120,7 +5142,7 @@
       <c r="E37" s="26"/>
       <c r="F37" s="40"/>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38" s="32" t="s">
         <v>103</v>
       </c>
@@ -5136,7 +5158,7 @@
       <c r="E38" s="26"/>
       <c r="F38" s="40"/>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" s="32" t="s">
         <v>103</v>
       </c>
@@ -5152,7 +5174,7 @@
       <c r="E39" s="26"/>
       <c r="F39" s="40"/>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" s="32" t="s">
         <v>103</v>
       </c>
@@ -5170,7 +5192,7 @@
       </c>
       <c r="F40" s="49"/>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" s="32" t="s">
         <v>103</v>
       </c>
@@ -5186,7 +5208,7 @@
       <c r="E41" s="26"/>
       <c r="F41" s="40"/>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" s="32" t="s">
         <v>103</v>
       </c>
@@ -5204,7 +5226,7 @@
       </c>
       <c r="F42" s="49"/>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" s="32" t="s">
         <v>103</v>
       </c>
@@ -5220,7 +5242,7 @@
       <c r="E43" s="26"/>
       <c r="F43" s="40"/>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44" s="32" t="s">
         <v>103</v>
       </c>
@@ -5236,7 +5258,7 @@
       <c r="E44" s="26"/>
       <c r="F44" s="40"/>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45" s="32" t="s">
         <v>103</v>
       </c>
@@ -5252,7 +5274,7 @@
       <c r="E45" s="26"/>
       <c r="F45" s="40"/>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" s="32" t="s">
         <v>103</v>
       </c>
@@ -5268,7 +5290,7 @@
       <c r="E46" s="26"/>
       <c r="F46" s="40"/>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47" s="32" t="s">
         <v>103</v>
       </c>
@@ -5284,7 +5306,7 @@
       <c r="E47" s="26"/>
       <c r="F47" s="40"/>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" s="32" t="s">
         <v>103</v>
       </c>
@@ -5300,7 +5322,7 @@
       <c r="E48" s="26"/>
       <c r="F48" s="40"/>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" s="32" t="s">
         <v>103</v>
       </c>
@@ -5316,7 +5338,7 @@
       <c r="E49" s="26"/>
       <c r="F49" s="40"/>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" s="32" t="s">
         <v>103</v>
       </c>
@@ -5334,7 +5356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" s="32" t="s">
         <v>103</v>
       </c>
@@ -5352,7 +5374,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52" s="32" t="s">
         <v>103</v>
       </c>
@@ -5370,7 +5392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53" s="32" t="s">
         <v>114</v>
       </c>
@@ -5388,7 +5410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" s="32" t="s">
         <v>114</v>
       </c>
@@ -5406,7 +5428,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55" s="32" t="s">
         <v>114</v>
       </c>
@@ -5424,7 +5446,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56" s="32" t="s">
         <v>114</v>
       </c>
@@ -5440,7 +5462,7 @@
       <c r="E56" s="38"/>
       <c r="F56" s="52"/>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57" s="32" t="s">
         <v>114</v>
       </c>
@@ -5458,7 +5480,7 @@
       </c>
       <c r="F57" s="49"/>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58" s="32" t="s">
         <v>114</v>
       </c>
@@ -5476,7 +5498,7 @@
       </c>
       <c r="F58" s="49"/>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A59" s="32" t="s">
         <v>114</v>
       </c>
@@ -5494,7 +5516,7 @@
       </c>
       <c r="F59" s="49"/>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A60" s="32" t="s">
         <v>114</v>
       </c>
@@ -5512,7 +5534,7 @@
       </c>
       <c r="F60" s="49"/>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61" s="32" t="s">
         <v>114</v>
       </c>
@@ -5528,7 +5550,7 @@
       <c r="E61" s="38"/>
       <c r="F61" s="52"/>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62" s="32" t="s">
         <v>114</v>
       </c>
@@ -5546,7 +5568,7 @@
       </c>
       <c r="F62" s="49"/>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63" s="32" t="s">
         <v>115</v>
       </c>
@@ -5564,7 +5586,7 @@
       </c>
       <c r="F63" s="49"/>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64" s="32" t="s">
         <v>115</v>
       </c>
@@ -5580,7 +5602,7 @@
       <c r="E64" s="40"/>
       <c r="F64" s="40"/>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" s="32" t="s">
         <v>115</v>
       </c>
@@ -5598,7 +5620,7 @@
       </c>
       <c r="F65" s="49"/>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66" s="32" t="s">
         <v>115</v>
       </c>
@@ -5616,7 +5638,7 @@
       </c>
       <c r="F66" s="49"/>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67" s="32" t="s">
         <v>115</v>
       </c>
@@ -5632,7 +5654,7 @@
       <c r="E67" s="40"/>
       <c r="F67" s="40"/>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68" s="32" t="s">
         <v>115</v>
       </c>
@@ -5648,7 +5670,7 @@
       <c r="E68" s="26"/>
       <c r="F68" s="40"/>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69" s="32" t="s">
         <v>115</v>
       </c>
@@ -5664,7 +5686,7 @@
       <c r="E69" s="40"/>
       <c r="F69" s="40"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70" s="32" t="s">
         <v>115</v>
       </c>
@@ -5680,7 +5702,7 @@
       <c r="E70" s="26"/>
       <c r="F70" s="40"/>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71" s="32" t="s">
         <v>115</v>
       </c>
@@ -5698,7 +5720,7 @@
       </c>
       <c r="F71" s="49"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72" s="32" t="s">
         <v>115</v>
       </c>
@@ -5716,7 +5738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73" s="32" t="s">
         <v>115</v>
       </c>
@@ -5734,7 +5756,7 @@
       </c>
       <c r="F73" s="49"/>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A74" s="32" t="s">
         <v>116</v>
       </c>
@@ -5752,7 +5774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A75" s="32" t="s">
         <v>116</v>
       </c>
@@ -5770,7 +5792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A76" s="32" t="s">
         <v>116</v>
       </c>
@@ -5788,7 +5810,7 @@
       </c>
       <c r="F76" s="49"/>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A77" s="32" t="s">
         <v>116</v>
       </c>
@@ -5806,7 +5828,7 @@
       </c>
       <c r="F77" s="49"/>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A78" s="32" t="s">
         <v>116</v>
       </c>
@@ -5822,7 +5844,7 @@
       <c r="E78" s="34"/>
       <c r="F78" s="47"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79" s="32" t="s">
         <v>116</v>
       </c>
@@ -5840,7 +5862,7 @@
       </c>
       <c r="F79" s="49"/>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80" s="32" t="s">
         <v>116</v>
       </c>
@@ -5858,7 +5880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A81" s="32" t="s">
         <v>116</v>
       </c>
@@ -5876,7 +5898,7 @@
       </c>
       <c r="F81" s="49"/>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A82" s="32" t="s">
         <v>116</v>
       </c>
@@ -5894,7 +5916,7 @@
       </c>
       <c r="F82" s="49"/>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A83" s="32" t="s">
         <v>124</v>
       </c>
@@ -5912,7 +5934,7 @@
       </c>
       <c r="F83" s="49"/>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A84" s="32" t="s">
         <v>124</v>
       </c>
@@ -5930,7 +5952,7 @@
       </c>
       <c r="F84" s="49"/>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A85" s="32" t="s">
         <v>124</v>
       </c>
@@ -5948,7 +5970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A86" s="32" t="s">
         <v>124</v>
       </c>
@@ -5964,7 +5986,7 @@
       <c r="E86" s="28"/>
       <c r="F86" s="53"/>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A87" s="32" t="s">
         <v>124</v>
       </c>
@@ -5982,7 +6004,7 @@
       </c>
       <c r="F87" s="49"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A88" s="32" t="s">
         <v>124</v>
       </c>
@@ -5998,7 +6020,7 @@
       <c r="E88" s="27"/>
       <c r="F88" s="54"/>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A89" s="32" t="s">
         <v>124</v>
       </c>
@@ -6016,7 +6038,7 @@
       </c>
       <c r="F89" s="49"/>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A90" s="32" t="s">
         <v>124</v>
       </c>
@@ -6032,7 +6054,7 @@
       <c r="E90" s="28"/>
       <c r="F90" s="53"/>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A91" s="32" t="s">
         <v>124</v>
       </c>
@@ -6048,7 +6070,7 @@
       <c r="E91" s="28"/>
       <c r="F91" s="53"/>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A92" s="32" t="s">
         <v>124</v>
       </c>
@@ -6066,7 +6088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A93" s="32" t="s">
         <v>124</v>
       </c>
@@ -6084,7 +6106,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A94" s="32" t="s">
         <v>124</v>
       </c>
@@ -6102,7 +6124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A95" s="32" t="s">
         <v>124</v>
       </c>
@@ -6118,7 +6140,7 @@
       <c r="E95" s="28"/>
       <c r="F95" s="53"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A96" s="32" t="s">
         <v>124</v>
       </c>
@@ -6136,7 +6158,7 @@
       </c>
       <c r="F96" s="49"/>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A97" s="32" t="s">
         <v>129</v>
       </c>
@@ -6154,7 +6176,7 @@
       </c>
       <c r="F97" s="49"/>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A98" s="32" t="s">
         <v>129</v>
       </c>
@@ -6172,7 +6194,7 @@
       </c>
       <c r="F98" s="49"/>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A99" s="32" t="s">
         <v>129</v>
       </c>
@@ -6190,7 +6212,7 @@
       </c>
       <c r="F99" s="49"/>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A100" s="32" t="s">
         <v>129</v>
       </c>
@@ -6208,7 +6230,7 @@
       </c>
       <c r="F100" s="49"/>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A101" s="32" t="s">
         <v>129</v>
       </c>
@@ -6226,7 +6248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A102" s="32" t="s">
         <v>129</v>
       </c>
@@ -6244,7 +6266,7 @@
       </c>
       <c r="F102" s="49"/>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A103" s="32" t="s">
         <v>129</v>
       </c>
@@ -6262,7 +6284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A104" s="32" t="s">
         <v>129</v>
       </c>
@@ -6280,7 +6302,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A105" s="32" t="s">
         <v>129</v>
       </c>
@@ -6295,6 +6317,168 @@
       </c>
       <c r="E105" s="32"/>
       <c r="F105" s="32" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A106" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="B106" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="C106" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="D106" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E106" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F106" s="49"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A107" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="B107" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="C107" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="D107" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E107" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F107" s="49"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A108" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="B108" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="C108" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D108" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="E108" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="F108" s="49"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A109" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="B109" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="C109" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="D109" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="E109" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="F109" s="49"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A110" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="B110" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="C110" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D110" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="E110" s="32"/>
+      <c r="F110" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A111" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="B111" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="C111" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="D111" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="E111" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F111" s="49"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A112" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="B112" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="C112" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="D112" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E112" s="32"/>
+      <c r="F112" s="32" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A113" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="B113" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="C113" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D113" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E113" s="32"/>
+      <c r="F113" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A114" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="B114" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="C114" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D114" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="E114" s="32"/>
+      <c r="F114" s="32" t="s">
         <v>139</v>
       </c>
     </row>
@@ -6342,22 +6526,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52549504-4590-40BA-B8EA-337736F4028C}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="14.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="6.92578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.35546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.35546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.9140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" style="2" customWidth="1"/>
     <col min="5" max="5" width="29.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="2"/>
+    <col min="6" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="45" t="s">
         <v>126</v>
       </c>
@@ -6374,7 +6558,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="60" t="s">
         <v>254</v>
       </c>
@@ -6391,7 +6575,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="60" t="s">
         <v>254</v>
       </c>
@@ -6408,7 +6592,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="60" t="s">
         <v>258</v>
       </c>
@@ -6425,7 +6609,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="60" t="s">
         <v>261</v>
       </c>
@@ -6442,7 +6626,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" s="60" t="s">
         <v>261</v>
       </c>
@@ -6459,7 +6643,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" s="60" t="s">
         <v>261</v>
       </c>
@@ -6476,7 +6660,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" s="60" t="s">
         <v>175</v>
       </c>
@@ -6493,7 +6677,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" s="60" t="s">
         <v>175</v>
       </c>
@@ -6510,7 +6694,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" s="60" t="s">
         <v>175</v>
       </c>
@@ -6527,7 +6711,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" s="60" t="s">
         <v>268</v>
       </c>
@@ -6544,7 +6728,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" s="45" t="s">
         <v>283</v>
       </c>
@@ -6558,7 +6742,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" s="60" t="s">
         <v>286</v>
       </c>
@@ -6572,7 +6756,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="60" t="s">
         <v>288</v>
       </c>
@@ -6586,7 +6770,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="60" t="s">
         <v>352</v>
       </c>
@@ -6600,7 +6784,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="60" t="s">
         <v>290</v>
       </c>
@@ -6614,7 +6798,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="60" t="s">
         <v>293</v>
       </c>
@@ -6626,7 +6810,7 @@
       </c>
       <c r="D20" s="60"/>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="60" t="s">
         <v>296</v>
       </c>
@@ -6638,7 +6822,7 @@
       </c>
       <c r="D21" s="60"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" s="60" t="s">
         <v>304</v>
       </c>
@@ -6652,7 +6836,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" s="60" t="s">
         <v>307</v>
       </c>
@@ -6666,7 +6850,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" s="60" t="s">
         <v>310</v>
       </c>
@@ -6680,7 +6864,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" s="60" t="s">
         <v>320</v>
       </c>
@@ -6694,7 +6878,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" s="60" t="s">
         <v>334</v>
       </c>
@@ -6708,7 +6892,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" s="60" t="s">
         <v>290</v>
       </c>
@@ -6722,7 +6906,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" s="60" t="s">
         <v>307</v>
       </c>
@@ -6736,7 +6920,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" s="60" t="s">
         <v>344</v>
       </c>
@@ -6750,27 +6934,27 @@
         <v>347</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" s="2" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>319</v>
       </c>
@@ -6787,18 +6971,18 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.2109375" style="63" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.78515625" style="63" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="63" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.7109375" style="63" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.78515625" style="63" customWidth="1"/>
-    <col min="6" max="6" width="78.2109375" style="63" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="63"/>
+    <col min="1" max="1" width="13.25" style="63" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.75" style="63" customWidth="1"/>
+    <col min="3" max="3" width="8.58203125" style="63" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.75" style="63" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.75" style="63" customWidth="1"/>
+    <col min="6" max="6" width="78.25" style="63" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.1640625" style="63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="62" t="s">
         <v>398</v>
       </c>
@@ -6818,7 +7002,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="64">
         <v>90726181415</v>
       </c>
@@ -6838,7 +7022,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="64">
         <v>90463359240</v>
       </c>
@@ -6858,7 +7042,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="64">
         <v>86263737582</v>
       </c>
@@ -6878,7 +7062,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="64">
         <v>90318747741</v>
       </c>
@@ -6898,7 +7082,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="64">
         <v>80648858007</v>
       </c>
@@ -6918,7 +7102,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="64">
         <v>93220547947</v>
       </c>
@@ -6938,7 +7122,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="64">
         <v>80648858026</v>
       </c>
@@ -6958,7 +7142,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="64">
         <v>91021780775</v>
       </c>
@@ -6978,7 +7162,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="64">
         <v>84634968862</v>
       </c>
@@ -6998,7 +7182,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="64">
         <v>93672537464</v>
       </c>
@@ -7018,7 +7202,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="64">
         <v>93179170670</v>
       </c>
@@ -7038,7 +7222,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="64">
         <v>93179170628</v>
       </c>
@@ -7058,7 +7242,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="64">
         <v>88176237136</v>
       </c>
@@ -7078,7 +7262,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="64">
         <v>90318747755</v>
       </c>
@@ -7098,7 +7282,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="64">
         <v>93672571449</v>
       </c>
@@ -7118,7 +7302,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="64">
         <v>93220547933</v>
       </c>
@@ -7138,7 +7322,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="64">
         <v>90726181419</v>
       </c>
@@ -7158,7 +7342,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="64">
         <v>87880167762</v>
       </c>
@@ -7178,7 +7362,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="64">
         <v>88186960178</v>
       </c>
@@ -7198,7 +7382,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="64">
         <v>88128325479</v>
       </c>
@@ -7218,7 +7402,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="64">
         <v>82314858827</v>
       </c>
@@ -7238,7 +7422,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="64">
         <v>75338048760</v>
       </c>
@@ -7258,7 +7442,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="64">
         <v>88176237168</v>
       </c>
@@ -7278,7 +7462,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="64">
         <v>77218920858</v>
       </c>
@@ -7298,7 +7482,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="64">
         <v>86263737587</v>
       </c>
@@ -7318,7 +7502,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="64">
         <v>87992013846</v>
       </c>
@@ -7338,7 +7522,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="64">
         <v>83700756628</v>
       </c>
@@ -7358,7 +7542,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="64">
         <v>73671510910</v>
       </c>
@@ -7378,7 +7562,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="64">
         <v>87418768783</v>
       </c>
@@ -7401,7 +7585,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="64">
         <v>74117666924</v>
       </c>
@@ -7421,7 +7605,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="64" t="s">
         <v>495</v>
       </c>
@@ -7441,7 +7625,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="64">
         <v>73672215064</v>
       </c>
@@ -7461,7 +7645,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="64">
         <v>88449262751</v>
       </c>
@@ -7493,18 +7677,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF47BDA5-BDD2-472E-B146-E1B4432935BA}">
   <dimension ref="A1:F105"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="40.85546875" style="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.85546875" style="30" customWidth="1"/>
-    <col min="3" max="3" width="2.78515625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" style="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="30" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.78515625" style="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="30"/>
+    <col min="1" max="1" width="40.83203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" style="30" customWidth="1"/>
+    <col min="3" max="3" width="2.75" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.58203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.75" style="30" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.1640625" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="41" t="s">
         <v>163</v>
       </c>
@@ -7524,7 +7708,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="32" t="s">
         <v>87</v>
       </c>
@@ -7540,7 +7724,7 @@
       <c r="E2" s="34"/>
       <c r="F2" s="47"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="32" t="s">
         <v>87</v>
       </c>
@@ -7556,7 +7740,7 @@
       <c r="E3" s="34"/>
       <c r="F3" s="47"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="32" t="s">
         <v>87</v>
       </c>
@@ -7574,7 +7758,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="32" t="s">
         <v>87</v>
       </c>
@@ -7592,7 +7776,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="32" t="s">
         <v>87</v>
       </c>
@@ -7608,7 +7792,7 @@
       <c r="E6" s="34"/>
       <c r="F6" s="47"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="32" t="s">
         <v>87</v>
       </c>
@@ -7624,7 +7808,7 @@
       <c r="E7" s="34"/>
       <c r="F7" s="47"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="32" t="s">
         <v>87</v>
       </c>
@@ -7642,7 +7826,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="32" t="s">
         <v>87</v>
       </c>
@@ -7660,7 +7844,7 @@
       </c>
       <c r="F9" s="49"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="32" t="s">
         <v>87</v>
       </c>
@@ -7678,7 +7862,7 @@
       </c>
       <c r="F10" s="49"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="32" t="s">
         <v>87</v>
       </c>
@@ -7694,7 +7878,7 @@
       <c r="E11" s="34"/>
       <c r="F11" s="47"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="32" t="s">
         <v>87</v>
       </c>
@@ -7710,7 +7894,7 @@
       <c r="E12" s="34"/>
       <c r="F12" s="47"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="32" t="s">
         <v>87</v>
       </c>
@@ -7728,7 +7912,7 @@
       </c>
       <c r="F13" s="49"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="32" t="s">
         <v>87</v>
       </c>
@@ -7744,7 +7928,7 @@
       <c r="E14" s="34"/>
       <c r="F14" s="47"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="32" t="s">
         <v>87</v>
       </c>
@@ -7760,7 +7944,7 @@
       <c r="E15" s="34"/>
       <c r="F15" s="47"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="32" t="s">
         <v>87</v>
       </c>
@@ -7778,7 +7962,7 @@
       </c>
       <c r="F16" s="49"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="32" t="s">
         <v>87</v>
       </c>
@@ -7796,7 +7980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="32" t="s">
         <v>87</v>
       </c>
@@ -7812,7 +7996,7 @@
       <c r="E18" s="34"/>
       <c r="F18" s="47"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="32" t="s">
         <v>87</v>
       </c>
@@ -7828,7 +8012,7 @@
       <c r="E19" s="34"/>
       <c r="F19" s="47"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="32" t="s">
         <v>87</v>
       </c>
@@ -7846,7 +8030,7 @@
       </c>
       <c r="F20" s="49"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="32" t="s">
         <v>87</v>
       </c>
@@ -7862,7 +8046,7 @@
       <c r="E21" s="34"/>
       <c r="F21" s="47"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="32" t="s">
         <v>87</v>
       </c>
@@ -7878,7 +8062,7 @@
       <c r="E22" s="34"/>
       <c r="F22" s="47"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="32" t="s">
         <v>93</v>
       </c>
@@ -7896,7 +8080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="32" t="s">
         <v>93</v>
       </c>
@@ -7914,7 +8098,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" s="32" t="s">
         <v>93</v>
       </c>
@@ -7932,7 +8116,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" s="32" t="s">
         <v>93</v>
       </c>
@@ -7950,7 +8134,7 @@
       </c>
       <c r="F26" s="49"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="32" t="s">
         <v>93</v>
       </c>
@@ -7968,7 +8152,7 @@
       </c>
       <c r="F27" s="49"/>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="32" t="s">
         <v>93</v>
       </c>
@@ -7986,7 +8170,7 @@
       </c>
       <c r="F28" s="49"/>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" s="32" t="s">
         <v>93</v>
       </c>
@@ -8004,7 +8188,7 @@
       </c>
       <c r="F29" s="49"/>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" s="32" t="s">
         <v>93</v>
       </c>
@@ -8020,7 +8204,7 @@
       <c r="E30" s="37"/>
       <c r="F30" s="50"/>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" s="32" t="s">
         <v>93</v>
       </c>
@@ -8038,7 +8222,7 @@
       </c>
       <c r="F31" s="49"/>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" s="32" t="s">
         <v>103</v>
       </c>
@@ -8056,7 +8240,7 @@
       </c>
       <c r="F32" s="49"/>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" s="32" t="s">
         <v>103</v>
       </c>
@@ -8074,7 +8258,7 @@
       </c>
       <c r="F33" s="49"/>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" s="32" t="s">
         <v>103</v>
       </c>
@@ -8092,7 +8276,7 @@
       </c>
       <c r="F34" s="49"/>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" s="32" t="s">
         <v>103</v>
       </c>
@@ -8108,7 +8292,7 @@
       <c r="E35" s="26"/>
       <c r="F35" s="40"/>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" s="32" t="s">
         <v>103</v>
       </c>
@@ -8126,7 +8310,7 @@
       </c>
       <c r="F36" s="49"/>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" s="32" t="s">
         <v>103</v>
       </c>
@@ -8142,7 +8326,7 @@
       <c r="E37" s="26"/>
       <c r="F37" s="40"/>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38" s="32" t="s">
         <v>103</v>
       </c>
@@ -8158,7 +8342,7 @@
       <c r="E38" s="26"/>
       <c r="F38" s="40"/>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" s="32" t="s">
         <v>103</v>
       </c>
@@ -8174,7 +8358,7 @@
       <c r="E39" s="26"/>
       <c r="F39" s="40"/>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" s="32" t="s">
         <v>103</v>
       </c>
@@ -8192,7 +8376,7 @@
       </c>
       <c r="F40" s="49"/>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" s="32" t="s">
         <v>103</v>
       </c>
@@ -8208,7 +8392,7 @@
       <c r="E41" s="26"/>
       <c r="F41" s="40"/>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" s="32" t="s">
         <v>103</v>
       </c>
@@ -8226,7 +8410,7 @@
       </c>
       <c r="F42" s="49"/>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" s="32" t="s">
         <v>103</v>
       </c>
@@ -8242,7 +8426,7 @@
       <c r="E43" s="26"/>
       <c r="F43" s="40"/>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44" s="32" t="s">
         <v>103</v>
       </c>
@@ -8258,7 +8442,7 @@
       <c r="E44" s="26"/>
       <c r="F44" s="40"/>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45" s="32" t="s">
         <v>103</v>
       </c>
@@ -8274,7 +8458,7 @@
       <c r="E45" s="26"/>
       <c r="F45" s="40"/>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" s="32" t="s">
         <v>103</v>
       </c>
@@ -8290,7 +8474,7 @@
       <c r="E46" s="26"/>
       <c r="F46" s="40"/>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47" s="32" t="s">
         <v>103</v>
       </c>
@@ -8306,7 +8490,7 @@
       <c r="E47" s="26"/>
       <c r="F47" s="40"/>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" s="32" t="s">
         <v>103</v>
       </c>
@@ -8322,7 +8506,7 @@
       <c r="E48" s="26"/>
       <c r="F48" s="40"/>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" s="32" t="s">
         <v>103</v>
       </c>
@@ -8338,7 +8522,7 @@
       <c r="E49" s="26"/>
       <c r="F49" s="40"/>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" s="32" t="s">
         <v>103</v>
       </c>
@@ -8356,7 +8540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" s="32" t="s">
         <v>103</v>
       </c>
@@ -8374,7 +8558,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52" s="32" t="s">
         <v>103</v>
       </c>
@@ -8392,7 +8576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53" s="32" t="s">
         <v>114</v>
       </c>
@@ -8410,7 +8594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" s="32" t="s">
         <v>114</v>
       </c>
@@ -8428,7 +8612,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55" s="32" t="s">
         <v>114</v>
       </c>
@@ -8446,7 +8630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56" s="32" t="s">
         <v>114</v>
       </c>
@@ -8462,7 +8646,7 @@
       <c r="E56" s="38"/>
       <c r="F56" s="52"/>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57" s="32" t="s">
         <v>114</v>
       </c>
@@ -8480,7 +8664,7 @@
       </c>
       <c r="F57" s="49"/>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58" s="32" t="s">
         <v>114</v>
       </c>
@@ -8498,7 +8682,7 @@
       </c>
       <c r="F58" s="49"/>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A59" s="32" t="s">
         <v>114</v>
       </c>
@@ -8516,7 +8700,7 @@
       </c>
       <c r="F59" s="49"/>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A60" s="32" t="s">
         <v>114</v>
       </c>
@@ -8534,7 +8718,7 @@
       </c>
       <c r="F60" s="49"/>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61" s="32" t="s">
         <v>114</v>
       </c>
@@ -8550,7 +8734,7 @@
       <c r="E61" s="38"/>
       <c r="F61" s="52"/>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62" s="32" t="s">
         <v>114</v>
       </c>
@@ -8568,7 +8752,7 @@
       </c>
       <c r="F62" s="49"/>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63" s="32" t="s">
         <v>115</v>
       </c>
@@ -8586,7 +8770,7 @@
       </c>
       <c r="F63" s="49"/>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64" s="32" t="s">
         <v>115</v>
       </c>
@@ -8602,7 +8786,7 @@
       <c r="E64" s="40"/>
       <c r="F64" s="40"/>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" s="32" t="s">
         <v>115</v>
       </c>
@@ -8620,7 +8804,7 @@
       </c>
       <c r="F65" s="49"/>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66" s="32" t="s">
         <v>115</v>
       </c>
@@ -8638,7 +8822,7 @@
       </c>
       <c r="F66" s="49"/>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67" s="32" t="s">
         <v>115</v>
       </c>
@@ -8654,7 +8838,7 @@
       <c r="E67" s="40"/>
       <c r="F67" s="40"/>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68" s="32" t="s">
         <v>115</v>
       </c>
@@ -8670,7 +8854,7 @@
       <c r="E68" s="26"/>
       <c r="F68" s="40"/>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69" s="32" t="s">
         <v>115</v>
       </c>
@@ -8686,7 +8870,7 @@
       <c r="E69" s="40"/>
       <c r="F69" s="40"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70" s="32" t="s">
         <v>115</v>
       </c>
@@ -8702,7 +8886,7 @@
       <c r="E70" s="26"/>
       <c r="F70" s="40"/>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71" s="32" t="s">
         <v>115</v>
       </c>
@@ -8720,7 +8904,7 @@
       </c>
       <c r="F71" s="49"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72" s="32" t="s">
         <v>115</v>
       </c>
@@ -8738,7 +8922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73" s="32" t="s">
         <v>115</v>
       </c>
@@ -8756,7 +8940,7 @@
       </c>
       <c r="F73" s="49"/>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A74" s="32" t="s">
         <v>116</v>
       </c>
@@ -8774,7 +8958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A75" s="32" t="s">
         <v>116</v>
       </c>
@@ -8792,7 +8976,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A76" s="32" t="s">
         <v>116</v>
       </c>
@@ -8810,7 +8994,7 @@
       </c>
       <c r="F76" s="49"/>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A77" s="32" t="s">
         <v>116</v>
       </c>
@@ -8828,7 +9012,7 @@
       </c>
       <c r="F77" s="49"/>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A78" s="32" t="s">
         <v>116</v>
       </c>
@@ -8844,7 +9028,7 @@
       <c r="E78" s="34"/>
       <c r="F78" s="47"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79" s="32" t="s">
         <v>116</v>
       </c>
@@ -8862,7 +9046,7 @@
       </c>
       <c r="F79" s="49"/>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80" s="32" t="s">
         <v>116</v>
       </c>
@@ -8880,7 +9064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A81" s="32" t="s">
         <v>116</v>
       </c>
@@ -8898,7 +9082,7 @@
       </c>
       <c r="F81" s="49"/>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A82" s="32" t="s">
         <v>116</v>
       </c>
@@ -8916,7 +9100,7 @@
       </c>
       <c r="F82" s="49"/>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A83" s="32" t="s">
         <v>124</v>
       </c>
@@ -8934,7 +9118,7 @@
       </c>
       <c r="F83" s="49"/>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A84" s="32" t="s">
         <v>124</v>
       </c>
@@ -8952,7 +9136,7 @@
       </c>
       <c r="F84" s="49"/>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A85" s="32" t="s">
         <v>124</v>
       </c>
@@ -8970,7 +9154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A86" s="32" t="s">
         <v>124</v>
       </c>
@@ -8986,7 +9170,7 @@
       <c r="E86" s="28"/>
       <c r="F86" s="53"/>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A87" s="32" t="s">
         <v>124</v>
       </c>
@@ -9004,7 +9188,7 @@
       </c>
       <c r="F87" s="49"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A88" s="32" t="s">
         <v>124</v>
       </c>
@@ -9020,7 +9204,7 @@
       <c r="E88" s="27"/>
       <c r="F88" s="54"/>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A89" s="32" t="s">
         <v>124</v>
       </c>
@@ -9038,7 +9222,7 @@
       </c>
       <c r="F89" s="49"/>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A90" s="32" t="s">
         <v>124</v>
       </c>
@@ -9054,7 +9238,7 @@
       <c r="E90" s="28"/>
       <c r="F90" s="53"/>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A91" s="32" t="s">
         <v>124</v>
       </c>
@@ -9070,7 +9254,7 @@
       <c r="E91" s="28"/>
       <c r="F91" s="53"/>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A92" s="32" t="s">
         <v>124</v>
       </c>
@@ -9088,7 +9272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A93" s="32" t="s">
         <v>124</v>
       </c>
@@ -9106,7 +9290,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A94" s="32" t="s">
         <v>124</v>
       </c>
@@ -9124,7 +9308,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A95" s="32" t="s">
         <v>124</v>
       </c>
@@ -9140,7 +9324,7 @@
       <c r="E95" s="28"/>
       <c r="F95" s="53"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A96" s="32" t="s">
         <v>124</v>
       </c>
@@ -9158,7 +9342,7 @@
       </c>
       <c r="F96" s="49"/>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A97" s="32" t="s">
         <v>129</v>
       </c>
@@ -9176,7 +9360,7 @@
       </c>
       <c r="F97" s="49"/>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A98" s="32" t="s">
         <v>129</v>
       </c>
@@ -9194,7 +9378,7 @@
       </c>
       <c r="F98" s="49"/>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A99" s="32" t="s">
         <v>129</v>
       </c>
@@ -9212,7 +9396,7 @@
       </c>
       <c r="F99" s="49"/>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A100" s="32" t="s">
         <v>129</v>
       </c>
@@ -9230,7 +9414,7 @@
       </c>
       <c r="F100" s="49"/>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A101" s="32" t="s">
         <v>129</v>
       </c>
@@ -9248,7 +9432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A102" s="32" t="s">
         <v>129</v>
       </c>
@@ -9266,7 +9450,7 @@
       </c>
       <c r="F102" s="49"/>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A103" s="32" t="s">
         <v>129</v>
       </c>
@@ -9284,7 +9468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A104" s="32" t="s">
         <v>129</v>
       </c>
@@ -9302,7 +9486,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A105" s="32" t="s">
         <v>129</v>
       </c>
@@ -9364,33 +9548,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D10536A-E0E0-49D9-841E-65214E1C7FD4}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:R56"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="14.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="20.640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.4140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.4140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.5" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.2109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.2109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.25" style="2" customWidth="1"/>
     <col min="9" max="9" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17.78515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.78515625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="11.0703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.0703125" style="2" customWidth="1"/>
-    <col min="17" max="17" width="11.2109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.42578125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.75" style="2" customWidth="1"/>
+    <col min="15" max="15" width="11.08203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.08203125" style="2" customWidth="1"/>
+    <col min="17" max="17" width="11.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.4140625" style="2" customWidth="1"/>
     <col min="19" max="20" width="28.5" style="2" customWidth="1"/>
-    <col min="21" max="21" width="54.5703125" style="2" customWidth="1"/>
+    <col min="21" max="21" width="54.58203125" style="2" customWidth="1"/>
     <col min="22" max="64" width="28.5" style="2" customWidth="1"/>
-    <col min="65" max="16384" width="9.140625" style="2"/>
+    <col min="65" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>65</v>
       </c>
@@ -9416,7 +9600,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -9470,7 +9654,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="45">
+    <row r="3" spans="1:18" ht="43.5" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -9520,7 +9704,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="45">
+    <row r="4" spans="1:18" ht="43.5" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -9576,7 +9760,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -9622,7 +9806,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -9670,7 +9854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -9714,7 +9898,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="34.75">
+    <row r="8" spans="1:18" ht="36" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -9762,7 +9946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -9806,7 +9990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -9858,7 +10042,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -9890,7 +10074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -9920,7 +10104,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -9942,7 +10126,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -9960,7 +10144,7 @@
       </c>
       <c r="P14" s="22"/>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -9980,7 +10164,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -9996,7 +10180,7 @@
       <c r="G16" s="14"/>
       <c r="H16" s="20"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -10012,7 +10196,7 @@
       <c r="G17" s="14"/>
       <c r="H17" s="20"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -10026,7 +10210,7 @@
       <c r="G18" s="14"/>
       <c r="H18" s="20"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -10040,7 +10224,7 @@
       <c r="G19" s="14"/>
       <c r="H19" s="20"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -10060,7 +10244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="46.3">
+    <row r="21" spans="1:8" ht="46" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -10078,7 +10262,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
@@ -10096,205 +10280,205 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B23" s="25"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B24" s="25"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B25" s="25"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B26" s="25"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B27" s="25"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B28" s="25"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B29" s="25"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B30" s="25"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B31" s="25"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B32" s="25"/>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B33" s="25"/>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B34" s="25"/>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B35" s="25"/>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B36" s="25"/>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B37" s="25"/>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B38" s="25"/>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B39" s="25"/>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B40" s="25"/>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B41" s="25"/>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B42" s="25"/>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B43" s="25"/>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B44" s="25"/>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B45" s="25"/>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B46" s="25"/>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B47" s="25"/>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B48" s="25"/>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B49" s="25"/>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B50" s="25"/>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B51" s="25"/>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B52" s="25"/>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B53" s="25"/>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B54" s="25"/>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B55" s="25"/>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" s="1" t="s">
         <v>64</v>
       </c>

--- a/config.xlsx
+++ b/config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulmann\Downloads\PJ_NAVER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulmann\Documents\Business\OwnBusiness\○네이버스마트스토어 RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A8BE92-B038-403C-985B-FA07D676E8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F0676F-6AE0-43F4-8844-C6F1BBD20779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductRoute" sheetId="3" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="516">
   <si>
     <t>보내는사람</t>
   </si>
@@ -892,10 +892,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>갑오징어, 생물오징어, 생물 호래기, 급냉 호래기, 생물 한치, 실속형 5미, 실속형 10미</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ActionType</t>
   </si>
   <si>
@@ -1147,10 +1143,6 @@
   </si>
   <si>
     <t>REPLACE_REGEX_SUB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>무라벨 /// 쭈구리</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2105,6 +2097,26 @@
   </si>
   <si>
     <t>장어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;&gt; 신상품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑오징어, 생물오징어, 생물 호래기, 급냉 호래기, 생물 한치, 실속형 5미, 실속형 10미, 주꾸미, 새조개, 꽃게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">주꾸미 선택: , (알배기 30~40%/국산), (알없음/중국산), (알배기 40~50%/중국산), 새조개 선택: ,꽃게 선택: , 꼬막 선택: </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무라벨 /// 쭈구리, 활주꾸미 /// 연안 활 쭈꾸미, 급냉 주꾸미 /// 봄 제철 쭈꾸미, 알주꾸미 /// 탱탱 알주꾸미, 활 암꽃게 소 /// 연안 활 소암게, 활 암꽃게 대 /// 연안 활 대암게, 새꼬막 소 /// 새꼬막 소짜, 새꼬막 중 /// 새꼬막 중짜, 새꼬막 대 /// 새꼬막 대짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑오징어, 생물오징어, 생물 호래기, 급냉 호래기, 생물 한치, 실속형 5미, 실속형 10미, 주꾸미, 새조개, 꽃게, 새꼬막</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3355,7 +3367,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C4" s="57" t="s">
         <v>116</v>
@@ -3399,7 +3411,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>249</v>
+        <v>515</v>
       </c>
       <c r="C8" s="57" t="s">
         <v>114</v>
@@ -3421,7 +3433,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C10" s="57" t="s">
         <v>129</v>
@@ -3443,10 +3455,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
@@ -3469,7 +3481,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE8C8B0-87AB-4B5A-85D1-21EF511A776A}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultColWidth="11.4140625" defaultRowHeight="14.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="2" bestFit="1" customWidth="1"/>
@@ -3481,7 +3493,7 @@
     <col min="7" max="16384" width="11.4140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="44" t="s">
         <v>5</v>
       </c>
@@ -3501,7 +3513,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="42">
         <v>1</v>
       </c>
@@ -3515,13 +3527,13 @@
         <v>166</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F2" s="42" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="42">
         <v>2</v>
       </c>
@@ -3529,19 +3541,19 @@
         <v>196</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D3" s="42" t="s">
         <v>166</v>
       </c>
       <c r="E3" s="42" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F3" s="42" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="42">
         <v>3</v>
       </c>
@@ -3549,19 +3561,19 @@
         <v>196</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D4" s="42" t="s">
         <v>166</v>
       </c>
       <c r="E4" s="42" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F4" s="42" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="42">
         <v>4</v>
       </c>
@@ -3569,7 +3581,7 @@
         <v>196</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D5" s="42" t="s">
         <v>246</v>
@@ -3581,7 +3593,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="42">
         <v>5</v>
       </c>
@@ -3599,7 +3611,7 @@
       </c>
       <c r="F6" s="42"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="42">
         <v>6</v>
       </c>
@@ -3619,12 +3631,12 @@
         <v>168</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="42">
         <v>7</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>7</v>
+        <v>512</v>
       </c>
       <c r="C8" s="42" t="s">
         <v>7</v>
@@ -3633,71 +3645,74 @@
         <v>169</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F8" s="42" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="42">
         <v>8</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>192</v>
+        <v>7</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>204</v>
+        <v>7</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>166</v>
-      </c>
-      <c r="E9" s="43" t="s">
-        <v>205</v>
+        <v>169</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>513</v>
       </c>
       <c r="F9" s="42" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+        <v>170</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="42">
         <v>9</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>365</v>
+        <v>192</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>364</v>
+        <v>204</v>
       </c>
       <c r="D10" s="42" t="s">
         <v>166</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>354</v>
-      </c>
-      <c r="F10" s="42"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+        <v>205</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="42">
         <v>10</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>7</v>
+        <v>363</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>7</v>
+        <v>362</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>331</v>
+        <v>166</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>330</v>
-      </c>
-      <c r="F11" s="42" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+        <v>352</v>
+      </c>
+      <c r="F11" s="42"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="42">
         <v>11</v>
       </c>
@@ -3708,16 +3723,16 @@
         <v>7</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="42">
         <v>12</v>
       </c>
@@ -3725,17 +3740,19 @@
         <v>7</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>376</v>
+        <v>7</v>
       </c>
       <c r="D13" s="42" t="s">
-        <v>169</v>
+        <v>330</v>
       </c>
       <c r="E13" s="43" t="s">
-        <v>377</v>
-      </c>
-      <c r="F13" s="42"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+        <v>348</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="42">
         <v>13</v>
       </c>
@@ -3743,17 +3760,17 @@
         <v>7</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E14" s="43" t="s">
-        <v>205</v>
+        <v>375</v>
       </c>
       <c r="F14" s="42"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="42">
         <v>14</v>
       </c>
@@ -3761,17 +3778,17 @@
         <v>7</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D15" s="42" t="s">
-        <v>215</v>
-      </c>
-      <c r="E15" s="42" t="s">
-        <v>327</v>
+        <v>166</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>205</v>
       </c>
       <c r="F15" s="42"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="42">
         <v>15</v>
       </c>
@@ -3779,51 +3796,51 @@
         <v>7</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>7</v>
+        <v>368</v>
       </c>
       <c r="D16" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="E16" s="43" t="s">
-        <v>332</v>
-      </c>
-      <c r="F16" s="42" t="s">
-        <v>333</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="F16" s="42"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="42">
         <v>16</v>
       </c>
       <c r="B17" s="42" t="s">
-        <v>196</v>
+        <v>7</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>358</v>
+        <v>7</v>
       </c>
       <c r="D17" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>362</v>
-      </c>
-      <c r="F17" s="42"/>
+        <v>514</v>
+      </c>
+      <c r="F17" s="42" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="42">
         <v>17</v>
       </c>
       <c r="B18" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>7</v>
+        <v>356</v>
       </c>
       <c r="D18" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="F18" s="42"/>
     </row>
@@ -3835,13 +3852,13 @@
         <v>7</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>371</v>
+        <v>7</v>
       </c>
       <c r="D19" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="F19" s="42"/>
     </row>
@@ -3850,30 +3867,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>511</v>
+        <v>7</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>204</v>
+        <v>369</v>
       </c>
       <c r="D20" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="E20" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="59" t="s">
-        <v>207</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>370</v>
+      </c>
+      <c r="F20" s="42"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="42">
         <v>20</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>7</v>
+        <v>509</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>374</v>
+        <v>204</v>
       </c>
       <c r="D21" s="42" t="s">
         <v>171</v>
@@ -3881,8 +3896,8 @@
       <c r="E21" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="42" t="s">
-        <v>243</v>
+      <c r="F21" s="59" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
@@ -3893,7 +3908,7 @@
         <v>7</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D22" s="42" t="s">
         <v>171</v>
@@ -3913,7 +3928,7 @@
         <v>7</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D23" s="42" t="s">
         <v>171</v>
@@ -3933,7 +3948,7 @@
         <v>7</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>248</v>
+        <v>367</v>
       </c>
       <c r="D24" s="42" t="s">
         <v>171</v>
@@ -3953,15 +3968,17 @@
         <v>7</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>379</v>
+        <v>248</v>
       </c>
       <c r="D25" s="42" t="s">
-        <v>169</v>
-      </c>
-      <c r="E25" s="43" t="s">
-        <v>377</v>
-      </c>
-      <c r="F25" s="42"/>
+        <v>171</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="42" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="42">
@@ -3971,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D26" s="42" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="F26" s="42"/>
     </row>
@@ -3989,13 +4006,13 @@
         <v>7</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D27" s="42" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F27" s="42"/>
     </row>
@@ -4007,35 +4024,35 @@
         <v>7</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D28" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="E28" s="42" t="s">
-        <v>380</v>
-      </c>
-      <c r="F28" s="42" t="s">
-        <v>243</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>375</v>
+      </c>
+      <c r="F28" s="42"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="42">
         <v>28</v>
       </c>
       <c r="B29" s="42" t="s">
-        <v>196</v>
+        <v>7</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="D29" s="42" t="s">
         <v>171</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="42"/>
+        <v>378</v>
+      </c>
+      <c r="F29" s="42" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="42">
@@ -4048,10 +4065,10 @@
         <v>356</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>215</v>
+        <v>171</v>
       </c>
       <c r="E30" s="42" t="s">
-        <v>327</v>
+        <v>9</v>
       </c>
       <c r="F30" s="42"/>
     </row>
@@ -4060,16 +4077,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="D31" s="42" t="s">
         <v>215</v>
       </c>
       <c r="E31" s="42" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F31" s="42"/>
     </row>
@@ -4081,17 +4098,15 @@
         <v>7</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>325</v>
+        <v>362</v>
       </c>
       <c r="D32" s="42" t="s">
         <v>215</v>
       </c>
       <c r="E32" s="42" t="s">
-        <v>217</v>
-      </c>
-      <c r="F32" s="59" t="s">
         <v>326</v>
       </c>
+      <c r="F32" s="42"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" s="42">
@@ -4101,16 +4116,16 @@
         <v>7</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="D33" s="42" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="42" t="s">
-        <v>224</v>
+        <v>217</v>
+      </c>
+      <c r="F33" s="59" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
@@ -4121,15 +4136,17 @@
         <v>7</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>395</v>
+        <v>7</v>
       </c>
       <c r="D34" s="42" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>327</v>
-      </c>
-      <c r="F34" s="42"/>
+        <v>8</v>
+      </c>
+      <c r="F34" s="42" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="42">
@@ -4139,17 +4156,15 @@
         <v>7</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>7</v>
+        <v>393</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="E35" s="42" t="s">
-        <v>225</v>
-      </c>
-      <c r="F35" s="42" t="s">
-        <v>226</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="F35" s="42"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="42">
@@ -4165,10 +4180,10 @@
         <v>172</v>
       </c>
       <c r="E36" s="42" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F36" s="42" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
@@ -4185,10 +4200,10 @@
         <v>172</v>
       </c>
       <c r="E37" s="42" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="F37" s="42" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.4">
@@ -4205,10 +4220,10 @@
         <v>172</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>359</v>
+        <v>244</v>
       </c>
       <c r="F38" s="42" t="s">
-        <v>360</v>
+        <v>245</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
@@ -4222,13 +4237,13 @@
         <v>7</v>
       </c>
       <c r="D39" s="42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>229</v>
+        <v>357</v>
       </c>
       <c r="F39" s="42" t="s">
-        <v>230</v>
+        <v>358</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
@@ -4245,10 +4260,10 @@
         <v>173</v>
       </c>
       <c r="E40" s="42" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F40" s="42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.4">
@@ -4265,10 +4280,10 @@
         <v>173</v>
       </c>
       <c r="E41" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F41" s="42" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.4">
@@ -4285,10 +4300,10 @@
         <v>173</v>
       </c>
       <c r="E42" s="42" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F42" s="42" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.4">
@@ -4299,54 +4314,54 @@
         <v>7</v>
       </c>
       <c r="C43" s="42" t="s">
-        <v>361</v>
+        <v>7</v>
       </c>
       <c r="D43" s="42" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>327</v>
-      </c>
-      <c r="F43" s="42"/>
-    </row>
-    <row r="44" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+        <v>240</v>
+      </c>
+      <c r="F43" s="42" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" s="42">
         <v>43</v>
       </c>
-      <c r="B44" s="57" t="s">
-        <v>124</v>
+      <c r="B44" s="42" t="s">
+        <v>7</v>
       </c>
       <c r="C44" s="42" t="s">
-        <v>203</v>
+        <v>359</v>
       </c>
       <c r="D44" s="42" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E44" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" s="42" t="s">
-        <v>209</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="F44" s="42"/>
     </row>
     <row r="45" spans="1:6" ht="16" x14ac:dyDescent="0.45">
       <c r="A45" s="42">
         <v>44</v>
       </c>
       <c r="B45" s="57" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="C45" s="42" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D45" s="42" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E45" s="42" t="s">
         <v>9</v>
       </c>
       <c r="F45" s="42" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="16" x14ac:dyDescent="0.45">
@@ -4354,38 +4369,38 @@
         <v>45</v>
       </c>
       <c r="B46" s="57" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="C46" s="42" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D46" s="42" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="E46" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="F46" s="42"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+      <c r="F46" s="42" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="16" x14ac:dyDescent="0.45">
       <c r="A47" s="42">
         <v>46</v>
       </c>
-      <c r="B47" s="42" t="s">
-        <v>7</v>
+      <c r="B47" s="57" t="s">
+        <v>124</v>
       </c>
       <c r="C47" s="42" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="D47" s="42" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="E47" s="42" t="s">
-        <v>327</v>
-      </c>
-      <c r="F47" s="42" t="s">
-        <v>220</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="F47" s="42"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" s="42">
@@ -4395,16 +4410,16 @@
         <v>7</v>
       </c>
       <c r="C48" s="42" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="D48" s="42" t="s">
         <v>215</v>
       </c>
       <c r="E48" s="42" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F48" s="42" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.4">
@@ -4415,13 +4430,13 @@
         <v>7</v>
       </c>
       <c r="C49" s="42" t="s">
-        <v>373</v>
+        <v>242</v>
       </c>
       <c r="D49" s="42" t="s">
         <v>215</v>
       </c>
       <c r="E49" s="42" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F49" s="42" t="s">
         <v>216</v>
@@ -4435,15 +4450,17 @@
         <v>7</v>
       </c>
       <c r="C50" s="42" t="s">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="D50" s="42" t="s">
         <v>215</v>
       </c>
       <c r="E50" s="42" t="s">
-        <v>327</v>
-      </c>
-      <c r="F50" s="42"/>
+        <v>326</v>
+      </c>
+      <c r="F50" s="42" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" s="42">
@@ -4453,13 +4470,13 @@
         <v>7</v>
       </c>
       <c r="C51" s="42" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="D51" s="42" t="s">
         <v>215</v>
       </c>
       <c r="E51" s="42" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F51" s="42"/>
     </row>
@@ -4471,15 +4488,33 @@
         <v>7</v>
       </c>
       <c r="C52" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="D52" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="E52" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="F52" s="42"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A53" s="42">
+        <v>52</v>
+      </c>
+      <c r="B53" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="D52" s="42" t="s">
+      <c r="C53" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="42" t="s">
         <v>166</v>
       </c>
-      <c r="E52" s="42" t="s">
+      <c r="E53" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="F52" s="42" t="s">
+      <c r="F53" s="42" t="s">
         <v>222</v>
       </c>
     </row>
@@ -4774,7 +4809,7 @@
         <v>80</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F16" s="49"/>
     </row>
@@ -5103,7 +5138,7 @@
         <v>145</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E35" s="26"/>
       <c r="F35" s="40"/>
@@ -5137,7 +5172,7 @@
         <v>147</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E37" s="26"/>
       <c r="F37" s="40"/>
@@ -5153,7 +5188,7 @@
         <v>148</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E38" s="26"/>
       <c r="F38" s="40"/>
@@ -5169,7 +5204,7 @@
         <v>149</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E39" s="26"/>
       <c r="F39" s="40"/>
@@ -5203,7 +5238,7 @@
         <v>151</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E41" s="26"/>
       <c r="F41" s="40"/>
@@ -5237,7 +5272,7 @@
         <v>153</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E43" s="26"/>
       <c r="F43" s="40"/>
@@ -5253,7 +5288,7 @@
         <v>154</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E44" s="26"/>
       <c r="F44" s="40"/>
@@ -5269,7 +5304,7 @@
         <v>155</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E45" s="26"/>
       <c r="F45" s="40"/>
@@ -5285,7 +5320,7 @@
         <v>156</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E46" s="26"/>
       <c r="F46" s="40"/>
@@ -5301,7 +5336,7 @@
         <v>157</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E47" s="26"/>
       <c r="F47" s="40"/>
@@ -5317,7 +5352,7 @@
         <v>158</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E48" s="26"/>
       <c r="F48" s="40"/>
@@ -5333,7 +5368,7 @@
         <v>159</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E49" s="26"/>
       <c r="F49" s="40"/>
@@ -5597,7 +5632,7 @@
         <v>143</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E64" s="40"/>
       <c r="F64" s="40"/>
@@ -5649,7 +5684,7 @@
         <v>146</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E67" s="40"/>
       <c r="F67" s="40"/>
@@ -5665,7 +5700,7 @@
         <v>147</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E68" s="26"/>
       <c r="F68" s="40"/>
@@ -5681,7 +5716,7 @@
         <v>148</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E69" s="40"/>
       <c r="F69" s="40"/>
@@ -5697,7 +5732,7 @@
         <v>149</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E70" s="26"/>
       <c r="F70" s="40"/>
@@ -5981,7 +6016,7 @@
         <v>145</v>
       </c>
       <c r="D86" s="26" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E86" s="28"/>
       <c r="F86" s="53"/>
@@ -6099,7 +6134,7 @@
         <v>152</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E93" s="27"/>
       <c r="F93" s="54" t="s">
@@ -6135,7 +6170,7 @@
         <v>154</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E95" s="28"/>
       <c r="F95" s="53"/>
@@ -6322,10 +6357,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A106" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B106" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C106" s="33" t="s">
         <v>142</v>
@@ -6340,10 +6375,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A107" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B107" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C107" s="33" t="s">
         <v>143</v>
@@ -6358,10 +6393,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A108" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B108" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C108" s="33" t="s">
         <v>144</v>
@@ -6376,10 +6411,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A109" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B109" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C109" s="33" t="s">
         <v>145</v>
@@ -6394,10 +6429,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A110" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B110" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C110" s="33" t="s">
         <v>146</v>
@@ -6412,10 +6447,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A111" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B111" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C111" s="33" t="s">
         <v>147</v>
@@ -6430,10 +6465,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A112" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B112" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C112" s="33" t="s">
         <v>148</v>
@@ -6448,10 +6483,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A113" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B113" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C113" s="33" t="s">
         <v>149</v>
@@ -6466,10 +6501,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A114" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B114" s="32" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C114" s="33" t="s">
         <v>150</v>
@@ -6546,118 +6581,118 @@
         <v>126</v>
       </c>
       <c r="B2" s="45" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" s="45" t="s">
         <v>250</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="D2" s="45" t="s">
         <v>251</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="E2" s="45" t="s">
         <v>252</v>
-      </c>
-      <c r="E2" s="45" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="60" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B3" s="60" t="s">
         <v>169</v>
       </c>
       <c r="C3" s="60" t="s">
+        <v>254</v>
+      </c>
+      <c r="D3" s="60" t="s">
         <v>255</v>
       </c>
-      <c r="D3" s="60" t="s">
-        <v>256</v>
-      </c>
       <c r="E3" s="60" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="60" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B4" s="60" t="s">
         <v>166</v>
       </c>
       <c r="C4" s="60" t="s">
+        <v>271</v>
+      </c>
+      <c r="D4" s="60" t="s">
+        <v>256</v>
+      </c>
+      <c r="E4" s="60" t="s">
         <v>272</v>
-      </c>
-      <c r="D4" s="60" t="s">
-        <v>257</v>
-      </c>
-      <c r="E4" s="60" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="60" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B5" s="60" t="s">
         <v>238</v>
       </c>
       <c r="C5" s="60" t="s">
+        <v>258</v>
+      </c>
+      <c r="D5" s="60" t="s">
         <v>259</v>
       </c>
-      <c r="D5" s="60" t="s">
-        <v>260</v>
-      </c>
       <c r="E5" s="60" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="60" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B6" s="60" t="s">
         <v>172</v>
       </c>
       <c r="C6" s="60" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D6" s="60" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="60" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" s="60" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B7" s="60" t="s">
         <v>171</v>
       </c>
       <c r="C7" s="60" t="s">
+        <v>262</v>
+      </c>
+      <c r="D7" s="60" t="s">
         <v>263</v>
       </c>
-      <c r="D7" s="60" t="s">
-        <v>264</v>
-      </c>
       <c r="E7" s="61" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" s="60" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B8" s="60" t="s">
         <v>246</v>
       </c>
       <c r="C8" s="60" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D8" s="60" t="s">
         <v>223</v>
       </c>
       <c r="E8" s="60" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
@@ -6668,13 +6703,13 @@
         <v>173</v>
       </c>
       <c r="C9" s="60" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D9" s="60" t="s">
         <v>218</v>
       </c>
       <c r="E9" s="60" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
@@ -6685,13 +6720,13 @@
         <v>174</v>
       </c>
       <c r="C10" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="D10" s="60" t="s">
         <v>265</v>
       </c>
-      <c r="D10" s="60" t="s">
-        <v>266</v>
-      </c>
       <c r="E10" s="60" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
@@ -6702,261 +6737,261 @@
         <v>213</v>
       </c>
       <c r="C11" s="60" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D11" s="60" t="s">
         <v>214</v>
       </c>
       <c r="E11" s="60" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" s="60" t="s">
+        <v>267</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>395</v>
+      </c>
+      <c r="C12" s="60" t="s">
         <v>268</v>
       </c>
-      <c r="B12" s="60" t="s">
-        <v>397</v>
-      </c>
-      <c r="C12" s="60" t="s">
+      <c r="D12" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="D12" s="60" t="s">
-        <v>270</v>
-      </c>
       <c r="E12" s="60" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" s="45" t="s">
+        <v>282</v>
+      </c>
+      <c r="B15" s="45" t="s">
         <v>283</v>
-      </c>
-      <c r="B15" s="45" t="s">
-        <v>284</v>
       </c>
       <c r="C15" s="45" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="45" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" s="60" t="s">
+        <v>285</v>
+      </c>
+      <c r="B16" s="60" t="s">
+        <v>298</v>
+      </c>
+      <c r="C16" s="60" t="s">
         <v>286</v>
       </c>
-      <c r="B16" s="60" t="s">
+      <c r="D16" s="60" t="s">
         <v>299</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>287</v>
-      </c>
-      <c r="D16" s="60" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="60" t="s">
+        <v>287</v>
+      </c>
+      <c r="B17" s="60" t="s">
+        <v>300</v>
+      </c>
+      <c r="C17" s="60" t="s">
         <v>288</v>
       </c>
-      <c r="B17" s="60" t="s">
+      <c r="D17" s="60" t="s">
         <v>301</v>
-      </c>
-      <c r="C17" s="60" t="s">
-        <v>289</v>
-      </c>
-      <c r="D17" s="60" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="60" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B18" s="60" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C18" s="60" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D18" s="60" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="60" t="s">
+        <v>289</v>
+      </c>
+      <c r="B19" s="60" t="s">
         <v>290</v>
       </c>
-      <c r="B19" s="60" t="s">
+      <c r="C19" s="60" t="s">
         <v>291</v>
       </c>
-      <c r="C19" s="60" t="s">
-        <v>292</v>
-      </c>
       <c r="D19" s="60" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="60" t="s">
+        <v>292</v>
+      </c>
+      <c r="B20" s="60" t="s">
         <v>293</v>
       </c>
-      <c r="B20" s="60" t="s">
+      <c r="C20" s="60" t="s">
         <v>294</v>
-      </c>
-      <c r="C20" s="60" t="s">
-        <v>295</v>
       </c>
       <c r="D20" s="60"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="60" t="s">
+        <v>295</v>
+      </c>
+      <c r="B21" s="60" t="s">
         <v>296</v>
       </c>
-      <c r="B21" s="60" t="s">
+      <c r="C21" s="60" t="s">
         <v>297</v>
-      </c>
-      <c r="C21" s="60" t="s">
-        <v>298</v>
       </c>
       <c r="D21" s="60"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" s="60" t="s">
+        <v>303</v>
+      </c>
+      <c r="B22" s="60" t="s">
         <v>304</v>
       </c>
-      <c r="B22" s="60" t="s">
+      <c r="C22" s="60" t="s">
         <v>305</v>
       </c>
-      <c r="C22" s="60" t="s">
-        <v>306</v>
-      </c>
       <c r="D22" s="60" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" s="60" t="s">
+        <v>306</v>
+      </c>
+      <c r="B23" s="60" t="s">
         <v>307</v>
       </c>
-      <c r="B23" s="60" t="s">
+      <c r="C23" s="60" t="s">
         <v>308</v>
       </c>
-      <c r="C23" s="60" t="s">
-        <v>309</v>
-      </c>
       <c r="D23" s="60" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" s="60" t="s">
+        <v>309</v>
+      </c>
+      <c r="B24" s="60" t="s">
         <v>310</v>
       </c>
-      <c r="B24" s="60" t="s">
+      <c r="C24" s="60" t="s">
         <v>311</v>
       </c>
-      <c r="C24" s="60" t="s">
-        <v>312</v>
-      </c>
       <c r="D24" s="60" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" s="60" t="s">
+        <v>319</v>
+      </c>
+      <c r="B25" s="60" t="s">
         <v>320</v>
       </c>
-      <c r="B25" s="60" t="s">
+      <c r="C25" s="60" t="s">
         <v>321</v>
       </c>
-      <c r="C25" s="60" t="s">
+      <c r="D25" s="60" t="s">
         <v>322</v>
-      </c>
-      <c r="D25" s="60" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" s="60" t="s">
+        <v>332</v>
+      </c>
+      <c r="B26" s="60" t="s">
+        <v>333</v>
+      </c>
+      <c r="C26" s="60" t="s">
         <v>334</v>
       </c>
-      <c r="B26" s="60" t="s">
+      <c r="D26" s="60" t="s">
         <v>335</v>
-      </c>
-      <c r="C26" s="60" t="s">
-        <v>336</v>
-      </c>
-      <c r="D26" s="60" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" s="60" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B27" s="60" t="s">
+        <v>336</v>
+      </c>
+      <c r="C27" s="60" t="s">
+        <v>337</v>
+      </c>
+      <c r="D27" s="60" t="s">
         <v>338</v>
-      </c>
-      <c r="C27" s="60" t="s">
-        <v>339</v>
-      </c>
-      <c r="D27" s="60" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" s="60" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B28" s="60" t="s">
+        <v>339</v>
+      </c>
+      <c r="C28" s="60" t="s">
+        <v>340</v>
+      </c>
+      <c r="D28" s="60" t="s">
         <v>341</v>
-      </c>
-      <c r="C28" s="60" t="s">
-        <v>342</v>
-      </c>
-      <c r="D28" s="60" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" s="60" t="s">
+        <v>342</v>
+      </c>
+      <c r="B29" s="60" t="s">
+        <v>343</v>
+      </c>
+      <c r="C29" s="60" t="s">
         <v>344</v>
       </c>
-      <c r="B29" s="60" t="s">
+      <c r="D29" s="60" t="s">
         <v>345</v>
-      </c>
-      <c r="C29" s="60" t="s">
-        <v>346</v>
-      </c>
-      <c r="D29" s="60" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -6984,22 +7019,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="62" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1" s="62" t="s">
+        <v>397</v>
+      </c>
+      <c r="C1" s="62" t="s">
         <v>398</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="D1" s="62" t="s">
         <v>399</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="E1" s="62" t="s">
         <v>400</v>
       </c>
-      <c r="D1" s="62" t="s">
+      <c r="F1" s="62" t="s">
         <v>401</v>
-      </c>
-      <c r="E1" s="62" t="s">
-        <v>402</v>
-      </c>
-      <c r="F1" s="62" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -7007,19 +7042,19 @@
         <v>90726181415</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C2" s="65">
         <v>1</v>
       </c>
       <c r="D2" s="63" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E2" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -7027,19 +7062,19 @@
         <v>90463359240</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C3" s="65">
         <v>1</v>
       </c>
       <c r="D3" s="63" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E3" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F3" s="66" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -7047,19 +7082,19 @@
         <v>86263737582</v>
       </c>
       <c r="B4" s="63" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C4" s="65">
         <v>1</v>
       </c>
       <c r="D4" s="63" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E4" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -7067,19 +7102,19 @@
         <v>90318747741</v>
       </c>
       <c r="B5" s="63" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C5" s="65">
         <v>1</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E5" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F5" s="66" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -7087,19 +7122,19 @@
         <v>80648858007</v>
       </c>
       <c r="B6" s="63" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C6" s="65">
         <v>2</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E6" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F6" s="66" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -7107,19 +7142,19 @@
         <v>93220547947</v>
       </c>
       <c r="B7" s="63" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C7" s="65">
         <v>1</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E7" s="66" t="s">
         <v>199</v>
       </c>
       <c r="F7" s="66" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -7127,19 +7162,19 @@
         <v>80648858026</v>
       </c>
       <c r="B8" s="63" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C8" s="65">
         <v>1</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E8" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F8" s="66" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
@@ -7147,19 +7182,19 @@
         <v>91021780775</v>
       </c>
       <c r="B9" s="63" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C9" s="65">
         <v>1</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E9" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F9" s="66" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
@@ -7167,19 +7202,19 @@
         <v>84634968862</v>
       </c>
       <c r="B10" s="63" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C10" s="65">
         <v>1</v>
       </c>
       <c r="D10" s="63" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E10" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F10" s="66" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
@@ -7187,19 +7222,19 @@
         <v>93672537464</v>
       </c>
       <c r="B11" s="63" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C11" s="65">
         <v>1</v>
       </c>
       <c r="D11" s="63" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E11" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F11" s="66" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
@@ -7207,19 +7242,19 @@
         <v>93179170670</v>
       </c>
       <c r="B12" s="63" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C12" s="65">
         <v>2</v>
       </c>
       <c r="D12" s="63" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E12" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F12" s="66" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
@@ -7227,19 +7262,19 @@
         <v>93179170628</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C13" s="65">
         <v>2</v>
       </c>
       <c r="D13" s="63" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E13" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
@@ -7247,19 +7282,19 @@
         <v>88176237136</v>
       </c>
       <c r="B14" s="63" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C14" s="65">
         <v>1</v>
       </c>
       <c r="D14" s="63" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E14" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F14" s="66" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
@@ -7267,19 +7302,19 @@
         <v>90318747755</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C15" s="65">
         <v>1</v>
       </c>
       <c r="D15" s="63" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E15" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F15" s="66" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
@@ -7287,19 +7322,19 @@
         <v>93672571449</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C16" s="65">
         <v>1</v>
       </c>
       <c r="D16" s="63" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E16" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F16" s="66" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -7307,19 +7342,19 @@
         <v>93220547933</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C17" s="65">
         <v>1</v>
       </c>
       <c r="D17" s="63" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E17" s="66" t="s">
         <v>199</v>
       </c>
       <c r="F17" s="66" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -7327,19 +7362,19 @@
         <v>90726181419</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C18" s="65">
         <v>1</v>
       </c>
       <c r="D18" s="63" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E18" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F18" s="66" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
@@ -7347,19 +7382,19 @@
         <v>87880167762</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C19" s="65">
         <v>1</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E19" s="66" t="s">
         <v>198</v>
       </c>
       <c r="F19" s="66" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -7367,19 +7402,19 @@
         <v>88186960178</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C20" s="65">
         <v>2</v>
       </c>
       <c r="D20" s="63" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E20" s="66" t="s">
         <v>197</v>
       </c>
       <c r="F20" s="66" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -7387,19 +7422,19 @@
         <v>88128325479</v>
       </c>
       <c r="B21" s="63" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C21" s="65">
         <v>1</v>
       </c>
       <c r="D21" s="63" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E21" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F21" s="66" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -7407,19 +7442,19 @@
         <v>82314858827</v>
       </c>
       <c r="B22" s="63" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C22" s="65">
         <v>1</v>
       </c>
       <c r="D22" s="63" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E22" s="66" t="s">
         <v>199</v>
       </c>
       <c r="F22" s="66" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -7427,19 +7462,19 @@
         <v>75338048760</v>
       </c>
       <c r="B23" s="63" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C23" s="65">
         <v>1</v>
       </c>
       <c r="D23" s="63" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E23" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F23" s="66" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
@@ -7447,19 +7482,19 @@
         <v>88176237168</v>
       </c>
       <c r="B24" s="63" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C24" s="65">
         <v>1</v>
       </c>
       <c r="D24" s="63" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E24" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F24" s="66" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
@@ -7467,19 +7502,19 @@
         <v>77218920858</v>
       </c>
       <c r="B25" s="63" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C25" s="65">
         <v>3</v>
       </c>
       <c r="D25" s="63" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E25" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F25" s="66" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -7487,19 +7522,19 @@
         <v>86263737587</v>
       </c>
       <c r="B26" s="63" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C26" s="65">
         <v>1</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E26" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F26" s="66" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
@@ -7507,19 +7542,19 @@
         <v>87992013846</v>
       </c>
       <c r="B27" s="63" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C27" s="65">
         <v>1</v>
       </c>
       <c r="D27" s="63" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E27" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F27" s="66" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -7527,19 +7562,19 @@
         <v>83700756628</v>
       </c>
       <c r="B28" s="63" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C28" s="65">
         <v>1</v>
       </c>
       <c r="D28" s="63" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E28" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F28" s="66" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -7547,19 +7582,19 @@
         <v>73671510910</v>
       </c>
       <c r="B29" s="63" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C29" s="65">
         <v>2</v>
       </c>
       <c r="D29" s="63" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E29" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F29" s="66" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -7567,22 +7602,22 @@
         <v>87418768783</v>
       </c>
       <c r="B30" s="63" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C30" s="65">
         <v>1</v>
       </c>
       <c r="D30" s="63" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E30" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G30" s="63" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -7590,39 +7625,39 @@
         <v>74117666924</v>
       </c>
       <c r="B31" s="63" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C31" s="65">
         <v>1</v>
       </c>
       <c r="D31" s="63" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E31" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F31" s="66" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="64" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B32" s="63" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C32" s="65">
         <v>1</v>
       </c>
       <c r="D32" s="63" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E32" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F32" s="66" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
@@ -7630,19 +7665,19 @@
         <v>73672215064</v>
       </c>
       <c r="B33" s="63" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C33" s="65">
         <v>1</v>
       </c>
       <c r="D33" s="63" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E33" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F33" s="66" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -7650,22 +7685,22 @@
         <v>88449262751</v>
       </c>
       <c r="B34" s="63" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C34" s="65">
         <v>1</v>
       </c>
       <c r="D34" s="63" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E34" s="66" t="s">
         <v>199</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G34" s="63" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -7840,7 +7875,7 @@
         <v>73</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F9" s="49"/>
     </row>
@@ -7858,7 +7893,7 @@
         <v>74</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F10" s="49"/>
     </row>
@@ -7908,7 +7943,7 @@
         <v>77</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F13" s="49"/>
     </row>
@@ -7958,7 +7993,7 @@
         <v>80</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F16" s="49"/>
     </row>
@@ -8130,7 +8165,7 @@
         <v>88</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F26" s="49"/>
     </row>
@@ -8148,7 +8183,7 @@
         <v>89</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F27" s="49"/>
     </row>
@@ -8166,7 +8201,7 @@
         <v>90</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F28" s="49"/>
     </row>
@@ -8184,7 +8219,7 @@
         <v>91</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F29" s="49"/>
     </row>
@@ -8236,7 +8271,7 @@
         <v>94</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F32" s="49"/>
     </row>
@@ -8272,7 +8307,7 @@
         <v>96</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F34" s="49"/>
     </row>
@@ -8287,7 +8322,7 @@
         <v>145</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E35" s="26"/>
       <c r="F35" s="40"/>
@@ -8306,7 +8341,7 @@
         <v>97</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F36" s="49"/>
     </row>
@@ -8321,7 +8356,7 @@
         <v>147</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E37" s="26"/>
       <c r="F37" s="40"/>
@@ -8337,7 +8372,7 @@
         <v>148</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E38" s="26"/>
       <c r="F38" s="40"/>
@@ -8353,7 +8388,7 @@
         <v>149</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E39" s="26"/>
       <c r="F39" s="40"/>
@@ -8372,7 +8407,7 @@
         <v>98</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F40" s="49"/>
     </row>
@@ -8387,7 +8422,7 @@
         <v>151</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E41" s="26"/>
       <c r="F41" s="40"/>
@@ -8421,7 +8456,7 @@
         <v>153</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E43" s="26"/>
       <c r="F43" s="40"/>
@@ -8437,7 +8472,7 @@
         <v>154</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E44" s="26"/>
       <c r="F44" s="40"/>
@@ -8453,7 +8488,7 @@
         <v>155</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E45" s="26"/>
       <c r="F45" s="40"/>
@@ -8469,7 +8504,7 @@
         <v>156</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E46" s="26"/>
       <c r="F46" s="40"/>
@@ -8485,7 +8520,7 @@
         <v>157</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E47" s="26"/>
       <c r="F47" s="40"/>
@@ -8501,7 +8536,7 @@
         <v>158</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E48" s="26"/>
       <c r="F48" s="40"/>
@@ -8517,7 +8552,7 @@
         <v>159</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E49" s="26"/>
       <c r="F49" s="40"/>
@@ -8660,7 +8695,7 @@
         <v>108</v>
       </c>
       <c r="E57" s="36" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F57" s="49"/>
     </row>
@@ -8678,7 +8713,7 @@
         <v>109</v>
       </c>
       <c r="E58" s="36" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F58" s="49"/>
     </row>
@@ -8696,7 +8731,7 @@
         <v>110</v>
       </c>
       <c r="E59" s="36" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F59" s="49"/>
     </row>
@@ -8714,7 +8749,7 @@
         <v>111</v>
       </c>
       <c r="E60" s="36" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F60" s="49"/>
     </row>
@@ -8766,7 +8801,7 @@
         <v>133</v>
       </c>
       <c r="E63" s="36" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F63" s="49"/>
     </row>
@@ -8781,7 +8816,7 @@
         <v>143</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E64" s="40"/>
       <c r="F64" s="40"/>
@@ -8800,7 +8835,7 @@
         <v>134</v>
       </c>
       <c r="E65" s="36" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F65" s="49"/>
     </row>
@@ -8818,7 +8853,7 @@
         <v>135</v>
       </c>
       <c r="E66" s="36" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F66" s="49"/>
     </row>
@@ -8833,7 +8868,7 @@
         <v>146</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E67" s="40"/>
       <c r="F67" s="40"/>
@@ -8849,7 +8884,7 @@
         <v>147</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E68" s="26"/>
       <c r="F68" s="40"/>
@@ -8865,7 +8900,7 @@
         <v>148</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E69" s="40"/>
       <c r="F69" s="40"/>
@@ -8881,7 +8916,7 @@
         <v>149</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E70" s="26"/>
       <c r="F70" s="40"/>
@@ -8900,7 +8935,7 @@
         <v>136</v>
       </c>
       <c r="E71" s="36" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F71" s="49"/>
     </row>
@@ -8990,7 +9025,7 @@
         <v>89</v>
       </c>
       <c r="E76" s="36" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F76" s="49"/>
     </row>
@@ -9008,7 +9043,7 @@
         <v>91</v>
       </c>
       <c r="E77" s="36" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F77" s="49"/>
     </row>
@@ -9042,7 +9077,7 @@
         <v>77</v>
       </c>
       <c r="E79" s="36" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F79" s="49"/>
     </row>
@@ -9078,7 +9113,7 @@
         <v>80</v>
       </c>
       <c r="E81" s="36" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F81" s="49"/>
     </row>
@@ -9114,7 +9149,7 @@
         <v>117</v>
       </c>
       <c r="E83" s="36" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F83" s="49"/>
     </row>
@@ -9132,7 +9167,7 @@
         <v>118</v>
       </c>
       <c r="E84" s="36" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F84" s="49"/>
     </row>
@@ -9165,7 +9200,7 @@
         <v>145</v>
       </c>
       <c r="D86" s="26" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E86" s="28"/>
       <c r="F86" s="53"/>
@@ -9184,7 +9219,7 @@
         <v>2</v>
       </c>
       <c r="E87" s="36" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F87" s="49"/>
     </row>
@@ -9218,7 +9253,7 @@
         <v>4</v>
       </c>
       <c r="E89" s="36" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F89" s="49"/>
     </row>
@@ -9283,7 +9318,7 @@
         <v>152</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E93" s="27"/>
       <c r="F93" s="54" t="s">
@@ -9319,7 +9354,7 @@
         <v>154</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E95" s="28"/>
       <c r="F95" s="53"/>
@@ -9356,7 +9391,7 @@
         <v>125</v>
       </c>
       <c r="E97" s="36" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F97" s="49"/>
     </row>
@@ -9374,7 +9409,7 @@
         <v>2</v>
       </c>
       <c r="E98" s="36" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F98" s="49"/>
     </row>
@@ -9392,7 +9427,7 @@
         <v>4</v>
       </c>
       <c r="E99" s="36" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F99" s="49"/>
     </row>
@@ -9410,7 +9445,7 @@
         <v>126</v>
       </c>
       <c r="E100" s="36" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F100" s="49"/>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulmann\Documents\Business\OwnBusiness\○네이버스마트스토어 RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F0676F-6AE0-43F4-8844-C6F1BBD20779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964C8247-9057-4E93-99CA-149871855C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProductRoute" sheetId="3" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="524">
   <si>
     <t>보내는사람</t>
   </si>
@@ -1143,6 +1143,10 @@
   </si>
   <si>
     <t>REPLACE_REGEX_SUB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무라벨 /// 쭈구리</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2108,15 +2112,43 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">주꾸미 선택: , (알배기 30~40%/국산), (알없음/중국산), (알배기 40~50%/중국산), 새조개 선택: ,꽃게 선택: , 꼬막 선택: </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>무라벨 /// 쭈구리, 활주꾸미 /// 연안 활 쭈꾸미, 급냉 주꾸미 /// 봄 제철 쭈꾸미, 알주꾸미 /// 탱탱 알주꾸미, 활 암꽃게 소 /// 연안 활 소암게, 활 암꽃게 대 /// 연안 활 대암게, 새꼬막 소 /// 새꼬막 소짜, 새꼬막 중 /// 새꼬막 중짜, 새꼬막 대 /// 새꼬막 대짜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>갑오징어, 생물오징어, 생물 호래기, 급냉 호래기, 생물 한치, 실속형 5미, 실속형 10미, 주꾸미, 새조개, 꽃게, 새꼬막</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활주꾸미 /// 연안 활 쭈꾸미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급냉 주꾸미 /// 봄 제철 쭈꾸미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알주꾸미 /// 탱탱 알주꾸미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활 암꽃게 소 /// 연안 활 소암게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활 암꽃게 대 /// 연안 활 대암게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새꼬막 소 /// 새꼬막 소짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새꼬막 중 /// 새꼬막 중짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새꼬막 대 /// 새꼬막 대짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주꾸미 선택: , (알배기 30~40%/국산), (알없음/중국산), (알배기 40~50%/중국산), 새조개 선택: ,꽃게 선택: , 꼬막 선택: , (4~6미내외), (2~4미내외)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3411,7 +3443,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C8" s="57" t="s">
         <v>114</v>
@@ -3455,10 +3487,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="57" t="s">
+        <v>511</v>
+      </c>
+      <c r="C12" s="57" t="s">
         <v>510</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
@@ -3481,7 +3513,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE8C8B0-87AB-4B5A-85D1-21EF511A776A}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultColWidth="11.4140625" defaultRowHeight="14.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="2" bestFit="1" customWidth="1"/>
@@ -3527,7 +3559,7 @@
         <v>166</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F2" s="42" t="s">
         <v>202</v>
@@ -3541,13 +3573,13 @@
         <v>196</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D3" s="42" t="s">
         <v>166</v>
       </c>
       <c r="E3" s="42" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F3" s="42" t="s">
         <v>202</v>
@@ -3561,13 +3593,13 @@
         <v>196</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D4" s="42" t="s">
         <v>166</v>
       </c>
       <c r="E4" s="42" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F4" s="42" t="s">
         <v>202</v>
@@ -3581,7 +3613,7 @@
         <v>196</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D5" s="42" t="s">
         <v>246</v>
@@ -3636,7 +3668,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C8" s="42" t="s">
         <v>7</v>
@@ -3645,7 +3677,7 @@
         <v>169</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F8" s="42" t="s">
         <v>170</v>
@@ -3665,13 +3697,13 @@
         <v>169</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="F9" s="42" t="s">
         <v>170</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
@@ -3699,16 +3731,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="42" t="s">
+        <v>364</v>
+      </c>
+      <c r="C11" s="42" t="s">
         <v>363</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>362</v>
       </c>
       <c r="D11" s="42" t="s">
         <v>166</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F11" s="42"/>
     </row>
@@ -3746,10 +3778,10 @@
         <v>330</v>
       </c>
       <c r="E13" s="43" t="s">
+        <v>349</v>
+      </c>
+      <c r="F13" s="42" t="s">
         <v>348</v>
-      </c>
-      <c r="F13" s="42" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
@@ -3760,13 +3792,13 @@
         <v>7</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D14" s="42" t="s">
         <v>169</v>
       </c>
       <c r="E14" s="43" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F14" s="42"/>
     </row>
@@ -3778,7 +3810,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D15" s="42" t="s">
         <v>166</v>
@@ -3796,7 +3828,7 @@
         <v>7</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D16" s="42" t="s">
         <v>215</v>
@@ -3820,10 +3852,10 @@
         <v>238</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>514</v>
+        <v>331</v>
       </c>
       <c r="F17" s="42" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
@@ -3834,13 +3866,13 @@
         <v>196</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D18" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F18" s="42"/>
     </row>
@@ -3858,7 +3890,7 @@
         <v>238</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F19" s="42"/>
     </row>
@@ -3870,13 +3902,13 @@
         <v>7</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D20" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F20" s="42"/>
     </row>
@@ -3885,20 +3917,18 @@
         <v>20</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>509</v>
+        <v>7</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>204</v>
+        <v>7</v>
       </c>
       <c r="D21" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="E21" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="59" t="s">
-        <v>207</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>515</v>
+      </c>
+      <c r="F21" s="42"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="42">
@@ -3908,17 +3938,15 @@
         <v>7</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>372</v>
+        <v>7</v>
       </c>
       <c r="D22" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="E22" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="42" t="s">
-        <v>243</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>516</v>
+      </c>
+      <c r="F22" s="42"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="42">
@@ -3928,17 +3956,15 @@
         <v>7</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>373</v>
+        <v>7</v>
       </c>
       <c r="D23" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="E23" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="42" t="s">
-        <v>243</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>517</v>
+      </c>
+      <c r="F23" s="42"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="42">
@@ -3948,17 +3974,15 @@
         <v>7</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>367</v>
+        <v>7</v>
       </c>
       <c r="D24" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="E24" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="42" t="s">
-        <v>243</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>518</v>
+      </c>
+      <c r="F24" s="42"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="42">
@@ -3968,17 +3992,15 @@
         <v>7</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>248</v>
+        <v>7</v>
       </c>
       <c r="D25" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="42" t="s">
-        <v>243</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>519</v>
+      </c>
+      <c r="F25" s="42"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="42">
@@ -3988,13 +4010,13 @@
         <v>7</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>377</v>
+        <v>7</v>
       </c>
       <c r="D26" s="42" t="s">
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>375</v>
+        <v>520</v>
       </c>
       <c r="F26" s="42"/>
     </row>
@@ -4006,13 +4028,13 @@
         <v>7</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>379</v>
+        <v>7</v>
       </c>
       <c r="D27" s="42" t="s">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>380</v>
+        <v>521</v>
       </c>
       <c r="F27" s="42"/>
     </row>
@@ -4024,13 +4046,13 @@
         <v>7</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>379</v>
+        <v>7</v>
       </c>
       <c r="D28" s="42" t="s">
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>375</v>
+        <v>522</v>
       </c>
       <c r="F28" s="42"/>
     </row>
@@ -4039,19 +4061,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="42" t="s">
-        <v>7</v>
+        <v>510</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>376</v>
+        <v>204</v>
       </c>
       <c r="D29" s="42" t="s">
         <v>171</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>378</v>
-      </c>
-      <c r="F29" s="42" t="s">
-        <v>243</v>
+        <v>9</v>
+      </c>
+      <c r="F29" s="59" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
@@ -4059,10 +4081,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="42" t="s">
-        <v>196</v>
+        <v>7</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="D30" s="42" t="s">
         <v>171</v>
@@ -4070,25 +4092,29 @@
       <c r="E30" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="42"/>
+      <c r="F30" s="42" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="42">
         <v>30</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>196</v>
+        <v>7</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="D31" s="42" t="s">
-        <v>215</v>
+        <v>171</v>
       </c>
       <c r="E31" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="F31" s="42"/>
+        <v>9</v>
+      </c>
+      <c r="F31" s="42" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="42">
@@ -4098,15 +4124,17 @@
         <v>7</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D32" s="42" t="s">
-        <v>215</v>
+        <v>171</v>
       </c>
       <c r="E32" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="F32" s="42"/>
+        <v>9</v>
+      </c>
+      <c r="F32" s="42" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" s="42">
@@ -4116,16 +4144,16 @@
         <v>7</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>324</v>
+        <v>248</v>
       </c>
       <c r="D33" s="42" t="s">
-        <v>215</v>
+        <v>171</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>217</v>
-      </c>
-      <c r="F33" s="59" t="s">
-        <v>325</v>
+        <v>9</v>
+      </c>
+      <c r="F33" s="42" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
@@ -4136,17 +4164,15 @@
         <v>7</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>7</v>
+        <v>378</v>
       </c>
       <c r="D34" s="42" t="s">
-        <v>172</v>
-      </c>
-      <c r="E34" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="42" t="s">
-        <v>224</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="E34" s="43" t="s">
+        <v>376</v>
+      </c>
+      <c r="F34" s="42"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="42">
@@ -4156,13 +4182,13 @@
         <v>7</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>215</v>
-      </c>
-      <c r="E35" s="42" t="s">
-        <v>326</v>
+        <v>166</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>381</v>
       </c>
       <c r="F35" s="42"/>
     </row>
@@ -4174,17 +4200,15 @@
         <v>7</v>
       </c>
       <c r="C36" s="42" t="s">
-        <v>7</v>
+        <v>380</v>
       </c>
       <c r="D36" s="42" t="s">
-        <v>172</v>
-      </c>
-      <c r="E36" s="42" t="s">
-        <v>225</v>
-      </c>
-      <c r="F36" s="42" t="s">
-        <v>226</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>376</v>
+      </c>
+      <c r="F36" s="42"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="42">
@@ -4194,16 +4218,16 @@
         <v>7</v>
       </c>
       <c r="C37" s="42" t="s">
-        <v>7</v>
+        <v>377</v>
       </c>
       <c r="D37" s="42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E37" s="42" t="s">
-        <v>227</v>
+        <v>379</v>
       </c>
       <c r="F37" s="42" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.4">
@@ -4211,40 +4235,36 @@
         <v>37</v>
       </c>
       <c r="B38" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C38" s="42" t="s">
-        <v>7</v>
+        <v>357</v>
       </c>
       <c r="D38" s="42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="F38" s="42" t="s">
-        <v>245</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F38" s="42"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="42">
         <v>38</v>
       </c>
       <c r="B39" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>7</v>
+        <v>355</v>
       </c>
       <c r="D39" s="42" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>357</v>
-      </c>
-      <c r="F39" s="42" t="s">
-        <v>358</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="F39" s="42"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="42">
@@ -4254,17 +4274,15 @@
         <v>7</v>
       </c>
       <c r="C40" s="42" t="s">
-        <v>7</v>
+        <v>363</v>
       </c>
       <c r="D40" s="42" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="E40" s="42" t="s">
-        <v>229</v>
-      </c>
-      <c r="F40" s="42" t="s">
-        <v>230</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="F40" s="42"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" s="42">
@@ -4274,16 +4292,16 @@
         <v>7</v>
       </c>
       <c r="C41" s="42" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="D41" s="42" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="E41" s="42" t="s">
-        <v>231</v>
-      </c>
-      <c r="F41" s="42" t="s">
-        <v>232</v>
+        <v>217</v>
+      </c>
+      <c r="F41" s="59" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.4">
@@ -4297,13 +4315,13 @@
         <v>7</v>
       </c>
       <c r="D42" s="42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E42" s="42" t="s">
-        <v>233</v>
+        <v>8</v>
       </c>
       <c r="F42" s="42" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.4">
@@ -4314,17 +4332,15 @@
         <v>7</v>
       </c>
       <c r="C43" s="42" t="s">
-        <v>7</v>
+        <v>394</v>
       </c>
       <c r="D43" s="42" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>240</v>
-      </c>
-      <c r="F43" s="42" t="s">
-        <v>241</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="F43" s="42"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" s="42">
@@ -4334,73 +4350,77 @@
         <v>7</v>
       </c>
       <c r="C44" s="42" t="s">
-        <v>359</v>
+        <v>7</v>
       </c>
       <c r="D44" s="42" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="E44" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="F44" s="42"/>
-    </row>
-    <row r="45" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+        <v>225</v>
+      </c>
+      <c r="F44" s="42" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" s="42">
         <v>44</v>
       </c>
-      <c r="B45" s="57" t="s">
-        <v>124</v>
+      <c r="B45" s="42" t="s">
+        <v>7</v>
       </c>
       <c r="C45" s="42" t="s">
-        <v>203</v>
+        <v>7</v>
       </c>
       <c r="D45" s="42" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="E45" s="42" t="s">
-        <v>9</v>
+        <v>227</v>
       </c>
       <c r="F45" s="42" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46" s="42">
         <v>45</v>
       </c>
-      <c r="B46" s="57" t="s">
-        <v>93</v>
+      <c r="B46" s="42" t="s">
+        <v>7</v>
       </c>
       <c r="C46" s="42" t="s">
-        <v>210</v>
+        <v>7</v>
       </c>
       <c r="D46" s="42" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="E46" s="42" t="s">
-        <v>9</v>
+        <v>244</v>
       </c>
       <c r="F46" s="42" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" s="42">
         <v>46</v>
       </c>
-      <c r="B47" s="57" t="s">
-        <v>124</v>
+      <c r="B47" s="42" t="s">
+        <v>7</v>
       </c>
       <c r="C47" s="42" t="s">
-        <v>203</v>
+        <v>7</v>
       </c>
       <c r="D47" s="42" t="s">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="E47" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="F47" s="42"/>
+        <v>358</v>
+      </c>
+      <c r="F47" s="42" t="s">
+        <v>359</v>
+      </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" s="42">
@@ -4410,16 +4430,16 @@
         <v>7</v>
       </c>
       <c r="C48" s="42" t="s">
-        <v>219</v>
+        <v>7</v>
       </c>
       <c r="D48" s="42" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="E48" s="42" t="s">
-        <v>326</v>
+        <v>229</v>
       </c>
       <c r="F48" s="42" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.4">
@@ -4430,16 +4450,16 @@
         <v>7</v>
       </c>
       <c r="C49" s="42" t="s">
-        <v>242</v>
+        <v>7</v>
       </c>
       <c r="D49" s="42" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="E49" s="42" t="s">
-        <v>326</v>
+        <v>231</v>
       </c>
       <c r="F49" s="42" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.4">
@@ -4450,16 +4470,16 @@
         <v>7</v>
       </c>
       <c r="C50" s="42" t="s">
-        <v>371</v>
+        <v>7</v>
       </c>
       <c r="D50" s="42" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="E50" s="42" t="s">
-        <v>326</v>
+        <v>233</v>
       </c>
       <c r="F50" s="42" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.4">
@@ -4470,15 +4490,17 @@
         <v>7</v>
       </c>
       <c r="C51" s="42" t="s">
-        <v>394</v>
+        <v>7</v>
       </c>
       <c r="D51" s="42" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="E51" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="F51" s="42"/>
+        <v>240</v>
+      </c>
+      <c r="F51" s="42" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" s="42">
@@ -4488,7 +4510,7 @@
         <v>7</v>
       </c>
       <c r="C52" s="42" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="D52" s="42" t="s">
         <v>215</v>
@@ -4498,23 +4520,177 @@
       </c>
       <c r="F52" s="42"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:6" ht="16" x14ac:dyDescent="0.45">
       <c r="A53" s="42">
         <v>52</v>
       </c>
-      <c r="B53" s="42" t="s">
+      <c r="B53" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="C53" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="D53" s="42" t="s">
+        <v>208</v>
+      </c>
+      <c r="E53" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" s="42" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+      <c r="A54" s="42">
+        <v>53</v>
+      </c>
+      <c r="B54" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="C54" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="D54" s="42" t="s">
+        <v>211</v>
+      </c>
+      <c r="E54" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" s="42" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+      <c r="A55" s="42">
+        <v>54</v>
+      </c>
+      <c r="B55" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="C55" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="D55" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="E55" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="F55" s="42"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A56" s="42">
+        <v>55</v>
+      </c>
+      <c r="B56" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="42" t="s">
+      <c r="C56" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="D56" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="E56" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="F56" s="42" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A57" s="42">
+        <v>56</v>
+      </c>
+      <c r="B57" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="D53" s="42" t="s">
+      <c r="C57" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="D57" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="E57" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="F57" s="42" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A58" s="42">
+        <v>57</v>
+      </c>
+      <c r="B58" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="42" t="s">
+        <v>372</v>
+      </c>
+      <c r="D58" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="E58" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="F58" s="42" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A59" s="42">
+        <v>58</v>
+      </c>
+      <c r="B59" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="42" t="s">
+        <v>395</v>
+      </c>
+      <c r="D59" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="E59" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="F59" s="42"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A60" s="42">
+        <v>59</v>
+      </c>
+      <c r="B60" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="D60" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="E60" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="F60" s="42"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A61" s="42">
+        <v>60</v>
+      </c>
+      <c r="B61" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="42" t="s">
         <v>166</v>
       </c>
-      <c r="E53" s="42" t="s">
+      <c r="E61" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="F53" s="42" t="s">
+      <c r="F61" s="42" t="s">
         <v>222</v>
       </c>
     </row>
@@ -4809,7 +4985,7 @@
         <v>80</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F16" s="49"/>
     </row>
@@ -5138,7 +5314,7 @@
         <v>145</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E35" s="26"/>
       <c r="F35" s="40"/>
@@ -5172,7 +5348,7 @@
         <v>147</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E37" s="26"/>
       <c r="F37" s="40"/>
@@ -5188,7 +5364,7 @@
         <v>148</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E38" s="26"/>
       <c r="F38" s="40"/>
@@ -5204,7 +5380,7 @@
         <v>149</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E39" s="26"/>
       <c r="F39" s="40"/>
@@ -5238,7 +5414,7 @@
         <v>151</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E41" s="26"/>
       <c r="F41" s="40"/>
@@ -5272,7 +5448,7 @@
         <v>153</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E43" s="26"/>
       <c r="F43" s="40"/>
@@ -5288,7 +5464,7 @@
         <v>154</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E44" s="26"/>
       <c r="F44" s="40"/>
@@ -5304,7 +5480,7 @@
         <v>155</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E45" s="26"/>
       <c r="F45" s="40"/>
@@ -5320,7 +5496,7 @@
         <v>156</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E46" s="26"/>
       <c r="F46" s="40"/>
@@ -5336,7 +5512,7 @@
         <v>157</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E47" s="26"/>
       <c r="F47" s="40"/>
@@ -5352,7 +5528,7 @@
         <v>158</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E48" s="26"/>
       <c r="F48" s="40"/>
@@ -5368,7 +5544,7 @@
         <v>159</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E49" s="26"/>
       <c r="F49" s="40"/>
@@ -5632,7 +5808,7 @@
         <v>143</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E64" s="40"/>
       <c r="F64" s="40"/>
@@ -5684,7 +5860,7 @@
         <v>146</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E67" s="40"/>
       <c r="F67" s="40"/>
@@ -5700,7 +5876,7 @@
         <v>147</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E68" s="26"/>
       <c r="F68" s="40"/>
@@ -5716,7 +5892,7 @@
         <v>148</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E69" s="40"/>
       <c r="F69" s="40"/>
@@ -5732,7 +5908,7 @@
         <v>149</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E70" s="26"/>
       <c r="F70" s="40"/>
@@ -6016,7 +6192,7 @@
         <v>145</v>
       </c>
       <c r="D86" s="26" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E86" s="28"/>
       <c r="F86" s="53"/>
@@ -6134,7 +6310,7 @@
         <v>152</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E93" s="27"/>
       <c r="F93" s="54" t="s">
@@ -6170,7 +6346,7 @@
         <v>154</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E95" s="28"/>
       <c r="F95" s="53"/>
@@ -6357,10 +6533,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A106" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B106" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C106" s="33" t="s">
         <v>142</v>
@@ -6375,10 +6551,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A107" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B107" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C107" s="33" t="s">
         <v>143</v>
@@ -6393,10 +6569,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A108" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B108" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C108" s="33" t="s">
         <v>144</v>
@@ -6411,10 +6587,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A109" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B109" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C109" s="33" t="s">
         <v>145</v>
@@ -6429,10 +6605,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A110" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B110" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C110" s="33" t="s">
         <v>146</v>
@@ -6447,10 +6623,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A111" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B111" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C111" s="33" t="s">
         <v>147</v>
@@ -6465,10 +6641,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A112" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B112" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C112" s="33" t="s">
         <v>148</v>
@@ -6483,10 +6659,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A113" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B113" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C113" s="33" t="s">
         <v>149</v>
@@ -6501,10 +6677,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A114" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B114" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C114" s="33" t="s">
         <v>150</v>
@@ -6709,7 +6885,7 @@
         <v>218</v>
       </c>
       <c r="E9" s="60" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
@@ -6751,7 +6927,7 @@
         <v>267</v>
       </c>
       <c r="B12" s="60" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C12" s="60" t="s">
         <v>268</v>
@@ -6807,7 +6983,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="60" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B18" s="60" t="s">
         <v>300</v>
@@ -6816,7 +6992,7 @@
         <v>288</v>
       </c>
       <c r="D18" s="60" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
@@ -6915,16 +7091,16 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" s="60" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B26" s="60" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C26" s="60" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D26" s="60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
@@ -6932,13 +7108,13 @@
         <v>289</v>
       </c>
       <c r="B27" s="60" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C27" s="60" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D27" s="60" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
@@ -6946,27 +7122,27 @@
         <v>306</v>
       </c>
       <c r="B28" s="60" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D28" s="60" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" s="60" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B29" s="60" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C29" s="60" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D29" s="60" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
@@ -7019,22 +7195,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="62" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B1" s="62" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C1" s="62" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D1" s="62" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E1" s="62" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F1" s="62" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -7042,19 +7218,19 @@
         <v>90726181415</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C2" s="65">
         <v>1</v>
       </c>
       <c r="D2" s="63" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E2" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -7062,19 +7238,19 @@
         <v>90463359240</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C3" s="65">
         <v>1</v>
       </c>
       <c r="D3" s="63" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E3" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F3" s="66" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -7082,19 +7258,19 @@
         <v>86263737582</v>
       </c>
       <c r="B4" s="63" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C4" s="65">
         <v>1</v>
       </c>
       <c r="D4" s="63" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E4" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -7102,19 +7278,19 @@
         <v>90318747741</v>
       </c>
       <c r="B5" s="63" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C5" s="65">
         <v>1</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E5" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F5" s="66" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -7122,19 +7298,19 @@
         <v>80648858007</v>
       </c>
       <c r="B6" s="63" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C6" s="65">
         <v>2</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E6" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F6" s="66" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -7142,19 +7318,19 @@
         <v>93220547947</v>
       </c>
       <c r="B7" s="63" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C7" s="65">
         <v>1</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E7" s="66" t="s">
         <v>199</v>
       </c>
       <c r="F7" s="66" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -7162,19 +7338,19 @@
         <v>80648858026</v>
       </c>
       <c r="B8" s="63" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C8" s="65">
         <v>1</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E8" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F8" s="66" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
@@ -7182,19 +7358,19 @@
         <v>91021780775</v>
       </c>
       <c r="B9" s="63" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C9" s="65">
         <v>1</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E9" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F9" s="66" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
@@ -7202,19 +7378,19 @@
         <v>84634968862</v>
       </c>
       <c r="B10" s="63" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C10" s="65">
         <v>1</v>
       </c>
       <c r="D10" s="63" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E10" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F10" s="66" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
@@ -7222,19 +7398,19 @@
         <v>93672537464</v>
       </c>
       <c r="B11" s="63" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C11" s="65">
         <v>1</v>
       </c>
       <c r="D11" s="63" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E11" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F11" s="66" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
@@ -7242,19 +7418,19 @@
         <v>93179170670</v>
       </c>
       <c r="B12" s="63" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C12" s="65">
         <v>2</v>
       </c>
       <c r="D12" s="63" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E12" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F12" s="66" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
@@ -7262,19 +7438,19 @@
         <v>93179170628</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C13" s="65">
         <v>2</v>
       </c>
       <c r="D13" s="63" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E13" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
@@ -7282,19 +7458,19 @@
         <v>88176237136</v>
       </c>
       <c r="B14" s="63" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C14" s="65">
         <v>1</v>
       </c>
       <c r="D14" s="63" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E14" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F14" s="66" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
@@ -7302,19 +7478,19 @@
         <v>90318747755</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C15" s="65">
         <v>1</v>
       </c>
       <c r="D15" s="63" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E15" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F15" s="66" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
@@ -7322,19 +7498,19 @@
         <v>93672571449</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C16" s="65">
         <v>1</v>
       </c>
       <c r="D16" s="63" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E16" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F16" s="66" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -7342,19 +7518,19 @@
         <v>93220547933</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C17" s="65">
         <v>1</v>
       </c>
       <c r="D17" s="63" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E17" s="66" t="s">
         <v>199</v>
       </c>
       <c r="F17" s="66" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -7362,19 +7538,19 @@
         <v>90726181419</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C18" s="65">
         <v>1</v>
       </c>
       <c r="D18" s="63" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E18" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F18" s="66" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
@@ -7382,19 +7558,19 @@
         <v>87880167762</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C19" s="65">
         <v>1</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E19" s="66" t="s">
         <v>198</v>
       </c>
       <c r="F19" s="66" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -7402,19 +7578,19 @@
         <v>88186960178</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C20" s="65">
         <v>2</v>
       </c>
       <c r="D20" s="63" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E20" s="66" t="s">
         <v>197</v>
       </c>
       <c r="F20" s="66" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -7422,19 +7598,19 @@
         <v>88128325479</v>
       </c>
       <c r="B21" s="63" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C21" s="65">
         <v>1</v>
       </c>
       <c r="D21" s="63" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E21" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F21" s="66" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -7442,19 +7618,19 @@
         <v>82314858827</v>
       </c>
       <c r="B22" s="63" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C22" s="65">
         <v>1</v>
       </c>
       <c r="D22" s="63" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E22" s="66" t="s">
         <v>199</v>
       </c>
       <c r="F22" s="66" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -7462,19 +7638,19 @@
         <v>75338048760</v>
       </c>
       <c r="B23" s="63" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C23" s="65">
         <v>1</v>
       </c>
       <c r="D23" s="63" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E23" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F23" s="66" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
@@ -7482,19 +7658,19 @@
         <v>88176237168</v>
       </c>
       <c r="B24" s="63" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C24" s="65">
         <v>1</v>
       </c>
       <c r="D24" s="63" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E24" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F24" s="66" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
@@ -7502,19 +7678,19 @@
         <v>77218920858</v>
       </c>
       <c r="B25" s="63" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C25" s="65">
         <v>3</v>
       </c>
       <c r="D25" s="63" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E25" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F25" s="66" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -7522,19 +7698,19 @@
         <v>86263737587</v>
       </c>
       <c r="B26" s="63" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C26" s="65">
         <v>1</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E26" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F26" s="66" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
@@ -7542,19 +7718,19 @@
         <v>87992013846</v>
       </c>
       <c r="B27" s="63" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C27" s="65">
         <v>1</v>
       </c>
       <c r="D27" s="63" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E27" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F27" s="66" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -7562,19 +7738,19 @@
         <v>83700756628</v>
       </c>
       <c r="B28" s="63" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C28" s="65">
         <v>1</v>
       </c>
       <c r="D28" s="63" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E28" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F28" s="66" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -7582,19 +7758,19 @@
         <v>73671510910</v>
       </c>
       <c r="B29" s="63" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C29" s="65">
         <v>2</v>
       </c>
       <c r="D29" s="63" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E29" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F29" s="66" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -7602,22 +7778,22 @@
         <v>87418768783</v>
       </c>
       <c r="B30" s="63" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C30" s="65">
         <v>1</v>
       </c>
       <c r="D30" s="63" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E30" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G30" s="63" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -7625,39 +7801,39 @@
         <v>74117666924</v>
       </c>
       <c r="B31" s="63" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C31" s="65">
         <v>1</v>
       </c>
       <c r="D31" s="63" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E31" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F31" s="66" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="64" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B32" s="63" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C32" s="65">
         <v>1</v>
       </c>
       <c r="D32" s="63" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E32" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F32" s="66" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
@@ -7665,19 +7841,19 @@
         <v>73672215064</v>
       </c>
       <c r="B33" s="63" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C33" s="65">
         <v>1</v>
       </c>
       <c r="D33" s="63" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E33" s="66" t="s">
         <v>192</v>
       </c>
       <c r="F33" s="66" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -7685,22 +7861,22 @@
         <v>88449262751</v>
       </c>
       <c r="B34" s="63" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C34" s="65">
         <v>1</v>
       </c>
       <c r="D34" s="63" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E34" s="66" t="s">
         <v>199</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G34" s="63" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -7875,7 +8051,7 @@
         <v>73</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F9" s="49"/>
     </row>
@@ -7893,7 +8069,7 @@
         <v>74</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F10" s="49"/>
     </row>
@@ -7943,7 +8119,7 @@
         <v>77</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F13" s="49"/>
     </row>
@@ -7993,7 +8169,7 @@
         <v>80</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F16" s="49"/>
     </row>
@@ -8165,7 +8341,7 @@
         <v>88</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F26" s="49"/>
     </row>
@@ -8183,7 +8359,7 @@
         <v>89</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F27" s="49"/>
     </row>
@@ -8201,7 +8377,7 @@
         <v>90</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F28" s="49"/>
     </row>
@@ -8219,7 +8395,7 @@
         <v>91</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F29" s="49"/>
     </row>
@@ -8271,7 +8447,7 @@
         <v>94</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F32" s="49"/>
     </row>
@@ -8307,7 +8483,7 @@
         <v>96</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F34" s="49"/>
     </row>
@@ -8322,7 +8498,7 @@
         <v>145</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E35" s="26"/>
       <c r="F35" s="40"/>
@@ -8341,7 +8517,7 @@
         <v>97</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F36" s="49"/>
     </row>
@@ -8356,7 +8532,7 @@
         <v>147</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E37" s="26"/>
       <c r="F37" s="40"/>
@@ -8372,7 +8548,7 @@
         <v>148</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E38" s="26"/>
       <c r="F38" s="40"/>
@@ -8388,7 +8564,7 @@
         <v>149</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E39" s="26"/>
       <c r="F39" s="40"/>
@@ -8407,7 +8583,7 @@
         <v>98</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F40" s="49"/>
     </row>
@@ -8422,7 +8598,7 @@
         <v>151</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E41" s="26"/>
       <c r="F41" s="40"/>
@@ -8456,7 +8632,7 @@
         <v>153</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E43" s="26"/>
       <c r="F43" s="40"/>
@@ -8472,7 +8648,7 @@
         <v>154</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E44" s="26"/>
       <c r="F44" s="40"/>
@@ -8488,7 +8664,7 @@
         <v>155</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E45" s="26"/>
       <c r="F45" s="40"/>
@@ -8504,7 +8680,7 @@
         <v>156</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E46" s="26"/>
       <c r="F46" s="40"/>
@@ -8520,7 +8696,7 @@
         <v>157</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E47" s="26"/>
       <c r="F47" s="40"/>
@@ -8536,7 +8712,7 @@
         <v>158</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E48" s="26"/>
       <c r="F48" s="40"/>
@@ -8552,7 +8728,7 @@
         <v>159</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E49" s="26"/>
       <c r="F49" s="40"/>
@@ -8695,7 +8871,7 @@
         <v>108</v>
       </c>
       <c r="E57" s="36" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F57" s="49"/>
     </row>
@@ -8713,7 +8889,7 @@
         <v>109</v>
       </c>
       <c r="E58" s="36" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F58" s="49"/>
     </row>
@@ -8731,7 +8907,7 @@
         <v>110</v>
       </c>
       <c r="E59" s="36" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F59" s="49"/>
     </row>
@@ -8749,7 +8925,7 @@
         <v>111</v>
       </c>
       <c r="E60" s="36" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F60" s="49"/>
     </row>
@@ -8801,7 +8977,7 @@
         <v>133</v>
       </c>
       <c r="E63" s="36" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F63" s="49"/>
     </row>
@@ -8816,7 +8992,7 @@
         <v>143</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E64" s="40"/>
       <c r="F64" s="40"/>
@@ -8835,7 +9011,7 @@
         <v>134</v>
       </c>
       <c r="E65" s="36" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F65" s="49"/>
     </row>
@@ -8853,7 +9029,7 @@
         <v>135</v>
       </c>
       <c r="E66" s="36" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F66" s="49"/>
     </row>
@@ -8868,7 +9044,7 @@
         <v>146</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E67" s="40"/>
       <c r="F67" s="40"/>
@@ -8884,7 +9060,7 @@
         <v>147</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E68" s="26"/>
       <c r="F68" s="40"/>
@@ -8900,7 +9076,7 @@
         <v>148</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E69" s="40"/>
       <c r="F69" s="40"/>
@@ -8916,7 +9092,7 @@
         <v>149</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E70" s="26"/>
       <c r="F70" s="40"/>
@@ -8935,7 +9111,7 @@
         <v>136</v>
       </c>
       <c r="E71" s="36" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F71" s="49"/>
     </row>
@@ -9025,7 +9201,7 @@
         <v>89</v>
       </c>
       <c r="E76" s="36" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F76" s="49"/>
     </row>
@@ -9043,7 +9219,7 @@
         <v>91</v>
       </c>
       <c r="E77" s="36" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F77" s="49"/>
     </row>
@@ -9077,7 +9253,7 @@
         <v>77</v>
       </c>
       <c r="E79" s="36" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F79" s="49"/>
     </row>
@@ -9113,7 +9289,7 @@
         <v>80</v>
       </c>
       <c r="E81" s="36" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F81" s="49"/>
     </row>
@@ -9149,7 +9325,7 @@
         <v>117</v>
       </c>
       <c r="E83" s="36" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F83" s="49"/>
     </row>
@@ -9167,7 +9343,7 @@
         <v>118</v>
       </c>
       <c r="E84" s="36" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F84" s="49"/>
     </row>
@@ -9200,7 +9376,7 @@
         <v>145</v>
       </c>
       <c r="D86" s="26" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E86" s="28"/>
       <c r="F86" s="53"/>
@@ -9219,7 +9395,7 @@
         <v>2</v>
       </c>
       <c r="E87" s="36" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F87" s="49"/>
     </row>
@@ -9253,7 +9429,7 @@
         <v>4</v>
       </c>
       <c r="E89" s="36" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F89" s="49"/>
     </row>
@@ -9318,7 +9494,7 @@
         <v>152</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E93" s="27"/>
       <c r="F93" s="54" t="s">
@@ -9354,7 +9530,7 @@
         <v>154</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E95" s="28"/>
       <c r="F95" s="53"/>
@@ -9391,7 +9567,7 @@
         <v>125</v>
       </c>
       <c r="E97" s="36" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F97" s="49"/>
     </row>
@@ -9409,7 +9585,7 @@
         <v>2</v>
       </c>
       <c r="E98" s="36" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F98" s="49"/>
     </row>
@@ -9427,7 +9603,7 @@
         <v>4</v>
       </c>
       <c r="E99" s="36" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F99" s="49"/>
     </row>
@@ -9445,7 +9621,7 @@
         <v>126</v>
       </c>
       <c r="E100" s="36" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F100" s="49"/>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulmann\Documents\Business\OwnBusiness\○네이버스마트스토어 RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964C8247-9057-4E93-99CA-149871855C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E842871C-A6A8-4911-9F12-9B7C00B1D729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2116,39 +2116,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>활주꾸미 /// 연안 활 쭈꾸미</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>급냉 주꾸미 /// 봄 제철 쭈꾸미</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>알주꾸미 /// 탱탱 알주꾸미</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>활 암꽃게 소 /// 연안 활 소암게</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>활 암꽃게 대 /// 연안 활 대암게</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>새꼬막 소 /// 새꼬막 소짜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>새꼬막 중 /// 새꼬막 중짜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>새꼬막 대 /// 새꼬막 대짜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>주꾸미 선택: , (알배기 30~40%/국산), (알없음/중국산), (알배기 40~50%/중국산), 새조개 선택: ,꽃게 선택: , 꼬막 선택: , (4~6미내외), (2~4미내외)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활주꾸미///연안 활 쭈꾸미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급냉 주꾸미///봄 제철 쭈꾸미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알주꾸미///탱탱 알주꾸미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활 암꽃게 소///연안 활 소암게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활 암꽃게 대///연안 활 대암게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새꼬막 소///새꼬막 소짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새꼬막 중///새꼬막 중짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새꼬막 대///새꼬막 대짜</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3697,7 +3697,7 @@
         <v>169</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="F9" s="42" t="s">
         <v>170</v>
@@ -3926,7 +3926,7 @@
         <v>238</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F21" s="42"/>
     </row>
@@ -3944,7 +3944,7 @@
         <v>238</v>
       </c>
       <c r="E22" s="43" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F22" s="42"/>
     </row>
@@ -3962,7 +3962,7 @@
         <v>238</v>
       </c>
       <c r="E23" s="43" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F23" s="42"/>
     </row>
@@ -3980,7 +3980,7 @@
         <v>238</v>
       </c>
       <c r="E24" s="43" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F24" s="42"/>
     </row>
@@ -3998,7 +3998,7 @@
         <v>238</v>
       </c>
       <c r="E25" s="43" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F25" s="42"/>
     </row>
@@ -4016,7 +4016,7 @@
         <v>238</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F26" s="42"/>
     </row>
@@ -4034,7 +4034,7 @@
         <v>238</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F27" s="42"/>
     </row>
@@ -4052,7 +4052,7 @@
         <v>238</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F28" s="42"/>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulmann\Documents\Business\OwnBusiness\○네이버스마트스토어 RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E842871C-A6A8-4911-9F12-9B7C00B1D729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7B50C8-24FE-458F-92F0-D0287AF988D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="532">
   <si>
     <t>보내는사람</t>
   </si>
@@ -2149,6 +2149,38 @@
   </si>
   <si>
     <t>새꼬막 대///새꼬막 대짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활주꾸미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급냉 주꾸미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알주꾸미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활 암꽃게 소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활 암꽃게 대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새꼬막 소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새꼬막 중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새꼬막 대</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3688,7 +3720,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C9" s="42" t="s">
         <v>7</v>
@@ -3917,10 +3949,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>7</v>
+        <v>524</v>
       </c>
       <c r="D21" s="42" t="s">
         <v>238</v>
@@ -3935,10 +3967,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>7</v>
+        <v>525</v>
       </c>
       <c r="D22" s="42" t="s">
         <v>238</v>
@@ -3953,10 +3985,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>7</v>
+        <v>526</v>
       </c>
       <c r="D23" s="42" t="s">
         <v>238</v>
@@ -3971,10 +4003,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>7</v>
+        <v>527</v>
       </c>
       <c r="D24" s="42" t="s">
         <v>238</v>
@@ -3989,10 +4021,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>7</v>
+        <v>528</v>
       </c>
       <c r="D25" s="42" t="s">
         <v>238</v>
@@ -4007,10 +4039,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>7</v>
+        <v>529</v>
       </c>
       <c r="D26" s="42" t="s">
         <v>238</v>
@@ -4025,10 +4057,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>7</v>
+        <v>530</v>
       </c>
       <c r="D27" s="42" t="s">
         <v>238</v>
@@ -4043,10 +4075,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>7</v>
+        <v>531</v>
       </c>
       <c r="D28" s="42" t="s">
         <v>238</v>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulmann\Documents\Business\OwnBusiness\○네이버스마트스토어 RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7B50C8-24FE-458F-92F0-D0287AF988D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6070EA29-E1F0-4A29-B5F8-99C02FF3430A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="531">
   <si>
     <t>보내는사람</t>
   </si>
@@ -2105,10 +2105,6 @@
   </si>
   <si>
     <t>&gt;&gt; 신상품</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>갑오징어, 생물오징어, 생물 호래기, 급냉 호래기, 생물 한치, 실속형 5미, 실속형 10미, 주꾸미, 새조개, 꽃게</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3475,7 +3471,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C8" s="57" t="s">
         <v>114</v>
@@ -3700,7 +3696,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>513</v>
+        <v>7</v>
       </c>
       <c r="C8" s="42" t="s">
         <v>7</v>
@@ -3729,7 +3725,7 @@
         <v>169</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F9" s="42" t="s">
         <v>170</v>
@@ -3952,13 +3948,13 @@
         <v>196</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D21" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F21" s="42"/>
     </row>
@@ -3970,13 +3966,13 @@
         <v>196</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D22" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E22" s="43" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F22" s="42"/>
     </row>
@@ -3988,13 +3984,13 @@
         <v>196</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D23" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E23" s="43" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F23" s="42"/>
     </row>
@@ -4006,13 +4002,13 @@
         <v>196</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D24" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E24" s="43" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F24" s="42"/>
     </row>
@@ -4024,13 +4020,13 @@
         <v>196</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D25" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E25" s="43" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F25" s="42"/>
     </row>
@@ -4042,13 +4038,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D26" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F26" s="42"/>
     </row>
@@ -4060,13 +4056,13 @@
         <v>196</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D27" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F27" s="42"/>
     </row>
@@ -4078,13 +4074,13 @@
         <v>196</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D28" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F28" s="42"/>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulmann\Documents\Business\OwnBusiness\○네이버스마트스토어 RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6070EA29-E1F0-4A29-B5F8-99C02FF3430A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4409C1-CA91-489F-B7B0-D990A5D05615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2112,10 +2112,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>주꾸미 선택: , (알배기 30~40%/국산), (알없음/중국산), (알배기 40~50%/중국산), 새조개 선택: ,꽃게 선택: , 꼬막 선택: , (4~6미내외), (2~4미내외)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>활주꾸미///연안 활 쭈꾸미</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2177,6 +2173,10 @@
   </si>
   <si>
     <t>새꼬막 대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주꾸미 선택: , (알배기 30~40%/국산), (알없음/중국산), (알배기 40~50%/중국산), 새조개 선택: ,꽃게 선택: , 꼬막 선택: , (4-6미내외), (2-4미내외)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3725,7 +3725,7 @@
         <v>169</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="F9" s="42" t="s">
         <v>170</v>
@@ -3948,13 +3948,13 @@
         <v>196</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D21" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F21" s="42"/>
     </row>
@@ -3966,13 +3966,13 @@
         <v>196</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D22" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E22" s="43" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F22" s="42"/>
     </row>
@@ -3984,13 +3984,13 @@
         <v>196</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D23" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E23" s="43" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F23" s="42"/>
     </row>
@@ -4002,13 +4002,13 @@
         <v>196</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D24" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E24" s="43" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F24" s="42"/>
     </row>
@@ -4020,13 +4020,13 @@
         <v>196</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D25" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E25" s="43" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F25" s="42"/>
     </row>
@@ -4038,13 +4038,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D26" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F26" s="42"/>
     </row>
@@ -4056,13 +4056,13 @@
         <v>196</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D27" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F27" s="42"/>
     </row>
@@ -4074,13 +4074,13 @@
         <v>196</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D28" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F28" s="42"/>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulmann\Documents\Business\OwnBusiness\○네이버스마트스토어 RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4409C1-CA91-489F-B7B0-D990A5D05615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077174BF-E5DF-4482-9191-5CC2A190A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3716,7 +3716,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>196</v>
+        <v>114</v>
       </c>
       <c r="C9" s="42" t="s">
         <v>7</v>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulmann\Documents\Business\OwnBusiness\○네이버스마트스토어 RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077174BF-E5DF-4482-9191-5CC2A190A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB35170C-2767-49BC-9446-0DE91455DE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="531">
   <si>
     <t>보내는사람</t>
   </si>
@@ -2176,7 +2176,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>주꾸미 선택: , (알배기 30~40%/국산), (알없음/중국산), (알배기 40~50%/중국산), 새조개 선택: ,꽃게 선택: , 꼬막 선택: , (4-6미내외), (2-4미내외)</t>
+    <t xml:space="preserve">주꾸미 선택: , (알배기 30~40%/국산), (알없음/중국산), (알배기 40~50%/중국산), 새조개 선택: ,꽃게 선택: , 꼬막 선택: </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3541,7 +3541,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE8C8B0-87AB-4B5A-85D1-21EF511A776A}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultColWidth="11.4140625" defaultRowHeight="14.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="2" bestFit="1" customWidth="1"/>
@@ -3739,10 +3739,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>192</v>
+        <v>114</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>204</v>
+        <v>7</v>
       </c>
       <c r="D10" s="42" t="s">
         <v>166</v>
@@ -3750,47 +3750,45 @@
       <c r="E10" s="43" t="s">
         <v>205</v>
       </c>
-      <c r="F10" s="42" t="s">
-        <v>206</v>
-      </c>
+      <c r="F10" s="42"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="42">
         <v>10</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>364</v>
+        <v>192</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>363</v>
+        <v>204</v>
       </c>
       <c r="D11" s="42" t="s">
         <v>166</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>353</v>
-      </c>
-      <c r="F11" s="42"/>
+        <v>205</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="42">
         <v>11</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>7</v>
+        <v>364</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>7</v>
+        <v>363</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>330</v>
+        <v>166</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>329</v>
-      </c>
-      <c r="F12" s="42" t="s">
-        <v>239</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="F12" s="42"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="42">
@@ -3806,10 +3804,10 @@
         <v>330</v>
       </c>
       <c r="E13" s="43" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="F13" s="42" t="s">
-        <v>348</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
@@ -3820,15 +3818,17 @@
         <v>7</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>375</v>
+        <v>7</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>169</v>
+        <v>330</v>
       </c>
       <c r="E14" s="43" t="s">
-        <v>376</v>
-      </c>
-      <c r="F14" s="42"/>
+        <v>349</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="42">
@@ -3838,13 +3838,13 @@
         <v>7</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D15" s="42" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>205</v>
+        <v>376</v>
       </c>
       <c r="F15" s="42"/>
     </row>
@@ -3859,10 +3859,10 @@
         <v>369</v>
       </c>
       <c r="D16" s="42" t="s">
-        <v>215</v>
-      </c>
-      <c r="E16" s="42" t="s">
-        <v>326</v>
+        <v>166</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>205</v>
       </c>
       <c r="F16" s="42"/>
     </row>
@@ -3874,51 +3874,51 @@
         <v>7</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>7</v>
+        <v>369</v>
       </c>
       <c r="D17" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="E17" s="43" t="s">
-        <v>331</v>
-      </c>
-      <c r="F17" s="42" t="s">
-        <v>332</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="F17" s="42"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="42">
         <v>17</v>
       </c>
       <c r="B18" s="42" t="s">
-        <v>196</v>
+        <v>7</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>357</v>
+        <v>7</v>
       </c>
       <c r="D18" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>361</v>
-      </c>
-      <c r="F18" s="42"/>
+        <v>331</v>
+      </c>
+      <c r="F18" s="42" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="42">
         <v>18</v>
       </c>
       <c r="B19" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>7</v>
+        <v>357</v>
       </c>
       <c r="D19" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F19" s="42"/>
     </row>
@@ -3930,13 +3930,13 @@
         <v>7</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>370</v>
+        <v>7</v>
       </c>
       <c r="D20" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="F20" s="42"/>
     </row>
@@ -3945,16 +3945,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="42" t="s">
-        <v>196</v>
+        <v>7</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>522</v>
+        <v>370</v>
       </c>
       <c r="D21" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>514</v>
+        <v>371</v>
       </c>
       <c r="F21" s="42"/>
     </row>
@@ -3966,13 +3966,13 @@
         <v>196</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D22" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E22" s="43" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F22" s="42"/>
     </row>
@@ -3984,13 +3984,13 @@
         <v>196</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D23" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E23" s="43" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F23" s="42"/>
     </row>
@@ -4002,13 +4002,13 @@
         <v>196</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D24" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E24" s="43" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F24" s="42"/>
     </row>
@@ -4020,13 +4020,13 @@
         <v>196</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D25" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E25" s="43" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F25" s="42"/>
     </row>
@@ -4038,13 +4038,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D26" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F26" s="42"/>
     </row>
@@ -4056,13 +4056,13 @@
         <v>196</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D27" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F27" s="42"/>
     </row>
@@ -4074,13 +4074,13 @@
         <v>196</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D28" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F28" s="42"/>
     </row>
@@ -4089,30 +4089,28 @@
         <v>28</v>
       </c>
       <c r="B29" s="42" t="s">
-        <v>510</v>
+        <v>196</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>204</v>
+        <v>529</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="E29" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="59" t="s">
-        <v>207</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>521</v>
+      </c>
+      <c r="F29" s="42"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="42">
         <v>29</v>
       </c>
       <c r="B30" s="42" t="s">
-        <v>7</v>
+        <v>510</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>373</v>
+        <v>204</v>
       </c>
       <c r="D30" s="42" t="s">
         <v>171</v>
@@ -4120,8 +4118,8 @@
       <c r="E30" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="42" t="s">
-        <v>243</v>
+      <c r="F30" s="59" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
@@ -4132,7 +4130,7 @@
         <v>7</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D31" s="42" t="s">
         <v>171</v>
@@ -4152,7 +4150,7 @@
         <v>7</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="D32" s="42" t="s">
         <v>171</v>
@@ -4172,7 +4170,7 @@
         <v>7</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>248</v>
+        <v>368</v>
       </c>
       <c r="D33" s="42" t="s">
         <v>171</v>
@@ -4192,15 +4190,17 @@
         <v>7</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>378</v>
+        <v>248</v>
       </c>
       <c r="D34" s="42" t="s">
-        <v>169</v>
-      </c>
-      <c r="E34" s="43" t="s">
-        <v>376</v>
-      </c>
-      <c r="F34" s="42"/>
+        <v>171</v>
+      </c>
+      <c r="E34" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="42" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="42">
@@ -4210,13 +4210,13 @@
         <v>7</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E35" s="43" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F35" s="42"/>
     </row>
@@ -4231,10 +4231,10 @@
         <v>380</v>
       </c>
       <c r="D36" s="42" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E36" s="43" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F36" s="42"/>
     </row>
@@ -4246,35 +4246,35 @@
         <v>7</v>
       </c>
       <c r="C37" s="42" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D37" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="E37" s="42" t="s">
-        <v>379</v>
-      </c>
-      <c r="F37" s="42" t="s">
-        <v>243</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>376</v>
+      </c>
+      <c r="F37" s="42"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" s="42">
         <v>37</v>
       </c>
       <c r="B38" s="42" t="s">
-        <v>196</v>
+        <v>7</v>
       </c>
       <c r="C38" s="42" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="D38" s="42" t="s">
         <v>171</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="42"/>
+        <v>379</v>
+      </c>
+      <c r="F38" s="42" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="42">
@@ -4284,13 +4284,13 @@
         <v>196</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D39" s="42" t="s">
-        <v>215</v>
+        <v>171</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>326</v>
+        <v>9</v>
       </c>
       <c r="F39" s="42"/>
     </row>
@@ -4299,10 +4299,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C40" s="42" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="D40" s="42" t="s">
         <v>215</v>
@@ -4320,17 +4320,15 @@
         <v>7</v>
       </c>
       <c r="C41" s="42" t="s">
-        <v>324</v>
+        <v>363</v>
       </c>
       <c r="D41" s="42" t="s">
         <v>215</v>
       </c>
       <c r="E41" s="42" t="s">
-        <v>217</v>
-      </c>
-      <c r="F41" s="59" t="s">
-        <v>325</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="F41" s="42"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" s="42">
@@ -4340,16 +4338,16 @@
         <v>7</v>
       </c>
       <c r="C42" s="42" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="D42" s="42" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="E42" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="42" t="s">
-        <v>224</v>
+        <v>217</v>
+      </c>
+      <c r="F42" s="59" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.4">
@@ -4360,15 +4358,17 @@
         <v>7</v>
       </c>
       <c r="C43" s="42" t="s">
-        <v>394</v>
+        <v>7</v>
       </c>
       <c r="D43" s="42" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="F43" s="42"/>
+        <v>8</v>
+      </c>
+      <c r="F43" s="42" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" s="42">
@@ -4378,17 +4378,15 @@
         <v>7</v>
       </c>
       <c r="C44" s="42" t="s">
-        <v>7</v>
+        <v>394</v>
       </c>
       <c r="D44" s="42" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="E44" s="42" t="s">
-        <v>225</v>
-      </c>
-      <c r="F44" s="42" t="s">
-        <v>226</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="F44" s="42"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" s="42">
@@ -4404,10 +4402,10 @@
         <v>172</v>
       </c>
       <c r="E45" s="42" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F45" s="42" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.4">
@@ -4424,10 +4422,10 @@
         <v>172</v>
       </c>
       <c r="E46" s="42" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="F46" s="42" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.4">
@@ -4444,10 +4442,10 @@
         <v>172</v>
       </c>
       <c r="E47" s="42" t="s">
-        <v>358</v>
+        <v>244</v>
       </c>
       <c r="F47" s="42" t="s">
-        <v>359</v>
+        <v>245</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.4">
@@ -4461,13 +4459,13 @@
         <v>7</v>
       </c>
       <c r="D48" s="42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E48" s="42" t="s">
-        <v>229</v>
+        <v>358</v>
       </c>
       <c r="F48" s="42" t="s">
-        <v>230</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.4">
@@ -4484,10 +4482,10 @@
         <v>173</v>
       </c>
       <c r="E49" s="42" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F49" s="42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.4">
@@ -4504,10 +4502,10 @@
         <v>173</v>
       </c>
       <c r="E50" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F50" s="42" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.4">
@@ -4524,10 +4522,10 @@
         <v>173</v>
       </c>
       <c r="E51" s="42" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F51" s="42" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.4">
@@ -4538,54 +4536,54 @@
         <v>7</v>
       </c>
       <c r="C52" s="42" t="s">
-        <v>360</v>
+        <v>7</v>
       </c>
       <c r="D52" s="42" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="E52" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="F52" s="42"/>
-    </row>
-    <row r="53" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+        <v>240</v>
+      </c>
+      <c r="F52" s="42" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53" s="42">
         <v>52</v>
       </c>
-      <c r="B53" s="57" t="s">
-        <v>124</v>
+      <c r="B53" s="42" t="s">
+        <v>7</v>
       </c>
       <c r="C53" s="42" t="s">
-        <v>203</v>
+        <v>360</v>
       </c>
       <c r="D53" s="42" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E53" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" s="42" t="s">
-        <v>209</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="F53" s="42"/>
     </row>
     <row r="54" spans="1:6" ht="16" x14ac:dyDescent="0.45">
       <c r="A54" s="42">
         <v>53</v>
       </c>
       <c r="B54" s="57" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="C54" s="42" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D54" s="42" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E54" s="42" t="s">
         <v>9</v>
       </c>
       <c r="F54" s="42" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="16" x14ac:dyDescent="0.45">
@@ -4593,38 +4591,38 @@
         <v>54</v>
       </c>
       <c r="B55" s="57" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="C55" s="42" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D55" s="42" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="E55" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="F55" s="42"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+      <c r="F55" s="42" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="16" x14ac:dyDescent="0.45">
       <c r="A56" s="42">
         <v>55</v>
       </c>
-      <c r="B56" s="42" t="s">
-        <v>7</v>
+      <c r="B56" s="57" t="s">
+        <v>124</v>
       </c>
       <c r="C56" s="42" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="D56" s="42" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="E56" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="F56" s="42" t="s">
-        <v>220</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="F56" s="42"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A57" s="42">
@@ -4634,7 +4632,7 @@
         <v>7</v>
       </c>
       <c r="C57" s="42" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="D57" s="42" t="s">
         <v>215</v>
@@ -4643,7 +4641,7 @@
         <v>326</v>
       </c>
       <c r="F57" s="42" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.4">
@@ -4654,7 +4652,7 @@
         <v>7</v>
       </c>
       <c r="C58" s="42" t="s">
-        <v>372</v>
+        <v>242</v>
       </c>
       <c r="D58" s="42" t="s">
         <v>215</v>
@@ -4674,7 +4672,7 @@
         <v>7</v>
       </c>
       <c r="C59" s="42" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="D59" s="42" t="s">
         <v>215</v>
@@ -4682,7 +4680,9 @@
       <c r="E59" s="42" t="s">
         <v>326</v>
       </c>
-      <c r="F59" s="42"/>
+      <c r="F59" s="42" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A60" s="42">
@@ -4692,7 +4692,7 @@
         <v>7</v>
       </c>
       <c r="C60" s="42" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="D60" s="42" t="s">
         <v>215</v>
@@ -4710,15 +4710,33 @@
         <v>7</v>
       </c>
       <c r="C61" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="D61" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="E61" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="F61" s="42"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A62" s="42">
+        <v>61</v>
+      </c>
+      <c r="B62" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="D61" s="42" t="s">
+      <c r="C62" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="42" t="s">
         <v>166</v>
       </c>
-      <c r="E61" s="42" t="s">
+      <c r="E62" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="F61" s="42" t="s">
+      <c r="F62" s="42" t="s">
         <v>222</v>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulmann\Documents\Business\OwnBusiness\○네이버스마트스토어 RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB35170C-2767-49BC-9446-0DE91455DE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339801E2-120A-4C04-A19F-07A2075C4767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="532">
   <si>
     <t>보내는사람</t>
   </si>
@@ -2177,6 +2177,10 @@
   </si>
   <si>
     <t xml:space="preserve">주꾸미 선택: , (알배기 30~40%/국산), (알없음/중국산), (알배기 40~50%/중국산), 새조개 선택: ,꽃게 선택: , 꼬막 선택: </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\(.*?\)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3748,7 +3752,7 @@
         <v>166</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>205</v>
+        <v>531</v>
       </c>
       <c r="F10" s="42"/>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulmann\Documents\Business\OwnBusiness\○네이버스마트스토어 RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339801E2-120A-4C04-A19F-07A2075C4767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59343015-3BF3-4590-9270-AF44BB0A3FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="534">
   <si>
     <t>보내는사람</t>
   </si>
@@ -2100,18 +2100,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>장어</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>&gt;&gt; 신상품</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>갑오징어, 생물오징어, 생물 호래기, 급냉 호래기, 생물 한치, 실속형 5미, 실속형 10미, 주꾸미, 새조개, 꽃게, 새꼬막</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>활주꾸미///연안 활 쭈꾸미</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2176,11 +2168,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">주꾸미 선택: , (알배기 30~40%/국산), (알없음/중국산), (알배기 40~50%/중국산), 새조개 선택: ,꽃게 선택: , 꼬막 선택: </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>\(.*?\)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장어, 초생강, 명이나물, 순한맛소스, 매운맛소스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑오징어, 생물오징어, 생물 호래기, 급냉 호래기, 생물 한치, 실속형 5미, 실속형 10미, 주꾸미, 새조개, 꽃게, 새꼬막, 실치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">호래기 선택: , 오징어 선택: , 주꾸미 선택: , (알배기 30~40%/국산), (알없음/중국산), (알배기 40~50%/중국산), 새조개 선택: ,꽃게 선택: , 꼬막 선택: , 실치 선택: </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생물 실치회///생물 실치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실치회</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3475,7 +3483,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="C8" s="57" t="s">
         <v>114</v>
@@ -3519,7 +3527,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="C12" s="57" t="s">
         <v>510</v>
@@ -3545,7 +3553,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE8C8B0-87AB-4B5A-85D1-21EF511A776A}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr defaultColWidth="11.4140625" defaultRowHeight="14.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="2" bestFit="1" customWidth="1"/>
@@ -3729,13 +3737,13 @@
         <v>169</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F9" s="42" t="s">
         <v>170</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
@@ -3752,7 +3760,7 @@
         <v>166</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F10" s="42"/>
     </row>
@@ -3970,13 +3978,13 @@
         <v>196</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D22" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E22" s="43" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F22" s="42"/>
     </row>
@@ -3988,13 +3996,13 @@
         <v>196</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D23" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E23" s="43" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F23" s="42"/>
     </row>
@@ -4006,13 +4014,13 @@
         <v>196</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D24" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E24" s="43" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F24" s="42"/>
     </row>
@@ -4024,13 +4032,13 @@
         <v>196</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D25" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E25" s="43" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F25" s="42"/>
     </row>
@@ -4042,13 +4050,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D26" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F26" s="42"/>
     </row>
@@ -4060,13 +4068,13 @@
         <v>196</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D27" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F27" s="42"/>
     </row>
@@ -4078,13 +4086,13 @@
         <v>196</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D28" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F28" s="42"/>
     </row>
@@ -4096,13 +4104,13 @@
         <v>196</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D29" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F29" s="42"/>
     </row>
@@ -4111,30 +4119,28 @@
         <v>29</v>
       </c>
       <c r="B30" s="42" t="s">
-        <v>510</v>
+        <v>196</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>204</v>
+        <v>533</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="E30" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="59" t="s">
-        <v>207</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>532</v>
+      </c>
+      <c r="F30" s="42"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="42">
         <v>30</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>7</v>
+        <v>510</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>373</v>
+        <v>204</v>
       </c>
       <c r="D31" s="42" t="s">
         <v>171</v>
@@ -4142,8 +4148,8 @@
       <c r="E31" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="F31" s="42" t="s">
-        <v>243</v>
+      <c r="F31" s="59" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
@@ -4154,7 +4160,7 @@
         <v>7</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D32" s="42" t="s">
         <v>171</v>
@@ -4174,7 +4180,7 @@
         <v>7</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="D33" s="42" t="s">
         <v>171</v>
@@ -4194,7 +4200,7 @@
         <v>7</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>248</v>
+        <v>368</v>
       </c>
       <c r="D34" s="42" t="s">
         <v>171</v>
@@ -4214,15 +4220,17 @@
         <v>7</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>378</v>
+        <v>248</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>169</v>
-      </c>
-      <c r="E35" s="43" t="s">
-        <v>376</v>
-      </c>
-      <c r="F35" s="42"/>
+        <v>171</v>
+      </c>
+      <c r="E35" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="42" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="42">
@@ -4232,13 +4240,13 @@
         <v>7</v>
       </c>
       <c r="C36" s="42" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D36" s="42" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E36" s="43" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F36" s="42"/>
     </row>
@@ -4253,10 +4261,10 @@
         <v>380</v>
       </c>
       <c r="D37" s="42" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E37" s="43" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F37" s="42"/>
     </row>
@@ -4268,35 +4276,35 @@
         <v>7</v>
       </c>
       <c r="C38" s="42" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D38" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="E38" s="42" t="s">
-        <v>379</v>
-      </c>
-      <c r="F38" s="42" t="s">
-        <v>243</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="E38" s="43" t="s">
+        <v>376</v>
+      </c>
+      <c r="F38" s="42"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="42">
         <v>38</v>
       </c>
       <c r="B39" s="42" t="s">
-        <v>196</v>
+        <v>7</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="D39" s="42" t="s">
         <v>171</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="42"/>
+        <v>379</v>
+      </c>
+      <c r="F39" s="42" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="42">
@@ -4306,13 +4314,13 @@
         <v>196</v>
       </c>
       <c r="C40" s="42" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D40" s="42" t="s">
-        <v>215</v>
+        <v>171</v>
       </c>
       <c r="E40" s="42" t="s">
-        <v>326</v>
+        <v>9</v>
       </c>
       <c r="F40" s="42"/>
     </row>
@@ -4321,10 +4329,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="42" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C41" s="42" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="D41" s="42" t="s">
         <v>215</v>
@@ -4342,17 +4350,15 @@
         <v>7</v>
       </c>
       <c r="C42" s="42" t="s">
-        <v>324</v>
+        <v>363</v>
       </c>
       <c r="D42" s="42" t="s">
         <v>215</v>
       </c>
       <c r="E42" s="42" t="s">
-        <v>217</v>
-      </c>
-      <c r="F42" s="59" t="s">
-        <v>325</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="F42" s="42"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" s="42">
@@ -4362,16 +4368,16 @@
         <v>7</v>
       </c>
       <c r="C43" s="42" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="D43" s="42" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="42" t="s">
-        <v>224</v>
+        <v>217</v>
+      </c>
+      <c r="F43" s="59" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.4">
@@ -4382,15 +4388,17 @@
         <v>7</v>
       </c>
       <c r="C44" s="42" t="s">
-        <v>394</v>
+        <v>7</v>
       </c>
       <c r="D44" s="42" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="E44" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="F44" s="42"/>
+        <v>8</v>
+      </c>
+      <c r="F44" s="42" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" s="42">
@@ -4400,17 +4408,15 @@
         <v>7</v>
       </c>
       <c r="C45" s="42" t="s">
-        <v>7</v>
+        <v>394</v>
       </c>
       <c r="D45" s="42" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="E45" s="42" t="s">
-        <v>225</v>
-      </c>
-      <c r="F45" s="42" t="s">
-        <v>226</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="F45" s="42"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46" s="42">
@@ -4426,10 +4432,10 @@
         <v>172</v>
       </c>
       <c r="E46" s="42" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F46" s="42" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.4">
@@ -4446,10 +4452,10 @@
         <v>172</v>
       </c>
       <c r="E47" s="42" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="F47" s="42" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.4">
@@ -4466,10 +4472,10 @@
         <v>172</v>
       </c>
       <c r="E48" s="42" t="s">
-        <v>358</v>
+        <v>244</v>
       </c>
       <c r="F48" s="42" t="s">
-        <v>359</v>
+        <v>245</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.4">
@@ -4483,13 +4489,13 @@
         <v>7</v>
       </c>
       <c r="D49" s="42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E49" s="42" t="s">
-        <v>229</v>
+        <v>358</v>
       </c>
       <c r="F49" s="42" t="s">
-        <v>230</v>
+        <v>359</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.4">
@@ -4506,10 +4512,10 @@
         <v>173</v>
       </c>
       <c r="E50" s="42" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F50" s="42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.4">
@@ -4526,10 +4532,10 @@
         <v>173</v>
       </c>
       <c r="E51" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F51" s="42" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.4">
@@ -4546,10 +4552,10 @@
         <v>173</v>
       </c>
       <c r="E52" s="42" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F52" s="42" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.4">
@@ -4560,54 +4566,54 @@
         <v>7</v>
       </c>
       <c r="C53" s="42" t="s">
-        <v>360</v>
+        <v>7</v>
       </c>
       <c r="D53" s="42" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="E53" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="F53" s="42"/>
-    </row>
-    <row r="54" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+        <v>240</v>
+      </c>
+      <c r="F53" s="42" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54" s="42">
         <v>53</v>
       </c>
-      <c r="B54" s="57" t="s">
-        <v>124</v>
+      <c r="B54" s="42" t="s">
+        <v>7</v>
       </c>
       <c r="C54" s="42" t="s">
-        <v>203</v>
+        <v>360</v>
       </c>
       <c r="D54" s="42" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E54" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" s="42" t="s">
-        <v>209</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="F54" s="42"/>
     </row>
     <row r="55" spans="1:6" ht="16" x14ac:dyDescent="0.45">
       <c r="A55" s="42">
         <v>54</v>
       </c>
       <c r="B55" s="57" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="C55" s="42" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D55" s="42" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E55" s="42" t="s">
         <v>9</v>
       </c>
       <c r="F55" s="42" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="16" x14ac:dyDescent="0.45">
@@ -4615,38 +4621,38 @@
         <v>55</v>
       </c>
       <c r="B56" s="57" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="C56" s="42" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D56" s="42" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="E56" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="F56" s="42"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+      <c r="F56" s="42" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="16" x14ac:dyDescent="0.45">
       <c r="A57" s="42">
         <v>56</v>
       </c>
-      <c r="B57" s="42" t="s">
-        <v>7</v>
+      <c r="B57" s="57" t="s">
+        <v>124</v>
       </c>
       <c r="C57" s="42" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="D57" s="42" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="E57" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="F57" s="42" t="s">
-        <v>220</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="F57" s="42"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A58" s="42">
@@ -4656,7 +4662,7 @@
         <v>7</v>
       </c>
       <c r="C58" s="42" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="D58" s="42" t="s">
         <v>215</v>
@@ -4665,7 +4671,7 @@
         <v>326</v>
       </c>
       <c r="F58" s="42" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.4">
@@ -4676,7 +4682,7 @@
         <v>7</v>
       </c>
       <c r="C59" s="42" t="s">
-        <v>372</v>
+        <v>242</v>
       </c>
       <c r="D59" s="42" t="s">
         <v>215</v>
@@ -4696,7 +4702,7 @@
         <v>7</v>
       </c>
       <c r="C60" s="42" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="D60" s="42" t="s">
         <v>215</v>
@@ -4704,7 +4710,9 @@
       <c r="E60" s="42" t="s">
         <v>326</v>
       </c>
-      <c r="F60" s="42"/>
+      <c r="F60" s="42" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A61" s="42">
@@ -4714,7 +4722,7 @@
         <v>7</v>
       </c>
       <c r="C61" s="42" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="D61" s="42" t="s">
         <v>215</v>
@@ -4732,15 +4740,33 @@
         <v>7</v>
       </c>
       <c r="C62" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="D62" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="E62" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="F62" s="42"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A63" s="42">
+        <v>62</v>
+      </c>
+      <c r="B63" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="D62" s="42" t="s">
+      <c r="C63" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="42" t="s">
         <v>166</v>
       </c>
-      <c r="E62" s="42" t="s">
+      <c r="E63" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="F62" s="42" t="s">
+      <c r="F63" s="42" t="s">
         <v>222</v>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulmann\Documents\Business\OwnBusiness\○네이버스마트스토어 RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59343015-3BF3-4590-9270-AF44BB0A3FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C47AE2-D913-4E16-A6E6-49DE4CD381C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2180,15 +2180,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">호래기 선택: , 오징어 선택: , 주꾸미 선택: , (알배기 30~40%/국산), (알없음/중국산), (알배기 40~50%/중국산), 새조개 선택: ,꽃게 선택: , 꼬막 선택: , 실치 선택: </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>생물 실치회///생물 실치</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>실치회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">호래기 선택: , 오징어 선택: , 오징어선택: , 주꾸미 선택: , (알배기 30~40%/국산), (알없음/중국산), (알배기 40~50%/중국산), 새조개 선택: ,꽃게 선택: , 꼬막 선택: , 실치 선택: </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3737,7 +3737,7 @@
         <v>169</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F9" s="42" t="s">
         <v>170</v>
@@ -4122,13 +4122,13 @@
         <v>196</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D30" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E30" s="43" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F30" s="42"/>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faulmann\Documents\Business\OwnBusiness\○네이버스마트스토어 RPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C47AE2-D913-4E16-A6E6-49DE4CD381C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96865B78-CE94-48A2-A569-506F2E22F386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1765,6 +1765,105 @@
   </si>
   <si>
     <t>수정된 주문</t>
+  </si>
+  <si>
+    <t>장어 발주양식</t>
+  </si>
+  <si>
+    <t>장어 발주양식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;&gt; 신상품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활주꾸미///연안 활 쭈꾸미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급냉 주꾸미///봄 제철 쭈꾸미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알주꾸미///탱탱 알주꾸미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활 암꽃게 소///연안 활 소암게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활 암꽃게 대///연안 활 대암게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새꼬막 소///새꼬막 소짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새꼬막 중///새꼬막 중짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새꼬막 대///새꼬막 대짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활주꾸미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급냉 주꾸미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알주꾸미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활 암꽃게 소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활 암꽃게 대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새꼬막 소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새꼬막 중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새꼬막 대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\(.*?\)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장어, 초생강, 명이나물, 순한맛소스, 매운맛소스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑오징어, 생물오징어, 생물 호래기, 급냉 호래기, 생물 한치, 실속형 5미, 실속형 10미, 주꾸미, 새조개, 꽃게, 새꼬막, 실치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생물 실치회///생물 실치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실치회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">호래기 선택: , 오징어 선택: , 오징어선택: , 주꾸미 선택: , (알배기 30~40%/국산), (알없음/중국산), (알배기 40~50%/중국산), 새조개 선택: ,꽃게 선택: , 꼬막 선택: , 실치 선택: </t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1968,7 +2067,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">함께 즐기는 동해안 골뱅이: , 초코오징어 선택: , 한정수량 생물오징어 /, 마릿수 선택: , 제철 생물 호래기 / , A급 온다리, (생물), (손질후 600g내외), (초벌후 480g내외), 소스 추가: , 초생강 추가: , 장어 선택: , </t>
+      <t xml:space="preserve">함께 즐기는 동해안 골뱅이: , 초코오징어 선택: , 한정수량 생물오징어 /, 마릿수 선택: , 제철 생물 호래기 / , A급 온다리, (생물), (손질후 600g내외), (초벌후 480g내외), (초벌후 250g내외), 소스 추가: , 초생강 추가: , 장어 선택: , </t>
     </r>
     <r>
       <rPr>
@@ -2090,105 +2189,6 @@
       </rPr>
       <t>아이스팩 추가: , (기본 2개 제공), 꿀조합! 오로바일렌 올리브오일&amp;초장: , 활멍게 선택:</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장어 발주양식</t>
-  </si>
-  <si>
-    <t>장어 발주양식</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;&gt; 신상품</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>활주꾸미///연안 활 쭈꾸미</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>급냉 주꾸미///봄 제철 쭈꾸미</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>알주꾸미///탱탱 알주꾸미</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>활 암꽃게 소///연안 활 소암게</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>활 암꽃게 대///연안 활 대암게</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>새꼬막 소///새꼬막 소짜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>새꼬막 중///새꼬막 중짜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>새꼬막 대///새꼬막 대짜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>활주꾸미</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>급냉 주꾸미</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>알주꾸미</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>활 암꽃게 소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>활 암꽃게 대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>새꼬막 소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>새꼬막 중</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>새꼬막 대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>\(.*?\)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장어, 초생강, 명이나물, 순한맛소스, 매운맛소스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>갑오징어, 생물오징어, 생물 호래기, 급냉 호래기, 생물 한치, 실속형 5미, 실속형 10미, 주꾸미, 새조개, 꽃게, 새꼬막, 실치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생물 실치회///생물 실치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>실치회</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">호래기 선택: , 오징어 선택: , 오징어선택: , 주꾸미 선택: , (알배기 30~40%/국산), (알없음/중국산), (알배기 40~50%/중국산), 새조개 선택: ,꽃게 선택: , 꼬막 선택: , 실치 선택: </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3483,7 +3483,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C8" s="57" t="s">
         <v>114</v>
@@ -3527,10 +3527,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
@@ -3717,7 +3717,7 @@
         <v>169</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>508</v>
+        <v>533</v>
       </c>
       <c r="F8" s="42" t="s">
         <v>170</v>
@@ -3737,13 +3737,13 @@
         <v>169</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F9" s="42" t="s">
         <v>170</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
@@ -3760,7 +3760,7 @@
         <v>166</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F10" s="42"/>
     </row>
@@ -3978,13 +3978,13 @@
         <v>196</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D22" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E22" s="43" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F22" s="42"/>
     </row>
@@ -3996,13 +3996,13 @@
         <v>196</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D23" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E23" s="43" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F23" s="42"/>
     </row>
@@ -4014,13 +4014,13 @@
         <v>196</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D24" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E24" s="43" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F24" s="42"/>
     </row>
@@ -4032,13 +4032,13 @@
         <v>196</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D25" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E25" s="43" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F25" s="42"/>
     </row>
@@ -4050,13 +4050,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D26" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F26" s="42"/>
     </row>
@@ -4068,13 +4068,13 @@
         <v>196</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D27" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F27" s="42"/>
     </row>
@@ -4086,13 +4086,13 @@
         <v>196</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D28" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F28" s="42"/>
     </row>
@@ -4104,13 +4104,13 @@
         <v>196</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D29" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F29" s="42"/>
     </row>
@@ -4122,13 +4122,13 @@
         <v>196</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D30" s="42" t="s">
         <v>238</v>
       </c>
       <c r="E30" s="43" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F30" s="42"/>
     </row>
@@ -4137,7 +4137,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="42" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C31" s="42" t="s">
         <v>204</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A106" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B106" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C106" s="33" t="s">
         <v>142</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A107" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B107" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C107" s="33" t="s">
         <v>143</v>
@@ -6645,10 +6645,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A108" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B108" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C108" s="33" t="s">
         <v>144</v>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A109" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B109" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C109" s="33" t="s">
         <v>145</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A110" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B110" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C110" s="33" t="s">
         <v>146</v>
@@ -6699,10 +6699,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A111" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B111" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C111" s="33" t="s">
         <v>147</v>
@@ -6717,10 +6717,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A112" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B112" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C112" s="33" t="s">
         <v>148</v>
@@ -6735,10 +6735,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A113" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B113" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C113" s="33" t="s">
         <v>149</v>
@@ -6753,10 +6753,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A114" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B114" s="32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C114" s="33" t="s">
         <v>150</v>
